--- a/tame_output/ON/bt/strategyON_20240809.xlsx
+++ b/tame_output/ON/bt/strategyON_20240809.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.2%</t>
+          <t>421.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-625.7%</t>
+          <t>-634.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-178.6%</t>
+          <t>-182.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.3%</t>
+          <t>-156.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-182.7%</t>
+          <t>-191.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-43.4%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.626458215463892</v>
+        <v>-6.716749561582301</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5031018507842644</v>
+        <v>0.4669853123369005</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3119688958444667</v>
+        <v>-0.4022602419628756</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.966860223776889</v>
+        <v>2.912685416105843</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.377458416780311</v>
+        <v>-6.46774976289872</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6156081114813556</v>
+        <v>0.5794915730339918</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06296909716088606</v>
+        <v>-0.1532604432792949</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.129166444210696</v>
+        <v>3.074991636539651</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.483048406553415</v>
+        <v>-6.573339752671824</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.445396185972895</v>
+        <v>0.4092796475255316</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1685590869339904</v>
+        <v>-0.2588504330523992</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937836520747615</v>
+        <v>2.883661713076569</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.501783308672012</v>
+        <v>-6.592074654790421</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4864465670025426</v>
+        <v>0.4503300285551788</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1741550965941217</v>
+        <v>-0.2644464427125305</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.983023256828622</v>
+        <v>2.928848449157577</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.353843267264413</v>
+        <v>-6.444134613382822</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4257436608774148</v>
+        <v>0.3896271224300509</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1538341806855641</v>
+        <v>-0.244125526803973</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.875336883685589</v>
+        <v>2.821162076014544</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.300873745010424</v>
+        <v>-6.391165091128833</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4382174835255319</v>
+        <v>0.4021009450781685</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1911560045499841</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.898404610784504</v>
+        <v>2.844229803113459</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.135085549050133</v>
+        <v>-6.225376895168543</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4975721498145553</v>
+        <v>0.4614556113671915</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1911560045499841</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.891443998689411</v>
+        <v>2.837269191018366</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.101722342571365</v>
+        <v>-6.192013688689774</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5253797867872056</v>
+        <v>0.4892632483398422</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1911560045499841</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.905906353070554</v>
+        <v>2.851731545399509</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.993463205448843</v>
+        <v>-6.083754551567252</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5632155620954094</v>
+        <v>0.527099023648046</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1911560045499841</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.900438473529749</v>
+        <v>2.846263665858704</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.870172070631712</v>
+        <v>-5.960463416750121</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6100301100328389</v>
+        <v>0.5739135715854751</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.02242647638555523</v>
+        <v>-0.06786486973285361</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.971911248430605</v>
+        <v>2.917736440759559</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.849022871728269</v>
+        <v>-5.939314217846678</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6261907678315413</v>
+        <v>0.5900742293841774</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.04357567528899858</v>
+        <v>-0.04671567082941025</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.992301746009995</v>
+        <v>2.93812693833895</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.605257429744825</v>
+        <v>-5.695548775863234</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7194776529719697</v>
+        <v>0.6833611145246059</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.04357567528899858</v>
+        <v>-0.04671567082941025</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.988082454357046</v>
+        <v>2.933907646686001</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.50349460946753</v>
+        <v>-5.593785955585939</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7623070950029036</v>
+        <v>0.7261905565555398</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.03349660243698155</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.998138209312519</v>
+        <v>2.943963401641474</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.253644215518455</v>
+        <v>-5.343935561636864</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8549893275662357</v>
+        <v>0.8188727891188718</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.03349660243698155</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.990880284296221</v>
+        <v>2.936705476625176</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.077752123051022</v>
+        <v>-5.168043469169431</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9289452880738573</v>
+        <v>0.8928287496264939</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.03349660243698155</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.99447940781687</v>
+        <v>2.940304600145825</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.906305660028559</v>
+        <v>-4.996597006146968</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.010851379337397</v>
+        <v>0.9747348408900329</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2282412067038904</v>
+        <v>0.1379498605854816</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.110674791684902</v>
+        <v>3.056499984013857</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.832016094290219</v>
+        <v>-4.922307440408629</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.039587683249029</v>
+        <v>1.003471144801666</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3025307724422297</v>
+        <v>0.2122394263238209</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.154269008744202</v>
+        <v>3.100094201073157</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.768380352056285</v>
+        <v>-4.858671698174694</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.06973678119692</v>
+        <v>1.033620242749557</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.2758751685577554</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.197145255138881</v>
+        <v>3.142970447467835</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.656953592730365</v>
+        <v>-4.747244938848774</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.095501743711084</v>
+        <v>1.05938520526372</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.2758751685577554</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.178339513922676</v>
+        <v>3.124164706251631</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.667456215795654</v>
+        <v>-4.757747561914063</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.093043771109846</v>
+        <v>1.056927232662482</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.2653725454924665</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.17378101670838</v>
+        <v>3.119606209037335</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.595213647624459</v>
+        <v>-4.685504993742868</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.125870112213144</v>
+        <v>1.08975357376578</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.2653725454924665</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.1777103305432</v>
+        <v>3.123535522872155</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.577499960746594</v>
+        <v>-4.667791306865003</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.13363417088163</v>
+        <v>1.097517632434266</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.2685538743893833</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.18029771179869</v>
+        <v>3.126122904127645</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.468695075266867</v>
+        <v>-4.558986421385276</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.174154196293514</v>
+        <v>1.138037657846151</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.2685538743893833</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.177295783018684</v>
+        <v>3.123120975347638</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.248674277229856</v>
+        <v>-4.338965623348265</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.263741552518933</v>
+        <v>1.227625014071569</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.4097737194573636</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.263606727070086</v>
+        <v>3.209431919399041</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.115806588166579</v>
+        <v>-4.206097934284988</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.332782810946067</v>
+        <v>1.296666272498703</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.4097737194573636</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.279500909871909</v>
+        <v>3.225326102200864</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.99563350480208</v>
+        <v>-4.085924850920489</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.381997888732168</v>
+        <v>1.345881350284805</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6202381489402713</v>
+        <v>0.5299468028218626</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.352750604330911</v>
+        <v>3.298575796659865</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.860380143472103</v>
+        <v>-3.950671489590512</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.446187335825599</v>
+        <v>1.410070797378235</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7554915102702484</v>
+        <v>0.6652001641518397</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.443990723690337</v>
+        <v>3.389815916019292</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.920254970829795</v>
+        <v>-4.010546316948204</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.408274896283948</v>
+        <v>1.372158357836584</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.6053253367941476</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.394103318677147</v>
+        <v>3.339928511006102</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.800434739918958</v>
+        <v>-3.890726086037367</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.471492157882492</v>
+        <v>1.435375619435128</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.6053253367941476</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.409392487911356</v>
+        <v>3.355217680240311</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.802904446380764</v>
+        <v>-3.893195792499173</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.378148474620211</v>
+        <v>1.342031936172847</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6931469764507501</v>
+        <v>0.6028556303323414</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.315554863356714</v>
+        <v>3.261380055685668</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.871274632704774</v>
+        <v>-3.961565978823183</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.270062261575908</v>
+        <v>1.233945723128544</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6121313293685563</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.240382144263744</v>
+        <v>3.186207336592699</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.88506268555182</v>
+        <v>-3.975354031670229</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.254983749068981</v>
+        <v>1.218867210621617</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6121313293685563</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.230818852895635</v>
+        <v>3.17664404522459</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.94058276144441</v>
+        <v>-4.030874107562819</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.369806555404147</v>
+        <v>1.333690016956784</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6121313293685563</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.367849689587838</v>
+        <v>3.313674881916793</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.765108501651941</v>
+        <v>-3.85539984777035</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.444563491312923</v>
+        <v>1.408446952865559</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6121313293685563</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.372416921579625</v>
+        <v>3.31824211390858</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.876044754293189</v>
+        <v>-3.966336100411598</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.37593101901763</v>
+        <v>1.339814480570267</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6121313293685563</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.348158950340832</v>
+        <v>3.293984142669787</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.842381208820907</v>
+        <v>-3.932672554939316</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.317934750607993</v>
+        <v>1.281818212160629</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6457948748408382</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.296895391025652</v>
+        <v>3.242720583354606</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.782528589617184</v>
+        <v>-3.872819935735593</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.352048184721615</v>
+        <v>1.315931646274251</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6457948748408382</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.307067777457784</v>
+        <v>3.252892969786739</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.696285126590807</v>
+        <v>-3.786576472709216</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.381491840506026</v>
+        <v>1.345375302058662</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6457948748408382</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.302014048031644</v>
+        <v>3.247839240360599</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.741591945989787</v>
+        <v>-3.831883292108196</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.355144888190959</v>
+        <v>1.319028349743596</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.6049847118316074</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.269303725670631</v>
+        <v>3.215128917999586</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.770625050692088</v>
+        <v>-3.860916396810497</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.34408351934314</v>
+        <v>1.307966980895777</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.6049847118316074</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.269855598703733</v>
+        <v>3.215680791032688</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.677814569241229</v>
+        <v>-3.768105915359638</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.31048040381485</v>
+        <v>1.274363865367486</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7880865394008755</v>
+        <v>0.6977951932824668</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.254814579465614</v>
+        <v>3.200639771794569</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.722204038570657</v>
+        <v>-3.812495384689066</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.294598092007679</v>
+        <v>1.258481553560316</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7436970700714478</v>
+        <v>0.6534057239530391</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.230054373792558</v>
+        <v>3.175879566121513</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.838745643675999</v>
+        <v>-3.929036989794409</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.243057158477265</v>
+        <v>1.206940620029902</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.5368641188476964</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.155205119241076</v>
+        <v>3.10103031157003</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.726368642493327</v>
+        <v>-3.816659988611736</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.293499254781002</v>
+        <v>1.257382716333638</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.5368641188476964</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.160696415071743</v>
+        <v>3.106521607400698</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.75414904039468</v>
+        <v>-3.844440386513089</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.293884297388999</v>
+        <v>1.257767758941636</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.599375067064752</v>
+        <v>0.5090837209463432</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.15552537809947</v>
+        <v>3.101350570428425</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.872529713124818</v>
+        <v>-3.962821059243228</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.084887748297597</v>
+        <v>1.048771209850234</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.441865868795367</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.953550386809538</v>
+        <v>2.899375579138492</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.98114379156815</v>
+        <v>-4.071435137686558</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.16159177763947</v>
+        <v>1.125475239192107</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.441865868795367</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.073700047528743</v>
+        <v>3.019525239857698</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.945734753320007</v>
+        <v>-4.036026099438415</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.190268419041051</v>
+        <v>1.154151880593687</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.441865868795367</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.088213073631066</v>
+        <v>3.034038265960021</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.907351090761856</v>
+        <v>-3.997642436880264</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.20304132540668</v>
+        <v>1.166924786959316</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.4802495313535182</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.108662712508325</v>
+        <v>3.054487904837281</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.730234760726689</v>
+        <v>-3.820526106845098</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.270616886266048</v>
+        <v>1.234500347818685</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.4802495313535182</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.105391741353627</v>
+        <v>3.051216933682583</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.775327005560235</v>
+        <v>-3.865618351678644</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.253263380094543</v>
+        <v>1.217146841647179</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5086448343025372</v>
+        <v>0.4183534881841284</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.068937507213907</v>
+        <v>3.014762699542862</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.595951584321467</v>
+        <v>-3.686242930439876</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.318800523896464</v>
+        <v>1.282683985449101</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6654215924732558</v>
+        <v>0.5751302463548471</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.156790537422753</v>
+        <v>3.102615729751707</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.640965797842073</v>
+        <v>-3.731257143960482</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.281602293819812</v>
+        <v>1.245485755372448</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6350726971586512</v>
+        <v>0.5447813510402425</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.119388655565579</v>
+        <v>3.065213847894534</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.907970308114509</v>
+        <v>-3.998261654232918</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.180492052049783</v>
+        <v>1.14437551360242</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4407096591157026</v>
+        <v>0.3504183129972939</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.008462395078756</v>
+        <v>2.954287587407711</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.009168089551681</v>
+        <v>-4.099459435670091</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.139216861371416</v>
+        <v>1.103100322924052</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.2820094994519747</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.966621028848066</v>
+        <v>2.912446221177021</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.002657122937369</v>
+        <v>-4.092948469055778</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.139421209571458</v>
+        <v>1.103304671124094</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.2820094994519747</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.964220990402382</v>
+        <v>2.910046182731338</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.983618995230072</v>
+        <v>-4.073910341348481</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.143561179862621</v>
+        <v>1.107444641415258</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.2238258881207802</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.925835542811911</v>
+        <v>2.871660735140865</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.01474562638069</v>
+        <v>-4.105036972499099</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.250404929036564</v>
+        <v>1.214288390589201</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.2238258881207802</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.045129944446101</v>
+        <v>2.990955136775056</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.028612387714608</v>
+        <v>-4.118903733833017</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.245691553489131</v>
+        <v>1.209575015041767</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.276259317505366</v>
+        <v>0.1859679713869573</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.023248523391941</v>
+        <v>2.969073715720896</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.983808216174678</v>
+        <v>-4.074099562293087</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.269621752502029</v>
+        <v>1.233505214054665</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.276259317505366</v>
+        <v>0.1859679713869573</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.029257053788867</v>
+        <v>2.975082246117822</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.836065245939676</v>
+        <v>-3.926356592058085</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.226669161873229</v>
+        <v>1.190552623425865</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.3537753286218404</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.027891689406996</v>
+        <v>2.973716881735951</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.919886467214374</v>
+        <v>-4.010177813332783</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.195934294894831</v>
+        <v>1.159817756447467</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.3537753286218404</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.030685310938477</v>
+        <v>2.976510503267432</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.913733761161589</v>
+        <v>-4.004025107279999</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.199057725707603</v>
+        <v>1.162941187260239</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4502193807930334</v>
+        <v>0.3599280346746247</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.035039282961806</v>
+        <v>2.980864475290761</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.930543059312091</v>
+        <v>-4.020834405430501</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.191414483187512</v>
+        <v>1.155297944740149</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.3431187365241231</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.024034180811615</v>
+        <v>2.96985937314057</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.868245060535969</v>
+        <v>-3.958536406654379</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.282669236494782</v>
+        <v>1.246552698047418</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.3431187365241231</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.090369734608436</v>
+        <v>3.036194926937391</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.666454862870811</v>
+        <v>-3.756746208989221</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.165677317274972</v>
+        <v>1.129560778827609</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6314282748116862</v>
+        <v>0.5411369286932775</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.011472651624056</v>
+        <v>2.957297843953011</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.717341575557006</v>
+        <v>-3.807632921675415</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.21561286452267</v>
+        <v>1.179496326075306</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5805415621254917</v>
+        <v>0.490250216007083</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.051230856334515</v>
+        <v>2.997056048663469</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.630730832907199</v>
+        <v>-3.721022179025608</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.264884897698636</v>
+        <v>1.228768359251272</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6591672933306499</v>
+        <v>0.5688759472122412</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.113034031173653</v>
+        <v>3.058859223502608</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.690940130912483</v>
+        <v>-3.781231477030893</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.239337159321194</v>
+        <v>1.20322062087383</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.5086666492069567</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.075444433195154</v>
+        <v>3.021269625524109</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.614518084480556</v>
+        <v>-3.704809430598966</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.268397595933893</v>
+        <v>1.232281057486529</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.5086666492069567</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.073936051235083</v>
+        <v>3.019761243564037</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.570144952841988</v>
+        <v>-3.660436298960397</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.286009716024757</v>
+        <v>1.249893177577393</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.643331126963934</v>
+        <v>0.5530397808455253</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.10042279765366</v>
+        <v>3.046247989982615</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.592625303700872</v>
+        <v>-3.682916649819282</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.271411369819794</v>
+        <v>1.23529483137243</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.643331126963934</v>
+        <v>0.5530397808455253</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.094816591792251</v>
+        <v>3.040641784121205</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.544969573139817</v>
+        <v>-3.635260919258227</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.296855419072021</v>
+        <v>1.260738880624657</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6909868575249897</v>
+        <v>0.600695511406581</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.129791787156689</v>
+        <v>3.075616979485643</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.444451414641062</v>
+        <v>-3.534742760759472</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.341955055846247</v>
+        <v>1.305838517398883</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7915050160237442</v>
+        <v>0.7012136699053355</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.194995055630666</v>
+        <v>3.140820247959621</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.428546085208709</v>
+        <v>-3.518837431327119</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.335071860095061</v>
+        <v>1.298955321647697</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7123923553145053</v>
+        <v>0.6221010091960966</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.134282131680995</v>
+        <v>3.08010732400995</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81683703393277</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.383707683600311</v>
+        <v>-3.473999029718721</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.357104923349048</v>
+        <v>1.320988384901684</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7169357882593748</v>
+        <v>0.626644442140966</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.141105894058545</v>
+        <v>3.0869310863875</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.403206139842319</v>
+        <v>-3.49349748596073</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.353466480483323</v>
+        <v>1.317349942035959</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6688511469794705</v>
+        <v>0.5785598008610617</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.116416048921681</v>
+        <v>3.062241241250635</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.359003302756419</v>
+        <v>-3.449294648874829</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.37702721784552</v>
+        <v>1.340910679398156</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7130539840653709</v>
+        <v>0.6227626379469622</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.148817353701058</v>
+        <v>3.094642546030013</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.395982330419862</v>
+        <v>-3.486273676538272</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.360645607249391</v>
+        <v>1.324529068802027</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7500278858567014</v>
+        <v>0.6597365397382927</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.169411695245104</v>
+        <v>3.115236887574059</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.23769091288059</v>
+        <v>-3.327982258999</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.475209939448139</v>
+        <v>1.439093401000775</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7500278858567014</v>
+        <v>0.6597365397382927</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.220659460428144</v>
+        <v>3.166484652757098</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.030048909246114</v>
+        <v>-3.120340255364524</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.556707445496183</v>
+        <v>1.520590907048819</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9576698894911776</v>
+        <v>0.8673785433727689</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.343685367203082</v>
+        <v>3.289510559532037</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.979016816523586</v>
+        <v>-3.069308162641996</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.572068510823464</v>
+        <v>1.5359519723761</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.008701982213706</v>
+        <v>0.9184106360952968</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.369252851074869</v>
+        <v>3.315078043403824</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.91379263539638</v>
+        <v>-3.00408398151479</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.615345587367051</v>
+        <v>1.579229048919687</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.073926163340911</v>
+        <v>0.9836348172225025</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.425574763843898</v>
+        <v>3.371399956172852</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.876365615325246</v>
+        <v>-2.966656961443656</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.626277367694785</v>
+        <v>1.590160829247421</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.079177701370093</v>
+        <v>0.988886355251684</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.424686658960687</v>
+        <v>3.370511851289641</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.896477271359954</v>
+        <v>-2.986768617478365</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.619489497612142</v>
+        <v>1.583372959164778</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.090205046367512</v>
+        <v>0.9999137002491032</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.432559858290379</v>
+        <v>3.378385050619333</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.84273245693275</v>
+        <v>-2.93302380305116</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.801545194404235</v>
+        <v>1.765428655956871</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.100268355807974</v>
+        <v>1.009977009689565</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.599155614975866</v>
+        <v>3.544980807304821</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.767950195907737</v>
+        <v>-2.858241542026147</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.951571008032057</v>
+        <v>1.915454469584693</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.175050616832987</v>
+        <v>1.084759270714578</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.764137880808692</v>
+        <v>3.709963073137646</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.741866111643929</v>
+        <v>-2.832157457762339</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.953712617751439</v>
+        <v>1.917596079304075</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.175050616832987</v>
+        <v>1.084759270714578</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.755845856822551</v>
+        <v>3.701671049151505</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.653988198534809</v>
+        <v>-2.744279544653219</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.987056978578867</v>
+        <v>1.950940440131503</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.290976259256338</v>
+        <v>1.200684913137929</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.823594437860341</v>
+        <v>3.769419630189295</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.645095737141525</v>
+        <v>-2.735387083259935</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.008168368862972</v>
+        <v>1.972051830415608</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.290976259256338</v>
+        <v>1.200684913137929</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.841148843587132</v>
+        <v>3.786974035916087</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.813571854111403</v>
+        <v>-2.903863200229813</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.932632969479605</v>
+        <v>1.89651643103224</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.263028423539757</v>
+        <v>1.172737077421348</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.816235189561767</v>
+        <v>3.762060381890722</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.11577232524982</v>
+        <v>-2.20606367136823</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.1930224782121</v>
+        <v>2.156905939764735</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.192680364169346</v>
+        <v>1.102389018050938</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.755296051127383</v>
+        <v>3.701121243456337</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.093051221566667</v>
+        <v>-2.183342567685077</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.192774942182265</v>
+        <v>2.156658403734901</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.192680364169346</v>
+        <v>1.102389018050938</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.745960073624287</v>
+        <v>3.691785265953242</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.22225303486071</v>
+        <v>-2.31254438097912</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.300000342715817</v>
+        <v>2.263883804268453</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.063478550875304</v>
+        <v>0.9731872047568955</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.827345111499031</v>
+        <v>3.773170303827986</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.377034041638965</v>
+        <v>-2.467325387757375</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.275165762498162</v>
+        <v>2.239049224050798</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.030110876820828</v>
+        <v>0.9398195307024193</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.844402329559992</v>
+        <v>3.790227521888947</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.369979351423792</v>
+        <v>-2.460270697542202</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.274662994573776</v>
+        <v>2.238546456126412</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.037165567036002</v>
+        <v>0.9468742209175931</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.845310499678642</v>
+        <v>3.791135692007596</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.343028127097304</v>
+        <v>-2.433319473215714</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.295449637949113</v>
+        <v>2.259333099501749</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.052045913063721</v>
+        <v>0.9617545669453123</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.864244860940015</v>
+        <v>3.810070053268969</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.47898113515362</v>
+        <v>-2.56927248127203</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.425171566871546</v>
+        <v>2.389055028424182</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.052045913063721</v>
+        <v>0.9617545669453123</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.048347993084974</v>
+        <v>3.994173185413929</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.501389252958492</v>
+        <v>-2.591680599076902</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.408325014652591</v>
+        <v>2.372208476205226</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.052045913063721</v>
+        <v>0.9617545669453123</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.040464687987967</v>
+        <v>3.986289880316922</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.529613488536092</v>
+        <v>-2.619904834654502</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.399089319971188</v>
+        <v>2.362972781523824</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.07002266551503</v>
+        <v>0.9797313193966208</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.05330473900839</v>
+        <v>3.999129931337345</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.539054414424622</v>
+        <v>-2.629345760543032</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.451566667337623</v>
+        <v>2.415450128890259</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.192449783058421</v>
+        <v>1.102158436940012</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.183014727256272</v>
+        <v>4.128839919585227</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.591328021760264</v>
+        <v>-2.681619367878674</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.433548318948668</v>
+        <v>2.397431780501303</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.14017617572278</v>
+        <v>1.049884829604371</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.154541657400188</v>
+        <v>4.100366849729143</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.66765799936117</v>
+        <v>-2.75794934547958</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.40112814080208</v>
+        <v>2.365011602354716</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.14017617572278</v>
+        <v>1.049884829604371</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.152653470293963</v>
+        <v>4.098478662622918</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.869911719685523</v>
+        <v>-2.960203065803933</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.315046882275201</v>
+        <v>2.278930343827837</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9379224553984262</v>
+        <v>0.8476311092800175</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.026121467702214</v>
+        <v>3.971946660031168</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.031480145212778</v>
+        <v>-3.121771491331188</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.248853522274451</v>
+        <v>2.212736983827087</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8111395316005469</v>
+        <v>0.7208481854821381</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.948485723633638</v>
+        <v>3.894310915962593</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.163781437310331</v>
+        <v>-3.254072783428741</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.209006412301349</v>
+        <v>2.172889873853984</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8111395316005469</v>
+        <v>0.7208481854821381</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.961559130499557</v>
+        <v>3.907384322828511</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.349649748149561</v>
+        <v>-3.439941094267971</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.126664284748597</v>
+        <v>2.090547746301232</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6525739382805992</v>
+        <v>0.5622825921621905</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.858424971290528</v>
+        <v>3.804250163619483</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.377550535259034</v>
+        <v>-3.467841881377444</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.114028011031809</v>
+        <v>2.077911472584446</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6179770141376644</v>
+        <v>0.5276856680192556</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.836190857931769</v>
+        <v>3.782016050260724</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.500076637961928</v>
+        <v>-3.590367984080338</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.061782013927851</v>
+        <v>2.025665475480487</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4954509114347705</v>
+        <v>0.4051595653163618</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.759439640287232</v>
+        <v>3.705264832616186</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.730591134147517</v>
+        <v>-3.820882480265927</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.036282175044119</v>
+        <v>2.000165636596755</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2649364152491818</v>
+        <v>0.174645069130773</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.687836902166382</v>
+        <v>3.633662094495337</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.987311952142341</v>
+        <v>-4.077603298260751</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.073905566848036</v>
+        <v>2.037789028400672</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1565218411053669</v>
+        <v>0.06623049498695821</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.76309987668194</v>
+        <v>3.708925069010895</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.141298369918481</v>
+        <v>-4.231589716036892</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.08129126888322</v>
+        <v>2.045174730435856</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1565218411053669</v>
+        <v>0.06623049498695821</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.83208014582758</v>
+        <v>3.777905338156535</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.090776466090815</v>
+        <v>-4.181067812209226</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.087551232534407</v>
+        <v>2.051434694087043</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1565218411053669</v>
+        <v>0.06623049498695821</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.818131347947701</v>
+        <v>3.763956540276656</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.343251620098539</v>
+        <v>-4.43354296621695</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.998431659986732</v>
+        <v>1.962315121539367</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1565218411053669</v>
+        <v>0.06623049498695821</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.830001837003115</v>
+        <v>3.77582702933207</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.636147376577951</v>
+        <v>-4.726438722696362</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.88248389191391</v>
+        <v>1.846367353466546</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1565218411053669</v>
+        <v>0.06623049498695821</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.831212371522059</v>
+        <v>3.777037563851013</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.793691448307393</v>
+        <v>-4.883982794425804</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.823588005449455</v>
+        <v>1.787471467002091</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.08962003596509244</v>
+        <v>-0.0006713101533162846</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.795193030665216</v>
+        <v>3.74101822299417</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.071655843890666</v>
+        <v>-5.161947190009077</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.707480099952335</v>
+        <v>1.671363561504971</v>
       </c>
       <c r="F2022" t="n">
-        <v>3.016796081833917e-07</v>
+        <v>-0.09029104443880054</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.736499042830114</v>
+        <v>3.682324235159069</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.188623536529557</v>
+        <v>-5.278914882647968</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.822897079595823</v>
+        <v>1.786780541148459</v>
       </c>
       <c r="F2023" t="n">
-        <v>3.016796081833917e-07</v>
+        <v>-0.09029104443880054</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.898703099529159</v>
+        <v>3.844528291858113</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.273341478750511</v>
+        <v>-5.363632824868922</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.783856540671256</v>
+        <v>1.747740002223892</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.08511572724843819</v>
+        <v>-0.1754070733668469</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.842480120136145</v>
+        <v>3.788305312465099</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.355276297019394</v>
+        <v>-5.445567643137805</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.761312030932194</v>
+        <v>1.725195492484829</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.09505047283551837</v>
+        <v>-0.1853418189539271</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.846748690352388</v>
+        <v>3.792573882681343</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.457252419267801</v>
+        <v>-5.547543765386212</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.729447220488733</v>
+        <v>1.693330682041369</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1970265950839259</v>
+        <v>-0.2873179412023347</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.794488655459246</v>
+        <v>3.740313847788201</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.34724613579058</v>
+        <v>-5.437537481908991</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.765602621123797</v>
+        <v>1.729486082676433</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1738220231666507</v>
+        <v>-0.2641133692850595</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.800564285853786</v>
+        <v>3.746389478182741</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.204186560049655</v>
+        <v>-5.294477906168066</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.827076462142141</v>
+        <v>1.790959923694777</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1658085965766715</v>
+        <v>-0.2560999426950802</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.809622352529748</v>
+        <v>3.755447544858703</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.902739834577817</v>
+        <v>-4.993031180696228</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.954916035213413</v>
+        <v>1.918799496766048</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1356381288951658</v>
+        <v>0.04534678277675708</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.997751270695386</v>
+        <v>3.943576463024341</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.927330078813001</v>
+        <v>-5.017621424931412</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.946051115272049</v>
+        <v>1.909934576824685</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1356381288951658</v>
+        <v>0.04534678277675708</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.998722448448097</v>
+        <v>3.944547640777052</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.876291702806481</v>
+        <v>-4.966583048924892</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.967309370054413</v>
+        <v>1.931192831607048</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1356381288951658</v>
+        <v>0.04534678277675708</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.999565352827852</v>
+        <v>3.945390545156807</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.83515240793985</v>
+        <v>-4.925443754058261</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.002803186875211</v>
+        <v>1.966686648427846</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1767774237617966</v>
+        <v>0.08648607764338789</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.043287028621976</v>
+        <v>3.989112220950931</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.724546267860248</v>
+        <v>-4.814837613978659</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.863229639030986</v>
+        <v>1.827113100583622</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2873835638413986</v>
+        <v>0.1970922177229899</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.925834708793672</v>
+        <v>3.871659901122626</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.85512700239109</v>
+        <v>-4.945418348509501</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.814499389292613</v>
+        <v>1.778382850845248</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1568028293105561</v>
+        <v>0.06651148319214739</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.85098831214913</v>
+        <v>3.796813504478085</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.690630668200129</v>
+        <v>-4.78092201431854</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.86472474204508</v>
+        <v>1.828608203597716</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.1568028293105561</v>
+        <v>0.06651148319214739</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.835415131225213</v>
+        <v>3.781240323554167</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.718000600884561</v>
+        <v>-4.808291947002972</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.852964479407737</v>
+        <v>1.816847940960372</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.1568028293105561</v>
+        <v>0.06651148319214739</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.834602841661642</v>
+        <v>3.780428033990597</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.72838579577445</v>
+        <v>-4.818677141892861</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.858679180576853</v>
+        <v>1.822562642129489</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1464176344206668</v>
+        <v>0.05612628830225808</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.838240503852781</v>
+        <v>3.784065696181736</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735281</v>
+        <v>3.834415493735279</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.746973954496675</v>
+        <v>-4.837265300615086</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.922080922864389</v>
+        <v>1.885964384417024</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1278294756984414</v>
+        <v>0.03753812958003272</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.897924614395871</v>
+        <v>3.843749806724826</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.747272501192711</v>
+        <v>-4.837563847311122</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.918830515004273</v>
+        <v>1.882713976556908</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1278294756984414</v>
+        <v>0.03753812958003272</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.89479362521417</v>
+        <v>3.840618817543124</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.646449367502283</v>
+        <v>-4.736740713620694</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.963690663419835</v>
+        <v>1.927574124972471</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.1402936911827953</v>
+        <v>0.05000234506438656</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.906803049444173</v>
+        <v>3.852628241773128</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.455668006749876</v>
+        <v>-4.545959352868287</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.040132461199341</v>
+        <v>2.004015922751977</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3310750519352026</v>
+        <v>0.2407837058167939</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.021401119374161</v>
+        <v>3.967226311703116</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.437151152708056</v>
+        <v>-4.527442498826467</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.027376048553666</v>
+        <v>1.991259510106302</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.3440051813604109</v>
+        <v>0.2537138352420021</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.008996042766882</v>
+        <v>3.954821235095837</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.411957968206738</v>
+        <v>-4.502249314325149</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.072420258966252</v>
+        <v>2.036303720518887</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.3691983658617292</v>
+        <v>0.2789070197433205</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.059078890079732</v>
+        <v>4.004904082408687</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.399903841293775</v>
+        <v>-4.490195187412186</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.070928477632874</v>
+        <v>2.03481193918551</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.381252492774692</v>
+        <v>0.2909611466562833</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.059997934128948</v>
+        <v>4.005823126457902</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.406527087984133</v>
+        <v>-4.496818434102544</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.070159809140867</v>
+        <v>2.034043270693503</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.3746292460843337</v>
+        <v>0.284337899965925</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.057904616298869</v>
+        <v>4.003729808627823</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.30364649845554</v>
+        <v>-4.393937844573951</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.124163070830186</v>
+        <v>2.088046532382823</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.4775098356129266</v>
+        <v>0.3872184894945179</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.132483995893907</v>
+        <v>4.078309188222861</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.327088537635627</v>
+        <v>-4.417379883754038</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.134988925331746</v>
+        <v>2.098872386884381</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.4775098356129266</v>
+        <v>0.3872184894945179</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.152686666067501</v>
+        <v>4.098511858396455</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781701</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.345161045927239</v>
+        <v>-4.43545239204565</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.127759922015102</v>
+        <v>2.091643383567737</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.4775098356129266</v>
+        <v>0.3872184894945179</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.152686666067501</v>
+        <v>4.098511858396455</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.67006888808283</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.576334839803871</v>
+        <v>-4.666626185922282</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.995542318057915</v>
+        <v>1.959425779610551</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.4775098356129266</v>
+        <v>0.3872184894945179</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.112938579660967</v>
+        <v>4.058763771989922</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.861406657545059</v>
+        <v>3.790525528200734</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.641297152843944</v>
+        <v>-4.732847467393282</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.976580011838826</v>
+        <v>1.939959886019091</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.4125475225728545</v>
+        <v>0.3209972080235182</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.080983810833864</v>
+        <v>4.026053622104262</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240809.xlsx
+++ b/tame_output/ON/bt/strategyON_20240809.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>20.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.2%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.1%</t>
+          <t>419.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-634.9%</t>
+          <t>-639.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-182.2%</t>
+          <t>-184.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>-637.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.0%</t>
+          <t>-191.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-191.9%</t>
+          <t>-195.1%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>-45.3%</t>
         </is>
       </c>
     </row>
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.716749561582301</v>
+        <v>-6.626458215463892</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4669853123369005</v>
+        <v>0.5031018507842644</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4022602419628756</v>
+        <v>-0.3119688958444667</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.912685416105843</v>
+        <v>2.966860223776889</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.46774976289872</v>
+        <v>-6.377458416780311</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5794915730339918</v>
+        <v>0.6156081114813556</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1532604432792949</v>
+        <v>-0.06296909716088606</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.074991636539651</v>
+        <v>3.129166444210696</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.573339752671824</v>
+        <v>-6.483048406553415</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4092796475255316</v>
+        <v>0.445396185972895</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2588504330523992</v>
+        <v>-0.1685590869339904</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.883661713076569</v>
+        <v>2.937836520747615</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.592074654790421</v>
+        <v>-6.501783308672012</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4503300285551788</v>
+        <v>0.4864465670025426</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2644464427125305</v>
+        <v>-0.1741550965941217</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.928848449157577</v>
+        <v>2.983023256828622</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.444134613382822</v>
+        <v>-6.353843267264413</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3896271224300509</v>
+        <v>0.4257436608774148</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.244125526803973</v>
+        <v>-0.1538341806855641</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.821162076014544</v>
+        <v>2.875336883685589</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.391165091128833</v>
+        <v>-6.300873745010424</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4021009450781685</v>
+        <v>0.4382174835255319</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1911560045499841</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.844229803113459</v>
+        <v>2.898404610784504</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.225376895168543</v>
+        <v>-6.135085549050133</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4614556113671915</v>
+        <v>0.4975721498145553</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1911560045499841</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.837269191018366</v>
+        <v>2.891443998689411</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.192013688689774</v>
+        <v>-6.101722342571365</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4892632483398422</v>
+        <v>0.5253797867872056</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1911560045499841</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.851731545399509</v>
+        <v>2.905906353070554</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.083754551567252</v>
+        <v>-5.993463205448843</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.527099023648046</v>
+        <v>0.5632155620954094</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1911560045499841</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.846263665858704</v>
+        <v>2.900438473529749</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.960463416750121</v>
+        <v>-5.870172070631712</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5739135715854751</v>
+        <v>0.6100301100328389</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.06786486973285361</v>
+        <v>0.02242647638555523</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.917736440759559</v>
+        <v>2.971911248430605</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.939314217846678</v>
+        <v>-5.849022871728269</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5900742293841774</v>
+        <v>0.6261907678315413</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.04671567082941025</v>
+        <v>0.04357567528899858</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.93812693833895</v>
+        <v>2.992301746009995</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.695548775863234</v>
+        <v>-5.605257429744825</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6833611145246059</v>
+        <v>0.7194776529719697</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.04671567082941025</v>
+        <v>0.04357567528899858</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.933907646686001</v>
+        <v>2.988082454357046</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.593785955585939</v>
+        <v>-5.50349460946753</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7261905565555398</v>
+        <v>0.7623070950029036</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.03349660243698155</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.943963401641474</v>
+        <v>2.998138209312519</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.343935561636864</v>
+        <v>-5.253644215518455</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8188727891188718</v>
+        <v>0.8549893275662357</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.03349660243698155</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.936705476625176</v>
+        <v>2.990880284296221</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.168043469169431</v>
+        <v>-5.077752123051022</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8928287496264939</v>
+        <v>0.9289452880738573</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.03349660243698155</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.940304600145825</v>
+        <v>2.99447940781687</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.996597006146968</v>
+        <v>-4.906305660028559</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9747348408900329</v>
+        <v>1.010851379337397</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1379498605854816</v>
+        <v>0.2282412067038904</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.056499984013857</v>
+        <v>3.110674791684902</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.922307440408629</v>
+        <v>-4.832016094290219</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.003471144801666</v>
+        <v>1.039587683249029</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2122394263238209</v>
+        <v>0.3025307724422297</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.100094201073157</v>
+        <v>3.154269008744202</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.858671698174694</v>
+        <v>-4.768380352056285</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.033620242749557</v>
+        <v>1.06973678119692</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2758751685577554</v>
+        <v>0.3661665146761642</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.142970447467835</v>
+        <v>3.197145255138881</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.747244938848774</v>
+        <v>-4.656953592730365</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.05938520526372</v>
+        <v>1.095501743711084</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2758751685577554</v>
+        <v>0.3661665146761642</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.124164706251631</v>
+        <v>3.178339513922676</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.757747561914063</v>
+        <v>-4.667456215795654</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.056927232662482</v>
+        <v>1.093043771109846</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2653725454924665</v>
+        <v>0.3556638916108754</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.119606209037335</v>
+        <v>3.17378101670838</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.685504993742868</v>
+        <v>-4.595213647624459</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.08975357376578</v>
+        <v>1.125870112213144</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2653725454924665</v>
+        <v>0.3556638916108754</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.123535522872155</v>
+        <v>3.1777103305432</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.667791306865003</v>
+        <v>-4.577499960746594</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.097517632434266</v>
+        <v>1.13363417088163</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2685538743893833</v>
+        <v>0.3588452205077922</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.126122904127645</v>
+        <v>3.18029771179869</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.558986421385276</v>
+        <v>-4.468695075266867</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.138037657846151</v>
+        <v>1.174154196293514</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2685538743893833</v>
+        <v>0.3588452205077922</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.123120975347638</v>
+        <v>3.177295783018684</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.338965623348265</v>
+        <v>-4.248674277229856</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.227625014071569</v>
+        <v>1.263741552518933</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4097737194573636</v>
+        <v>0.5000650655757723</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.209431919399041</v>
+        <v>3.263606727070086</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.206097934284988</v>
+        <v>-4.115806588166579</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.296666272498703</v>
+        <v>1.332782810946067</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4097737194573636</v>
+        <v>0.5000650655757723</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.225326102200864</v>
+        <v>3.279500909871909</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.085924850920489</v>
+        <v>-3.99563350480208</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.345881350284805</v>
+        <v>1.381997888732168</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5299468028218626</v>
+        <v>0.6202381489402713</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.298575796659865</v>
+        <v>3.352750604330911</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.950671489590512</v>
+        <v>-3.860380143472103</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.410070797378235</v>
+        <v>1.446187335825599</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6652001641518397</v>
+        <v>0.7554915102702484</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.389815916019292</v>
+        <v>3.443990723690337</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.010546316948204</v>
+        <v>-3.920254970829795</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.372158357836584</v>
+        <v>1.408274896283948</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6053253367941476</v>
+        <v>0.6956166829125563</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.339928511006102</v>
+        <v>3.394103318677147</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.890726086037367</v>
+        <v>-3.800434739918958</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.435375619435128</v>
+        <v>1.471492157882492</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6053253367941476</v>
+        <v>0.6956166829125563</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.355217680240311</v>
+        <v>3.409392487911356</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.893195792499173</v>
+        <v>-3.802904446380764</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.342031936172847</v>
+        <v>1.378148474620211</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6028556303323414</v>
+        <v>0.6931469764507501</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.261380055685668</v>
+        <v>3.315554863356714</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.961565978823183</v>
+        <v>-3.871274632704774</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.233945723128544</v>
+        <v>1.270062261575908</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6121313293685563</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.186207336592699</v>
+        <v>3.240382144263744</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.975354031670229</v>
+        <v>-3.88506268555182</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.218867210621617</v>
+        <v>1.254983749068981</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6121313293685563</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.17664404522459</v>
+        <v>3.230818852895635</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.030874107562819</v>
+        <v>-3.94058276144441</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.333690016956784</v>
+        <v>1.369806555404147</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6121313293685563</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.313674881916793</v>
+        <v>3.367849689587838</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.85539984777035</v>
+        <v>-3.765108501651941</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.408446952865559</v>
+        <v>1.444563491312923</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6121313293685563</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.31824211390858</v>
+        <v>3.372416921579625</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.966336100411598</v>
+        <v>-3.876044754293189</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.339814480570267</v>
+        <v>1.37593101901763</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6121313293685563</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.293984142669787</v>
+        <v>3.348158950340832</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.932672554939316</v>
+        <v>-3.842381208820907</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.281818212160629</v>
+        <v>1.317934750607993</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6457948748408382</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.242720583354606</v>
+        <v>3.296895391025652</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.872819935735593</v>
+        <v>-3.782528589617184</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.315931646274251</v>
+        <v>1.352048184721615</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6457948748408382</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.252892969786739</v>
+        <v>3.307067777457784</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.786576472709216</v>
+        <v>-3.696285126590807</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.345375302058662</v>
+        <v>1.381491840506026</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6457948748408382</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.247839240360599</v>
+        <v>3.302014048031644</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.831883292108196</v>
+        <v>-3.741591945989787</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.319028349743596</v>
+        <v>1.355144888190959</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6049847118316074</v>
+        <v>0.6952760579500161</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.215128917999586</v>
+        <v>3.269303725670631</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.860916396810497</v>
+        <v>-3.770625050692088</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.307966980895777</v>
+        <v>1.34408351934314</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6049847118316074</v>
+        <v>0.6952760579500161</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.215680791032688</v>
+        <v>3.269855598703733</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.768105915359638</v>
+        <v>-3.677814569241229</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.274363865367486</v>
+        <v>1.31048040381485</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6977951932824668</v>
+        <v>0.7880865394008755</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.200639771794569</v>
+        <v>3.254814579465614</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.812495384689066</v>
+        <v>-3.722204038570657</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.258481553560316</v>
+        <v>1.294598092007679</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6534057239530391</v>
+        <v>0.7436970700714478</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.175879566121513</v>
+        <v>3.230054373792558</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.929036989794409</v>
+        <v>-3.838745643675999</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.206940620029902</v>
+        <v>1.243057158477265</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5368641188476964</v>
+        <v>0.6271554649661051</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.10103031157003</v>
+        <v>3.155205119241076</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.816659988611736</v>
+        <v>-3.726368642493327</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.257382716333638</v>
+        <v>1.293499254781002</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5368641188476964</v>
+        <v>0.6271554649661051</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.106521607400698</v>
+        <v>3.160696415071743</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.844440386513089</v>
+        <v>-3.75414904039468</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.257767758941636</v>
+        <v>1.293884297388999</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5090837209463432</v>
+        <v>0.599375067064752</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.101350570428425</v>
+        <v>3.15552537809947</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.962821059243228</v>
+        <v>-3.872529713124818</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.048771209850234</v>
+        <v>1.084887748297597</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.441865868795367</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.899375579138492</v>
+        <v>2.953550386809538</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.071435137686558</v>
+        <v>-3.98114379156815</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.125475239192107</v>
+        <v>1.16159177763947</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.441865868795367</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.019525239857698</v>
+        <v>3.073700047528743</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.036026099438415</v>
+        <v>-3.945734753320007</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.154151880593687</v>
+        <v>1.190268419041051</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.441865868795367</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.034038265960021</v>
+        <v>3.088213073631066</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.997642436880264</v>
+        <v>-3.907351090761856</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.166924786959316</v>
+        <v>1.20304132540668</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4802495313535182</v>
+        <v>0.5705408774719269</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.054487904837281</v>
+        <v>3.108662712508325</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.820526106845098</v>
+        <v>-3.730234760726689</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.234500347818685</v>
+        <v>1.270616886266048</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4802495313535182</v>
+        <v>0.5705408774719269</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.051216933682583</v>
+        <v>3.105391741353627</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.865618351678644</v>
+        <v>-3.775327005560235</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.217146841647179</v>
+        <v>1.253263380094543</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4183534881841284</v>
+        <v>0.5086448343025372</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.014762699542862</v>
+        <v>3.068937507213907</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.686242930439876</v>
+        <v>-3.595951584321467</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.282683985449101</v>
+        <v>1.318800523896464</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5751302463548471</v>
+        <v>0.6654215924732558</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.102615729751707</v>
+        <v>3.156790537422753</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.731257143960482</v>
+        <v>-3.640965797842073</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.245485755372448</v>
+        <v>1.281602293819812</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5447813510402425</v>
+        <v>0.6350726971586512</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.065213847894534</v>
+        <v>3.119388655565579</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.998261654232918</v>
+        <v>-3.907970308114509</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.14437551360242</v>
+        <v>1.180492052049783</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3504183129972939</v>
+        <v>0.4407096591157026</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.954287587407711</v>
+        <v>3.008462395078756</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.099459435670091</v>
+        <v>-4.009168089551681</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.103100322924052</v>
+        <v>1.139216861371416</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2820094994519747</v>
+        <v>0.3723008455703835</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.912446221177021</v>
+        <v>2.966621028848066</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.092948469055778</v>
+        <v>-4.002657122937369</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.103304671124094</v>
+        <v>1.139421209571458</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2820094994519747</v>
+        <v>0.3723008455703835</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.910046182731338</v>
+        <v>2.964220990402382</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.073910341348481</v>
+        <v>-3.983618995230072</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.107444641415258</v>
+        <v>1.143561179862621</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2238258881207802</v>
+        <v>0.3141172342391889</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.871660735140865</v>
+        <v>2.925835542811911</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.105036972499099</v>
+        <v>-4.01474562638069</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.214288390589201</v>
+        <v>1.250404929036564</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2238258881207802</v>
+        <v>0.3141172342391889</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.990955136775056</v>
+        <v>3.045129944446101</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.118903733833017</v>
+        <v>-4.028612387714608</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.209575015041767</v>
+        <v>1.245691553489131</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1859679713869573</v>
+        <v>0.276259317505366</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.969073715720896</v>
+        <v>3.023248523391941</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.074099562293087</v>
+        <v>-3.983808216174678</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.233505214054665</v>
+        <v>1.269621752502029</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1859679713869573</v>
+        <v>0.276259317505366</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.975082246117822</v>
+        <v>3.029257053788867</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.926356592058085</v>
+        <v>-3.836065245939676</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.190552623425865</v>
+        <v>1.226669161873229</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3537753286218404</v>
+        <v>0.4440666747402491</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.973716881735951</v>
+        <v>3.027891689406996</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.010177813332783</v>
+        <v>-3.919886467214374</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.159817756447467</v>
+        <v>1.195934294894831</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3537753286218404</v>
+        <v>0.4440666747402491</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.976510503267432</v>
+        <v>3.030685310938477</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.004025107279999</v>
+        <v>-3.913733761161589</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.162941187260239</v>
+        <v>1.199057725707603</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3599280346746247</v>
+        <v>0.4502193807930334</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.980864475290761</v>
+        <v>3.035039282961806</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.020834405430501</v>
+        <v>-3.930543059312091</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.155297944740149</v>
+        <v>1.191414483187512</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3431187365241231</v>
+        <v>0.4334100826425318</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.96985937314057</v>
+        <v>3.024034180811615</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.958536406654379</v>
+        <v>-3.868245060535969</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.246552698047418</v>
+        <v>1.282669236494782</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3431187365241231</v>
+        <v>0.4334100826425318</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.036194926937391</v>
+        <v>3.090369734608436</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.756746208989221</v>
+        <v>-3.666454862870811</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.129560778827609</v>
+        <v>1.165677317274972</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5411369286932775</v>
+        <v>0.6314282748116862</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.957297843953011</v>
+        <v>3.011472651624056</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.807632921675415</v>
+        <v>-3.717341575557006</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.179496326075306</v>
+        <v>1.21561286452267</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.490250216007083</v>
+        <v>0.5805415621254917</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.997056048663469</v>
+        <v>3.051230856334515</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.721022179025608</v>
+        <v>-3.630730832907199</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.228768359251272</v>
+        <v>1.264884897698636</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5688759472122412</v>
+        <v>0.6591672933306499</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.058859223502608</v>
+        <v>3.113034031173653</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.781231477030893</v>
+        <v>-3.690940130912483</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.20322062087383</v>
+        <v>1.239337159321194</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5086666492069567</v>
+        <v>0.5989579953253654</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.021269625524109</v>
+        <v>3.075444433195154</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.704809430598966</v>
+        <v>-3.614518084480556</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.232281057486529</v>
+        <v>1.268397595933893</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5086666492069567</v>
+        <v>0.5989579953253654</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.019761243564037</v>
+        <v>3.073936051235083</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.660436298960397</v>
+        <v>-3.570144952841988</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.249893177577393</v>
+        <v>1.286009716024757</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5530397808455253</v>
+        <v>0.643331126963934</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.046247989982615</v>
+        <v>3.10042279765366</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.682916649819282</v>
+        <v>-3.592625303700872</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.23529483137243</v>
+        <v>1.271411369819794</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5530397808455253</v>
+        <v>0.643331126963934</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.040641784121205</v>
+        <v>3.094816591792251</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.635260919258227</v>
+        <v>-3.544969573139817</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.260738880624657</v>
+        <v>1.296855419072021</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.600695511406581</v>
+        <v>0.6909868575249897</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.075616979485643</v>
+        <v>3.129791787156689</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.534742760759472</v>
+        <v>-3.444451414641062</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.305838517398883</v>
+        <v>1.341955055846247</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7012136699053355</v>
+        <v>0.7915050160237442</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.140820247959621</v>
+        <v>3.194995055630666</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.518837431327119</v>
+        <v>-3.428546085208709</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.298955321647697</v>
+        <v>1.335071860095061</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6221010091960966</v>
+        <v>0.7123923553145053</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.08010732400995</v>
+        <v>3.134282131680995</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.473999029718721</v>
+        <v>-3.383707683600311</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.320988384901684</v>
+        <v>1.357104923349048</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.626644442140966</v>
+        <v>0.7169357882593748</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.0869310863875</v>
+        <v>3.141105894058545</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.49349748596073</v>
+        <v>-3.403206139842319</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.317349942035959</v>
+        <v>1.353466480483323</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5785598008610617</v>
+        <v>0.6688511469794705</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.062241241250635</v>
+        <v>3.116416048921681</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.449294648874829</v>
+        <v>-3.359003302756419</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.340910679398156</v>
+        <v>1.37702721784552</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6227626379469622</v>
+        <v>0.7130539840653709</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.094642546030013</v>
+        <v>3.148817353701058</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.486273676538272</v>
+        <v>-3.395982330419862</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.324529068802027</v>
+        <v>1.360645607249391</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6597365397382927</v>
+        <v>0.7500278858567014</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.115236887574059</v>
+        <v>3.169411695245104</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.327982258999</v>
+        <v>-3.23769091288059</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.439093401000775</v>
+        <v>1.475209939448139</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6597365397382927</v>
+        <v>0.7500278858567014</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.166484652757098</v>
+        <v>3.220659460428144</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.120340255364524</v>
+        <v>-3.030048909246114</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.520590907048819</v>
+        <v>1.556707445496183</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8673785433727689</v>
+        <v>0.9576698894911776</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.289510559532037</v>
+        <v>3.343685367203082</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.069308162641996</v>
+        <v>-2.979016816523586</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.5359519723761</v>
+        <v>1.572068510823464</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9184106360952968</v>
+        <v>1.008701982213706</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.315078043403824</v>
+        <v>3.369252851074869</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.00408398151479</v>
+        <v>-2.91379263539638</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.579229048919687</v>
+        <v>1.615345587367051</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9836348172225025</v>
+        <v>1.073926163340911</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.371399956172852</v>
+        <v>3.425574763843898</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.966656961443656</v>
+        <v>-2.876365615325246</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.590160829247421</v>
+        <v>1.626277367694785</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.988886355251684</v>
+        <v>1.079177701370093</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.370511851289641</v>
+        <v>3.424686658960687</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.986768617478365</v>
+        <v>-2.896477271359954</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.583372959164778</v>
+        <v>1.619489497612142</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9999137002491032</v>
+        <v>1.090205046367512</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.378385050619333</v>
+        <v>3.432559858290379</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.93302380305116</v>
+        <v>-2.84273245693275</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.765428655956871</v>
+        <v>1.801545194404235</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.009977009689565</v>
+        <v>1.100268355807974</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.544980807304821</v>
+        <v>3.599155614975866</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.858241542026147</v>
+        <v>-2.767950195907737</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.915454469584693</v>
+        <v>1.951571008032057</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.084759270714578</v>
+        <v>1.175050616832987</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.709963073137646</v>
+        <v>3.764137880808692</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.832157457762339</v>
+        <v>-2.741866111643929</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.917596079304075</v>
+        <v>1.953712617751439</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.084759270714578</v>
+        <v>1.175050616832987</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.701671049151505</v>
+        <v>3.755845856822551</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.744279544653219</v>
+        <v>-2.653988198534809</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.950940440131503</v>
+        <v>1.987056978578867</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.200684913137929</v>
+        <v>1.290976259256338</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.769419630189295</v>
+        <v>3.823594437860341</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.735387083259935</v>
+        <v>-2.645095737141525</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.972051830415608</v>
+        <v>2.008168368862972</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.200684913137929</v>
+        <v>1.290976259256338</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.786974035916087</v>
+        <v>3.841148843587132</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.903863200229813</v>
+        <v>-2.813571854111403</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.89651643103224</v>
+        <v>1.932632969479605</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.172737077421348</v>
+        <v>1.263028423539757</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.762060381890722</v>
+        <v>3.816235189561767</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.20606367136823</v>
+        <v>-2.11577232524982</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.156905939764735</v>
+        <v>2.1930224782121</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.102389018050938</v>
+        <v>1.192680364169346</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.701121243456337</v>
+        <v>3.755296051127383</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.183342567685077</v>
+        <v>-2.093051221566667</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.156658403734901</v>
+        <v>2.192774942182265</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.102389018050938</v>
+        <v>1.192680364169346</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.691785265953242</v>
+        <v>3.745960073624287</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.31254438097912</v>
+        <v>-2.22225303486071</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.263883804268453</v>
+        <v>2.300000342715817</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9731872047568955</v>
+        <v>1.063478550875304</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.773170303827986</v>
+        <v>3.827345111499031</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.467325387757375</v>
+        <v>-2.377034041638965</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.239049224050798</v>
+        <v>2.275165762498162</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9398195307024193</v>
+        <v>1.030110876820828</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.790227521888947</v>
+        <v>3.844402329559992</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.460270697542202</v>
+        <v>-2.369979351423792</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.238546456126412</v>
+        <v>2.274662994573776</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9468742209175931</v>
+        <v>1.037165567036002</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.791135692007596</v>
+        <v>3.845310499678642</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.433319473215714</v>
+        <v>-2.343028127097304</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.259333099501749</v>
+        <v>2.295449637949113</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9617545669453123</v>
+        <v>1.052045913063721</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.810070053268969</v>
+        <v>3.864244860940015</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.56927248127203</v>
+        <v>-2.47898113515362</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.389055028424182</v>
+        <v>2.425171566871546</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9617545669453123</v>
+        <v>1.052045913063721</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.994173185413929</v>
+        <v>4.048347993084974</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.591680599076902</v>
+        <v>-2.501389252958492</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.372208476205226</v>
+        <v>2.408325014652591</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9617545669453123</v>
+        <v>1.052045913063721</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.986289880316922</v>
+        <v>4.040464687987967</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.619904834654502</v>
+        <v>-2.529613488536092</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.362972781523824</v>
+        <v>2.399089319971188</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9797313193966208</v>
+        <v>1.07002266551503</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.999129931337345</v>
+        <v>4.05330473900839</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.629345760543032</v>
+        <v>-2.677617538147089</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.415450128890259</v>
+        <v>2.396141417848637</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.102158436940012</v>
+        <v>1.070552805220698</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.128839919585227</v>
+        <v>4.109876540553638</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.681619367878674</v>
+        <v>-2.72989114548273</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.397431780501303</v>
+        <v>2.378123069459681</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.049884829604371</v>
+        <v>1.018279197885057</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.100366849729143</v>
+        <v>4.081403470697555</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.75794934547958</v>
+        <v>-2.806221123083636</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.365011602354716</v>
+        <v>2.345702891313094</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.049884829604371</v>
+        <v>1.018279197885057</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.098478662622918</v>
+        <v>4.07951528359133</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.960203065803933</v>
+        <v>-3.008474843407989</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.278930343827837</v>
+        <v>2.259621632786215</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8476311092800175</v>
+        <v>0.8160254775607034</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.971946660031168</v>
+        <v>3.95298328099958</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.121771491331188</v>
+        <v>-3.170043268935244</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.212736983827087</v>
+        <v>2.193428272785465</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7208481854821381</v>
+        <v>0.6892425537628241</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.894310915962593</v>
+        <v>3.875347536931005</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.254072783428741</v>
+        <v>-3.302344561032798</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.172889873853984</v>
+        <v>2.153581162812362</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7208481854821381</v>
+        <v>0.6892425537628241</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.907384322828511</v>
+        <v>3.888420943796923</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.439941094267971</v>
+        <v>-3.488212871872028</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.090547746301232</v>
+        <v>2.07123903525961</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5622825921621905</v>
+        <v>0.5306769604428764</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.804250163619483</v>
+        <v>3.785286784587894</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.467841881377444</v>
+        <v>-3.516113658981501</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.077911472584446</v>
+        <v>2.058602761542823</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5276856680192556</v>
+        <v>0.4960800362999416</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.782016050260724</v>
+        <v>3.763052671229135</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.590367984080338</v>
+        <v>-3.638639761684395</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.025665475480487</v>
+        <v>2.006356764438864</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4051595653163618</v>
+        <v>0.3735539335970477</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.705264832616186</v>
+        <v>3.686301453584598</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.820882480265927</v>
+        <v>-3.869154257869983</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.000165636596755</v>
+        <v>1.980856925555132</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.174645069130773</v>
+        <v>0.143039437411459</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.633662094495337</v>
+        <v>3.614698715463748</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.077603298260751</v>
+        <v>-4.125875075864807</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.037789028400672</v>
+        <v>2.01848031735905</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.06623049498695821</v>
+        <v>0.03462486326764413</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.708925069010895</v>
+        <v>3.689961689979307</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.231589716036892</v>
+        <v>-4.279861493640947</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.045174730435856</v>
+        <v>2.025866019394233</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.06623049498695821</v>
+        <v>0.03462486326764413</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.777905338156535</v>
+        <v>3.758941959124947</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.181067812209226</v>
+        <v>-4.229339589813281</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.051434694087043</v>
+        <v>2.032125983045421</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.06623049498695821</v>
+        <v>0.03462486326764413</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.763956540276656</v>
+        <v>3.744993161245068</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.43354296621695</v>
+        <v>-4.481814743821006</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.962315121539367</v>
+        <v>1.943006410497745</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.06623049498695821</v>
+        <v>0.03462486326764413</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.77582702933207</v>
+        <v>3.756863650300482</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.726438722696362</v>
+        <v>-4.774710500300418</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.846367353466546</v>
+        <v>1.827058642424924</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.06623049498695821</v>
+        <v>0.03462486326764413</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.777037563851013</v>
+        <v>3.758074184819425</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.883982794425804</v>
+        <v>-4.932254572029859</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.787471467002091</v>
+        <v>1.768162755960469</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.0006713101533162846</v>
+        <v>-0.03227694187263036</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.74101822299417</v>
+        <v>3.722054843962582</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.161947190009077</v>
+        <v>-5.210218967613133</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.671363561504971</v>
+        <v>1.652054850463349</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.09029104443880054</v>
+        <v>-0.1218966761581146</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.682324235159069</v>
+        <v>3.663360856127481</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.278914882647968</v>
+        <v>-5.327186660252024</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.786780541148459</v>
+        <v>1.767471830106837</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.09029104443880054</v>
+        <v>-0.1218966761581146</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.844528291858113</v>
+        <v>3.825564912826525</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.363632824868922</v>
+        <v>-5.411904602472977</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.747740002223892</v>
+        <v>1.728431291182269</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1754070733668469</v>
+        <v>-0.207012705086161</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.788305312465099</v>
+        <v>3.769341933433511</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.445567643137805</v>
+        <v>-5.49383942074186</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.725195492484829</v>
+        <v>1.705886781443207</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1853418189539271</v>
+        <v>-0.2169474506732412</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.792573882681343</v>
+        <v>3.773610503649754</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.547543765386212</v>
+        <v>-5.595815542990268</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.693330682041369</v>
+        <v>1.674021970999747</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2873179412023347</v>
+        <v>-0.3189235729216487</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.740313847788201</v>
+        <v>3.721350468756612</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.437537481908991</v>
+        <v>-5.485809259513046</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.729486082676433</v>
+        <v>1.710177371634811</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2641133692850595</v>
+        <v>-0.2957190010043735</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.746389478182741</v>
+        <v>3.727426099151153</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.294477906168066</v>
+        <v>-5.342749683772121</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.790959923694777</v>
+        <v>1.771651212653155</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2560999426950802</v>
+        <v>-0.2877055744143943</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.755447544858703</v>
+        <v>3.736484165827114</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.993031180696228</v>
+        <v>-5.041302958300284</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.918799496766048</v>
+        <v>1.899490785724426</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.04534678277675708</v>
+        <v>0.013741151057443</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.943576463024341</v>
+        <v>3.924613083992753</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.017621424931412</v>
+        <v>-5.065893202535467</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.909934576824685</v>
+        <v>1.890625865783063</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.04534678277675708</v>
+        <v>0.013741151057443</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.944547640777052</v>
+        <v>3.925584261745463</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.966583048924892</v>
+        <v>-5.014854826528947</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.931192831607048</v>
+        <v>1.911884120565426</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.04534678277675708</v>
+        <v>0.013741151057443</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.945390545156807</v>
+        <v>3.926427166125219</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.925443754058261</v>
+        <v>-4.973715531662316</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.966686648427846</v>
+        <v>1.947377937386224</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.08648607764338789</v>
+        <v>0.05488044592407382</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.989112220950931</v>
+        <v>3.970148841919342</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.814837613978659</v>
+        <v>-4.863109391582714</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.827113100583622</v>
+        <v>1.807804389541999</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1970922177229899</v>
+        <v>0.1654865860036758</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.871659901122626</v>
+        <v>3.852696522091038</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.945418348509501</v>
+        <v>-4.993690126113557</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.778382850845248</v>
+        <v>1.759074139803626</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.06651148319214739</v>
+        <v>0.03490585147283332</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.796813504478085</v>
+        <v>3.777850125446496</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.78092201431854</v>
+        <v>-4.829193791922595</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.828608203597716</v>
+        <v>1.809299492556093</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.06651148319214739</v>
+        <v>0.03490585147283332</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.781240323554167</v>
+        <v>3.762276944522579</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.808291947002972</v>
+        <v>-4.856563724607027</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.816847940960372</v>
+        <v>1.79753922991875</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.06651148319214739</v>
+        <v>0.03490585147283332</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.780428033990597</v>
+        <v>3.761464654959009</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.818677141892861</v>
+        <v>-4.866948919496917</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.822562642129489</v>
+        <v>1.803253931087867</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.05612628830225808</v>
+        <v>0.024520656582944</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.784065696181736</v>
+        <v>3.765102317150148</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.837265300615086</v>
+        <v>-4.885537078219142</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.885964384417024</v>
+        <v>1.866655673375402</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.03753812958003272</v>
+        <v>0.005932497860718644</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.843749806724826</v>
+        <v>3.824786427693237</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.837563847311122</v>
+        <v>-4.885835624915178</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.882713976556908</v>
+        <v>1.863405265515286</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.03753812958003272</v>
+        <v>0.005932497860718644</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.840618817543124</v>
+        <v>3.821655438511536</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.736740713620694</v>
+        <v>-4.78501249122475</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.927574124972471</v>
+        <v>1.908265413930849</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.05000234506438656</v>
+        <v>0.01839671334507248</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.852628241773128</v>
+        <v>3.83366486274154</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.545959352868287</v>
+        <v>-4.594231130472343</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.004015922751977</v>
+        <v>1.984707211710355</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.2407837058167939</v>
+        <v>0.2091780740974798</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.967226311703116</v>
+        <v>3.948262932671527</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.527442498826467</v>
+        <v>-4.575714276430523</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.991259510106302</v>
+        <v>1.971950799064679</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.2537138352420021</v>
+        <v>0.2221082035226881</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.954821235095837</v>
+        <v>3.935857856064249</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.502249314325149</v>
+        <v>-4.550521091929205</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.036303720518887</v>
+        <v>2.016995009477265</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.2789070197433205</v>
+        <v>0.2473013880240064</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.004904082408687</v>
+        <v>3.985940703377098</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.490195187412186</v>
+        <v>-4.538466965016242</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.03481193918551</v>
+        <v>2.015503228143888</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.2909611466562833</v>
+        <v>0.2593555149369692</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.005823126457902</v>
+        <v>3.986859747426314</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.496818434102544</v>
+        <v>-4.5450902117066</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.034043270693503</v>
+        <v>2.01473455965188</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.284337899965925</v>
+        <v>0.2527322682466109</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.003729808627823</v>
+        <v>3.984766429596235</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.393937844573951</v>
+        <v>-4.442209622178007</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.088046532382823</v>
+        <v>2.0687378213412</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.3872184894945179</v>
+        <v>0.3556128577752038</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.078309188222861</v>
+        <v>4.059345809191273</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.417379883754038</v>
+        <v>-4.465651661358094</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.098872386884381</v>
+        <v>2.07956367584276</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.3872184894945179</v>
+        <v>0.3556128577752038</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.098511858396455</v>
+        <v>4.079548479364867</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.43545239204565</v>
+        <v>-4.483724169649705</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.091643383567737</v>
+        <v>2.072334672526115</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.3872184894945179</v>
+        <v>0.3556128577752038</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.098511858396455</v>
+        <v>4.079548479364867</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.666626185922282</v>
+        <v>-4.714897963526337</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.959425779610551</v>
+        <v>1.940117068568929</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.3872184894945179</v>
+        <v>0.3556128577752038</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.058763771989922</v>
+        <v>4.039800392958334</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.790525528200734</v>
+        <v>3.487846497586397</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.732847467393282</v>
+        <v>-4.781119244997337</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.939959886019091</v>
+        <v>1.920651174977469</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.3209972080235182</v>
+        <v>0.2893915763042041</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.026053622104262</v>
+        <v>4.007090243072674</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240809.xlsx
+++ b/tame_output/ON/bt/strategyON_20240809.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>50.7%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>80.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.0%</t>
+          <t>421.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-639.7%</t>
+          <t>-634.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-184.2%</t>
+          <t>-182.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-637.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-191.7%</t>
+          <t>-156.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-195.1%</t>
+          <t>-191.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-54.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2050"/>
+  <dimension ref="A1:G2051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.626458215463892</v>
+        <v>-6.716749561582301</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5031018507842644</v>
+        <v>0.4669853123369005</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3119688958444667</v>
+        <v>-0.4022602419628756</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.966860223776889</v>
+        <v>2.912685416105843</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.377458416780311</v>
+        <v>-6.46774976289872</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6156081114813556</v>
+        <v>0.5794915730339918</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06296909716088606</v>
+        <v>-0.1532604432792949</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.129166444210696</v>
+        <v>3.074991636539651</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.483048406553415</v>
+        <v>-6.573339752671824</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.445396185972895</v>
+        <v>0.4092796475255316</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1685590869339904</v>
+        <v>-0.2588504330523992</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937836520747615</v>
+        <v>2.883661713076569</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.501783308672012</v>
+        <v>-6.592074654790421</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4864465670025426</v>
+        <v>0.4503300285551788</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1741550965941217</v>
+        <v>-0.2644464427125305</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.983023256828622</v>
+        <v>2.928848449157577</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.353843267264413</v>
+        <v>-6.444134613382822</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4257436608774148</v>
+        <v>0.3896271224300509</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1538341806855641</v>
+        <v>-0.244125526803973</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.875336883685589</v>
+        <v>2.821162076014544</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.300873745010424</v>
+        <v>-6.391165091128833</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4382174835255319</v>
+        <v>0.4021009450781685</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1911560045499841</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.898404610784504</v>
+        <v>2.844229803113459</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.135085549050133</v>
+        <v>-6.225376895168543</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4975721498145553</v>
+        <v>0.4614556113671915</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1911560045499841</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.891443998689411</v>
+        <v>2.837269191018366</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.101722342571365</v>
+        <v>-6.192013688689774</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5253797867872056</v>
+        <v>0.4892632483398422</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1911560045499841</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.905906353070554</v>
+        <v>2.851731545399509</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.993463205448843</v>
+        <v>-6.083754551567252</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5632155620954094</v>
+        <v>0.527099023648046</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1911560045499841</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.900438473529749</v>
+        <v>2.846263665858704</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.870172070631712</v>
+        <v>-5.960463416750121</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6100301100328389</v>
+        <v>0.5739135715854751</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.02242647638555523</v>
+        <v>-0.06786486973285361</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.971911248430605</v>
+        <v>2.917736440759559</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.849022871728269</v>
+        <v>-5.939314217846678</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6261907678315413</v>
+        <v>0.5900742293841774</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.04357567528899858</v>
+        <v>-0.04671567082941025</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.992301746009995</v>
+        <v>2.93812693833895</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.605257429744825</v>
+        <v>-5.695548775863234</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7194776529719697</v>
+        <v>0.6833611145246059</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.04357567528899858</v>
+        <v>-0.04671567082941025</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.988082454357046</v>
+        <v>2.933907646686001</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.50349460946753</v>
+        <v>-5.593785955585939</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7623070950029036</v>
+        <v>0.7261905565555398</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.03349660243698155</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.998138209312519</v>
+        <v>2.943963401641474</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.253644215518455</v>
+        <v>-5.343935561636864</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8549893275662357</v>
+        <v>0.8188727891188718</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.03349660243698155</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.990880284296221</v>
+        <v>2.936705476625176</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.077752123051022</v>
+        <v>-5.168043469169431</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9289452880738573</v>
+        <v>0.8928287496264939</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.03349660243698155</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.99447940781687</v>
+        <v>2.940304600145825</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.906305660028559</v>
+        <v>-4.996597006146968</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.010851379337397</v>
+        <v>0.9747348408900329</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2282412067038904</v>
+        <v>0.1379498605854816</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.110674791684902</v>
+        <v>3.056499984013857</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.832016094290219</v>
+        <v>-4.922307440408629</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.039587683249029</v>
+        <v>1.003471144801666</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3025307724422297</v>
+        <v>0.2122394263238209</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.154269008744202</v>
+        <v>3.100094201073157</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.768380352056285</v>
+        <v>-4.858671698174694</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.06973678119692</v>
+        <v>1.033620242749557</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.2758751685577554</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.197145255138881</v>
+        <v>3.142970447467835</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.656953592730365</v>
+        <v>-4.747244938848774</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.095501743711084</v>
+        <v>1.05938520526372</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.2758751685577554</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.178339513922676</v>
+        <v>3.124164706251631</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.667456215795654</v>
+        <v>-4.757747561914063</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.093043771109846</v>
+        <v>1.056927232662482</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.2653725454924665</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.17378101670838</v>
+        <v>3.119606209037335</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.595213647624459</v>
+        <v>-4.685504993742868</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.125870112213144</v>
+        <v>1.08975357376578</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.2653725454924665</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.1777103305432</v>
+        <v>3.123535522872155</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.577499960746594</v>
+        <v>-4.667791306865003</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.13363417088163</v>
+        <v>1.097517632434266</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.2685538743893833</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.18029771179869</v>
+        <v>3.126122904127645</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.468695075266867</v>
+        <v>-4.558986421385276</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.174154196293514</v>
+        <v>1.138037657846151</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.2685538743893833</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.177295783018684</v>
+        <v>3.123120975347638</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.248674277229856</v>
+        <v>-4.338965623348265</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.263741552518933</v>
+        <v>1.227625014071569</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.4097737194573636</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.263606727070086</v>
+        <v>3.209431919399041</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.115806588166579</v>
+        <v>-4.206097934284988</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.332782810946067</v>
+        <v>1.296666272498703</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.4097737194573636</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.279500909871909</v>
+        <v>3.225326102200864</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.99563350480208</v>
+        <v>-4.085924850920489</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.381997888732168</v>
+        <v>1.345881350284805</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6202381489402713</v>
+        <v>0.5299468028218626</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.352750604330911</v>
+        <v>3.298575796659865</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.860380143472103</v>
+        <v>-3.950671489590512</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.446187335825599</v>
+        <v>1.410070797378235</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7554915102702484</v>
+        <v>0.6652001641518397</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.443990723690337</v>
+        <v>3.389815916019292</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.920254970829795</v>
+        <v>-4.010546316948204</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.408274896283948</v>
+        <v>1.372158357836584</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.6053253367941476</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.394103318677147</v>
+        <v>3.339928511006102</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.800434739918958</v>
+        <v>-3.890726086037367</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.471492157882492</v>
+        <v>1.435375619435128</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.6053253367941476</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.409392487911356</v>
+        <v>3.355217680240311</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.802904446380764</v>
+        <v>-3.893195792499173</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.378148474620211</v>
+        <v>1.342031936172847</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6931469764507501</v>
+        <v>0.6028556303323414</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.315554863356714</v>
+        <v>3.261380055685668</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.871274632704774</v>
+        <v>-3.961565978823183</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.270062261575908</v>
+        <v>1.233945723128544</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6121313293685563</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.240382144263744</v>
+        <v>3.186207336592699</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.88506268555182</v>
+        <v>-3.975354031670229</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.254983749068981</v>
+        <v>1.218867210621617</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6121313293685563</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.230818852895635</v>
+        <v>3.17664404522459</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.94058276144441</v>
+        <v>-4.030874107562819</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.369806555404147</v>
+        <v>1.333690016956784</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6121313293685563</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.367849689587838</v>
+        <v>3.313674881916793</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.765108501651941</v>
+        <v>-3.85539984777035</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.444563491312923</v>
+        <v>1.408446952865559</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6121313293685563</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.372416921579625</v>
+        <v>3.31824211390858</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.876044754293189</v>
+        <v>-3.966336100411598</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.37593101901763</v>
+        <v>1.339814480570267</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6121313293685563</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.348158950340832</v>
+        <v>3.293984142669787</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.842381208820907</v>
+        <v>-3.932672554939316</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.317934750607993</v>
+        <v>1.281818212160629</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6457948748408382</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.296895391025652</v>
+        <v>3.242720583354606</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.782528589617184</v>
+        <v>-3.872819935735593</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.352048184721615</v>
+        <v>1.315931646274251</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6457948748408382</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.307067777457784</v>
+        <v>3.252892969786739</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.696285126590807</v>
+        <v>-3.786576472709216</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.381491840506026</v>
+        <v>1.345375302058662</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6457948748408382</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.302014048031644</v>
+        <v>3.247839240360599</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.741591945989787</v>
+        <v>-3.831883292108196</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.355144888190959</v>
+        <v>1.319028349743596</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.6049847118316074</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.269303725670631</v>
+        <v>3.215128917999586</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.770625050692088</v>
+        <v>-3.860916396810497</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.34408351934314</v>
+        <v>1.307966980895777</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.6049847118316074</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.269855598703733</v>
+        <v>3.215680791032688</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.677814569241229</v>
+        <v>-3.768105915359638</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.31048040381485</v>
+        <v>1.274363865367486</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7880865394008755</v>
+        <v>0.6977951932824668</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.254814579465614</v>
+        <v>3.200639771794569</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.722204038570657</v>
+        <v>-3.812495384689066</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.294598092007679</v>
+        <v>1.258481553560316</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7436970700714478</v>
+        <v>0.6534057239530391</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.230054373792558</v>
+        <v>3.175879566121513</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.838745643675999</v>
+        <v>-3.929036989794409</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.243057158477265</v>
+        <v>1.206940620029902</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.5368641188476964</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.155205119241076</v>
+        <v>3.10103031157003</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.726368642493327</v>
+        <v>-3.816659988611736</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.293499254781002</v>
+        <v>1.257382716333638</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.5368641188476964</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.160696415071743</v>
+        <v>3.106521607400698</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.75414904039468</v>
+        <v>-3.844440386513089</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.293884297388999</v>
+        <v>1.257767758941636</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.599375067064752</v>
+        <v>0.5090837209463432</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.15552537809947</v>
+        <v>3.101350570428425</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.872529713124818</v>
+        <v>-3.962821059243228</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.084887748297597</v>
+        <v>1.048771209850234</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.441865868795367</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.953550386809538</v>
+        <v>2.899375579138492</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.98114379156815</v>
+        <v>-4.071435137686558</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.16159177763947</v>
+        <v>1.125475239192107</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.441865868795367</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.073700047528743</v>
+        <v>3.019525239857698</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.945734753320007</v>
+        <v>-4.036026099438415</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.190268419041051</v>
+        <v>1.154151880593687</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.441865868795367</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.088213073631066</v>
+        <v>3.034038265960021</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.907351090761856</v>
+        <v>-3.997642436880264</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.20304132540668</v>
+        <v>1.166924786959316</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.4802495313535182</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.108662712508325</v>
+        <v>3.054487904837281</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.730234760726689</v>
+        <v>-3.820526106845098</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.270616886266048</v>
+        <v>1.234500347818685</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.4802495313535182</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.105391741353627</v>
+        <v>3.051216933682583</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.775327005560235</v>
+        <v>-3.865618351678644</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.253263380094543</v>
+        <v>1.217146841647179</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5086448343025372</v>
+        <v>0.4183534881841284</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.068937507213907</v>
+        <v>3.014762699542862</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.595951584321467</v>
+        <v>-3.686242930439876</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.318800523896464</v>
+        <v>1.282683985449101</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6654215924732558</v>
+        <v>0.5751302463548471</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.156790537422753</v>
+        <v>3.102615729751707</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.640965797842073</v>
+        <v>-3.731257143960482</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.281602293819812</v>
+        <v>1.245485755372448</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6350726971586512</v>
+        <v>0.5447813510402425</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.119388655565579</v>
+        <v>3.065213847894534</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.907970308114509</v>
+        <v>-3.998261654232918</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.180492052049783</v>
+        <v>1.14437551360242</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4407096591157026</v>
+        <v>0.3504183129972939</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.008462395078756</v>
+        <v>2.954287587407711</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.009168089551681</v>
+        <v>-4.099459435670091</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.139216861371416</v>
+        <v>1.103100322924052</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.2820094994519747</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.966621028848066</v>
+        <v>2.912446221177021</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.002657122937369</v>
+        <v>-4.092948469055778</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.139421209571458</v>
+        <v>1.103304671124094</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.2820094994519747</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.964220990402382</v>
+        <v>2.910046182731338</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.983618995230072</v>
+        <v>-4.073910341348481</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.143561179862621</v>
+        <v>1.107444641415258</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.2238258881207802</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.925835542811911</v>
+        <v>2.871660735140865</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.01474562638069</v>
+        <v>-4.105036972499099</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.250404929036564</v>
+        <v>1.214288390589201</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.2238258881207802</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.045129944446101</v>
+        <v>2.990955136775056</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.028612387714608</v>
+        <v>-4.118903733833017</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.245691553489131</v>
+        <v>1.209575015041767</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.276259317505366</v>
+        <v>0.1859679713869573</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.023248523391941</v>
+        <v>2.969073715720896</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.983808216174678</v>
+        <v>-4.074099562293087</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.269621752502029</v>
+        <v>1.233505214054665</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.276259317505366</v>
+        <v>0.1859679713869573</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.029257053788867</v>
+        <v>2.975082246117822</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.836065245939676</v>
+        <v>-3.926356592058085</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.226669161873229</v>
+        <v>1.190552623425865</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.3537753286218404</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.027891689406996</v>
+        <v>2.973716881735951</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.919886467214374</v>
+        <v>-4.010177813332783</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.195934294894831</v>
+        <v>1.159817756447467</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.3537753286218404</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.030685310938477</v>
+        <v>2.976510503267432</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.913733761161589</v>
+        <v>-4.004025107279999</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.199057725707603</v>
+        <v>1.162941187260239</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4502193807930334</v>
+        <v>0.3599280346746247</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.035039282961806</v>
+        <v>2.980864475290761</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.930543059312091</v>
+        <v>-4.020834405430501</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.191414483187512</v>
+        <v>1.155297944740149</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.3431187365241231</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.024034180811615</v>
+        <v>2.96985937314057</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.868245060535969</v>
+        <v>-3.958536406654379</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.282669236494782</v>
+        <v>1.246552698047418</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.3431187365241231</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.090369734608436</v>
+        <v>3.036194926937391</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.666454862870811</v>
+        <v>-3.756746208989221</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.165677317274972</v>
+        <v>1.129560778827609</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6314282748116862</v>
+        <v>0.5411369286932775</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.011472651624056</v>
+        <v>2.957297843953011</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.717341575557006</v>
+        <v>-3.807632921675415</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.21561286452267</v>
+        <v>1.179496326075306</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5805415621254917</v>
+        <v>0.490250216007083</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.051230856334515</v>
+        <v>2.997056048663469</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.630730832907199</v>
+        <v>-3.721022179025608</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.264884897698636</v>
+        <v>1.228768359251272</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6591672933306499</v>
+        <v>0.5688759472122412</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.113034031173653</v>
+        <v>3.058859223502608</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.690940130912483</v>
+        <v>-3.781231477030893</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.239337159321194</v>
+        <v>1.20322062087383</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.5086666492069567</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.075444433195154</v>
+        <v>3.021269625524109</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.614518084480556</v>
+        <v>-3.704809430598966</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.268397595933893</v>
+        <v>1.232281057486529</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.5086666492069567</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.073936051235083</v>
+        <v>3.019761243564037</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.570144952841988</v>
+        <v>-3.660436298960397</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.286009716024757</v>
+        <v>1.249893177577393</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.643331126963934</v>
+        <v>0.5530397808455253</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.10042279765366</v>
+        <v>3.046247989982615</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.592625303700872</v>
+        <v>-3.682916649819282</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.271411369819794</v>
+        <v>1.23529483137243</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.643331126963934</v>
+        <v>0.5530397808455253</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.094816591792251</v>
+        <v>3.040641784121205</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.544969573139817</v>
+        <v>-3.635260919258227</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.296855419072021</v>
+        <v>1.260738880624657</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6909868575249897</v>
+        <v>0.600695511406581</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.129791787156689</v>
+        <v>3.075616979485643</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.444451414641062</v>
+        <v>-3.534742760759472</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.341955055846247</v>
+        <v>1.305838517398883</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7915050160237442</v>
+        <v>0.7012136699053355</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.194995055630666</v>
+        <v>3.140820247959621</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.428546085208709</v>
+        <v>-3.518837431327119</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.335071860095061</v>
+        <v>1.298955321647697</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7123923553145053</v>
+        <v>0.6221010091960966</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.134282131680995</v>
+        <v>3.08010732400995</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.383707683600311</v>
+        <v>-3.473999029718721</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.357104923349048</v>
+        <v>1.320988384901684</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7169357882593748</v>
+        <v>0.626644442140966</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.141105894058545</v>
+        <v>3.0869310863875</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.403206139842319</v>
+        <v>-3.49349748596073</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.353466480483323</v>
+        <v>1.317349942035959</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6688511469794705</v>
+        <v>0.5785598008610617</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.116416048921681</v>
+        <v>3.062241241250635</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.359003302756419</v>
+        <v>-3.449294648874829</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.37702721784552</v>
+        <v>1.340910679398156</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7130539840653709</v>
+        <v>0.6227626379469622</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.148817353701058</v>
+        <v>3.094642546030013</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.395982330419862</v>
+        <v>-3.486273676538272</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.360645607249391</v>
+        <v>1.324529068802027</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7500278858567014</v>
+        <v>0.6597365397382927</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.169411695245104</v>
+        <v>3.115236887574059</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.23769091288059</v>
+        <v>-3.327982258999</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.475209939448139</v>
+        <v>1.439093401000775</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7500278858567014</v>
+        <v>0.6597365397382927</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.220659460428144</v>
+        <v>3.166484652757098</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.030048909246114</v>
+        <v>-3.120340255364524</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.556707445496183</v>
+        <v>1.520590907048819</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9576698894911776</v>
+        <v>0.8673785433727689</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.343685367203082</v>
+        <v>3.289510559532037</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.979016816523586</v>
+        <v>-3.069308162641996</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.572068510823464</v>
+        <v>1.5359519723761</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.008701982213706</v>
+        <v>0.9184106360952968</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.369252851074869</v>
+        <v>3.315078043403824</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.91379263539638</v>
+        <v>-3.00408398151479</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.615345587367051</v>
+        <v>1.579229048919687</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.073926163340911</v>
+        <v>0.9836348172225025</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.425574763843898</v>
+        <v>3.371399956172852</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.876365615325246</v>
+        <v>-2.966656961443656</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.626277367694785</v>
+        <v>1.590160829247421</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.079177701370093</v>
+        <v>0.988886355251684</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.424686658960687</v>
+        <v>3.370511851289641</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.896477271359954</v>
+        <v>-2.986768617478365</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.619489497612142</v>
+        <v>1.583372959164778</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.090205046367512</v>
+        <v>0.9999137002491032</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.432559858290379</v>
+        <v>3.378385050619333</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.84273245693275</v>
+        <v>-2.93302380305116</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.801545194404235</v>
+        <v>1.765428655956871</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.100268355807974</v>
+        <v>1.009977009689565</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.599155614975866</v>
+        <v>3.544980807304821</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.767950195907737</v>
+        <v>-2.858241542026147</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.951571008032057</v>
+        <v>1.915454469584693</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.175050616832987</v>
+        <v>1.084759270714578</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.764137880808692</v>
+        <v>3.709963073137646</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.741866111643929</v>
+        <v>-2.832157457762339</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.953712617751439</v>
+        <v>1.917596079304075</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.175050616832987</v>
+        <v>1.084759270714578</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.755845856822551</v>
+        <v>3.701671049151505</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.653988198534809</v>
+        <v>-2.744279544653219</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.987056978578867</v>
+        <v>1.950940440131503</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.290976259256338</v>
+        <v>1.200684913137929</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.823594437860341</v>
+        <v>3.769419630189295</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.645095737141525</v>
+        <v>-2.735387083259935</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.008168368862972</v>
+        <v>1.972051830415608</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.290976259256338</v>
+        <v>1.200684913137929</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.841148843587132</v>
+        <v>3.786974035916087</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.813571854111403</v>
+        <v>-2.903863200229813</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.932632969479605</v>
+        <v>1.89651643103224</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.263028423539757</v>
+        <v>1.172737077421348</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.816235189561767</v>
+        <v>3.762060381890722</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.11577232524982</v>
+        <v>-2.20606367136823</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.1930224782121</v>
+        <v>2.156905939764735</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.192680364169346</v>
+        <v>1.102389018050938</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.755296051127383</v>
+        <v>3.701121243456337</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.093051221566667</v>
+        <v>-2.183342567685077</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.192774942182265</v>
+        <v>2.156658403734901</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.192680364169346</v>
+        <v>1.102389018050938</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.745960073624287</v>
+        <v>3.691785265953242</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.22225303486071</v>
+        <v>-2.31254438097912</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.300000342715817</v>
+        <v>2.263883804268453</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.063478550875304</v>
+        <v>0.9731872047568955</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.827345111499031</v>
+        <v>3.773170303827986</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.377034041638965</v>
+        <v>-2.467325387757375</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.275165762498162</v>
+        <v>2.239049224050798</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.030110876820828</v>
+        <v>0.9398195307024193</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.844402329559992</v>
+        <v>3.790227521888947</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.369979351423792</v>
+        <v>-2.460270697542202</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.274662994573776</v>
+        <v>2.238546456126412</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.037165567036002</v>
+        <v>0.9468742209175931</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.845310499678642</v>
+        <v>3.791135692007596</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.343028127097304</v>
+        <v>-2.433319473215714</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.295449637949113</v>
+        <v>2.259333099501749</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.052045913063721</v>
+        <v>0.9617545669453123</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.864244860940015</v>
+        <v>3.810070053268969</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.47898113515362</v>
+        <v>-2.56927248127203</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.425171566871546</v>
+        <v>2.389055028424182</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.052045913063721</v>
+        <v>0.9617545669453123</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.048347993084974</v>
+        <v>3.994173185413929</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.501389252958492</v>
+        <v>-2.591680599076902</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.408325014652591</v>
+        <v>2.372208476205226</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.052045913063721</v>
+        <v>0.9617545669453123</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.040464687987967</v>
+        <v>3.986289880316922</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.529613488536092</v>
+        <v>-2.619904834654502</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.399089319971188</v>
+        <v>2.362972781523824</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.07002266551503</v>
+        <v>0.9797313193966208</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.05330473900839</v>
+        <v>3.999129931337345</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.677617538147089</v>
+        <v>-2.629345760543032</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.396141417848637</v>
+        <v>2.415450128890259</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.070552805220698</v>
+        <v>1.102158436940012</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.109876540553638</v>
+        <v>4.128839919585227</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.72989114548273</v>
+        <v>-2.681619367878674</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.378123069459681</v>
+        <v>2.397431780501303</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.018279197885057</v>
+        <v>1.049884829604371</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.081403470697555</v>
+        <v>4.100366849729143</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.806221123083636</v>
+        <v>-2.75794934547958</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.345702891313094</v>
+        <v>2.365011602354716</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.018279197885057</v>
+        <v>1.049884829604371</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.07951528359133</v>
+        <v>4.098478662622918</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.008474843407989</v>
+        <v>-2.960203065803933</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.259621632786215</v>
+        <v>2.278930343827837</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8160254775607034</v>
+        <v>0.8476311092800175</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.95298328099958</v>
+        <v>3.971946660031168</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.170043268935244</v>
+        <v>-3.121771491331188</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.193428272785465</v>
+        <v>2.212736983827087</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6892425537628241</v>
+        <v>0.7208481854821381</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.875347536931005</v>
+        <v>3.894310915962593</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.302344561032798</v>
+        <v>-3.254072783428741</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.153581162812362</v>
+        <v>2.172889873853984</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6892425537628241</v>
+        <v>0.7208481854821381</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.888420943796923</v>
+        <v>3.907384322828511</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.488212871872028</v>
+        <v>-3.439941094267971</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.07123903525961</v>
+        <v>2.090547746301232</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5306769604428764</v>
+        <v>0.5622825921621905</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.785286784587894</v>
+        <v>3.804250163619483</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.516113658981501</v>
+        <v>-3.467841881377444</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.058602761542823</v>
+        <v>2.077911472584446</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4960800362999416</v>
+        <v>0.5276856680192556</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.763052671229135</v>
+        <v>3.782016050260724</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.638639761684395</v>
+        <v>-3.590367984080338</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.006356764438864</v>
+        <v>2.025665475480487</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3735539335970477</v>
+        <v>0.4051595653163618</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.686301453584598</v>
+        <v>3.705264832616186</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.869154257869983</v>
+        <v>-3.820882480265927</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.980856925555132</v>
+        <v>2.000165636596755</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.143039437411459</v>
+        <v>0.174645069130773</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.614698715463748</v>
+        <v>3.633662094495337</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.125875075864807</v>
+        <v>-4.077603298260751</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.01848031735905</v>
+        <v>2.037789028400672</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.03462486326764413</v>
+        <v>0.06623049498695821</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.689961689979307</v>
+        <v>3.708925069010895</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.279861493640947</v>
+        <v>-4.231589716036892</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.025866019394233</v>
+        <v>2.045174730435856</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.03462486326764413</v>
+        <v>0.06623049498695821</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.758941959124947</v>
+        <v>3.777905338156535</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.229339589813281</v>
+        <v>-4.181067812209226</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.032125983045421</v>
+        <v>2.051434694087043</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.03462486326764413</v>
+        <v>0.06623049498695821</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.744993161245068</v>
+        <v>3.763956540276656</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.481814743821006</v>
+        <v>-4.43354296621695</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.943006410497745</v>
+        <v>1.962315121539367</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.03462486326764413</v>
+        <v>0.06623049498695821</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.756863650300482</v>
+        <v>3.77582702933207</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.774710500300418</v>
+        <v>-4.726438722696362</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.827058642424924</v>
+        <v>1.846367353466546</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.03462486326764413</v>
+        <v>0.06623049498695821</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.758074184819425</v>
+        <v>3.777037563851013</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.932254572029859</v>
+        <v>-4.883982794425804</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.768162755960469</v>
+        <v>1.787471467002091</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.03227694187263036</v>
+        <v>-0.0006713101533162846</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.722054843962582</v>
+        <v>3.74101822299417</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.210218967613133</v>
+        <v>-5.161947190009077</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.652054850463349</v>
+        <v>1.671363561504971</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.1218966761581146</v>
+        <v>-0.09029104443880054</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.663360856127481</v>
+        <v>3.682324235159069</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.327186660252024</v>
+        <v>-5.278914882647968</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.767471830106837</v>
+        <v>1.786780541148459</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.1218966761581146</v>
+        <v>-0.09029104443880054</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.825564912826525</v>
+        <v>3.844528291858113</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.411904602472977</v>
+        <v>-5.363632824868922</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.728431291182269</v>
+        <v>1.747740002223892</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.207012705086161</v>
+        <v>-0.1754070733668469</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.769341933433511</v>
+        <v>3.788305312465099</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.49383942074186</v>
+        <v>-5.445567643137805</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.705886781443207</v>
+        <v>1.725195492484829</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.2169474506732412</v>
+        <v>-0.1853418189539271</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.773610503649754</v>
+        <v>3.792573882681343</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.595815542990268</v>
+        <v>-5.547543765386212</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.674021970999747</v>
+        <v>1.693330682041369</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.3189235729216487</v>
+        <v>-0.2873179412023347</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.721350468756612</v>
+        <v>3.740313847788201</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.485809259513046</v>
+        <v>-5.437537481908991</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.710177371634811</v>
+        <v>1.729486082676433</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2957190010043735</v>
+        <v>-0.2641133692850595</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.727426099151153</v>
+        <v>3.746389478182741</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.342749683772121</v>
+        <v>-5.294477906168066</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.771651212653155</v>
+        <v>1.790959923694777</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2877055744143943</v>
+        <v>-0.2560999426950802</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.736484165827114</v>
+        <v>3.755447544858703</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.041302958300284</v>
+        <v>-4.993031180696228</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.899490785724426</v>
+        <v>1.918799496766048</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.013741151057443</v>
+        <v>0.04534678277675708</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.924613083992753</v>
+        <v>3.943576463024341</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.065893202535467</v>
+        <v>-5.017621424931412</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.890625865783063</v>
+        <v>1.909934576824685</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.013741151057443</v>
+        <v>0.04534678277675708</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.925584261745463</v>
+        <v>3.944547640777052</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.014854826528947</v>
+        <v>-4.966583048924892</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.911884120565426</v>
+        <v>1.931192831607048</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.013741151057443</v>
+        <v>0.04534678277675708</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.926427166125219</v>
+        <v>3.945390545156807</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.973715531662316</v>
+        <v>-4.925443754058261</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.947377937386224</v>
+        <v>1.966686648427846</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.05488044592407382</v>
+        <v>0.08648607764338789</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.970148841919342</v>
+        <v>3.989112220950931</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.863109391582714</v>
+        <v>-4.814837613978659</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.807804389541999</v>
+        <v>1.827113100583622</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1654865860036758</v>
+        <v>0.1970922177229899</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.852696522091038</v>
+        <v>3.871659901122626</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.993690126113557</v>
+        <v>-4.945418348509501</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.759074139803626</v>
+        <v>1.778382850845248</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.03490585147283332</v>
+        <v>0.06651148319214739</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.777850125446496</v>
+        <v>3.796813504478085</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.829193791922595</v>
+        <v>-4.78092201431854</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.809299492556093</v>
+        <v>1.828608203597716</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.03490585147283332</v>
+        <v>0.06651148319214739</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.762276944522579</v>
+        <v>3.781240323554167</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.856563724607027</v>
+        <v>-4.808291947002972</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.79753922991875</v>
+        <v>1.816847940960372</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.03490585147283332</v>
+        <v>0.06651148319214739</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.761464654959009</v>
+        <v>3.780428033990597</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.866948919496917</v>
+        <v>-4.818677141892861</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.803253931087867</v>
+        <v>1.822562642129489</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.024520656582944</v>
+        <v>0.05612628830225808</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.765102317150148</v>
+        <v>3.784065696181736</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.885537078219142</v>
+        <v>-4.837265300615086</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.866655673375402</v>
+        <v>1.885964384417024</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.005932497860718644</v>
+        <v>0.03753812958003272</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.824786427693237</v>
+        <v>3.843749806724826</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.885835624915178</v>
+        <v>-4.837563847311122</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.863405265515286</v>
+        <v>1.882713976556908</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.005932497860718644</v>
+        <v>0.03753812958003272</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.821655438511536</v>
+        <v>3.840618817543124</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.78501249122475</v>
+        <v>-4.736740713620694</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.908265413930849</v>
+        <v>1.927574124972471</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.01839671334507248</v>
+        <v>0.05000234506438656</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.83366486274154</v>
+        <v>3.852628241773128</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.594231130472343</v>
+        <v>-4.545959352868287</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.984707211710355</v>
+        <v>2.004015922751977</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.2091780740974798</v>
+        <v>0.2407837058167939</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.948262932671527</v>
+        <v>3.967226311703116</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.575714276430523</v>
+        <v>-4.527442498826467</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.971950799064679</v>
+        <v>1.991259510106302</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.2221082035226881</v>
+        <v>0.2537138352420021</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.935857856064249</v>
+        <v>3.954821235095837</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.550521091929205</v>
+        <v>-4.502249314325149</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.016995009477265</v>
+        <v>2.036303720518887</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.2473013880240064</v>
+        <v>0.2789070197433205</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.985940703377098</v>
+        <v>4.004904082408687</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.538466965016242</v>
+        <v>-4.490195187412186</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.015503228143888</v>
+        <v>2.03481193918551</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.2593555149369692</v>
+        <v>0.2909611466562833</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.986859747426314</v>
+        <v>4.005823126457902</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.5450902117066</v>
+        <v>-4.496818434102544</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.01473455965188</v>
+        <v>2.034043270693503</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.2527322682466109</v>
+        <v>0.284337899965925</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.984766429596235</v>
+        <v>4.003729808627823</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.442209622178007</v>
+        <v>-4.393937844573951</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.0687378213412</v>
+        <v>2.088046532382823</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.3556128577752038</v>
+        <v>0.3872184894945179</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.059345809191273</v>
+        <v>4.078309188222861</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.465651661358094</v>
+        <v>-4.417379883754038</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.07956367584276</v>
+        <v>2.098872386884381</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.3556128577752038</v>
+        <v>0.3872184894945179</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.079548479364867</v>
+        <v>4.098511858396455</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.483724169649705</v>
+        <v>-4.43545239204565</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.072334672526115</v>
+        <v>2.091643383567737</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.3556128577752038</v>
+        <v>0.3872184894945179</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.079548479364867</v>
+        <v>4.098511858396455</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.714897963526337</v>
+        <v>-4.666626185922282</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.940117068568929</v>
+        <v>1.959425779610551</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.3556128577752038</v>
+        <v>0.3872184894945179</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.039800392958334</v>
+        <v>4.058763771989922</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,45 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.487846497586397</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.781119244997337</v>
+        <v>-4.732847467393282</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.920651174977469</v>
+        <v>1.939959886019091</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.2893915763042041</v>
+        <v>0.3209972080235182</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.007090243072674</v>
+        <v>4.026053622104262</v>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" s="2" t="n">
+        <v>45513</v>
+      </c>
+      <c r="B2051" t="n">
+        <v>3.787370342760144</v>
+      </c>
+      <c r="C2051" t="n">
+        <v>3.920651892801788</v>
+      </c>
+      <c r="D2051" t="n">
+        <v>-4.732847467393282</v>
+      </c>
+      <c r="E2051" t="n">
+        <v>1.939959886019091</v>
+      </c>
+      <c r="F2051" t="n">
+        <v>0.3209972080235182</v>
+      </c>
+      <c r="G2051" t="n">
+        <v>3.913715689788156</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240809.xlsx
+++ b/tame_output/ON/bt/strategyON_20240809.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>22.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>125.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.1%</t>
+          <t>419.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-634.9%</t>
+          <t>-646.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-182.2%</t>
+          <t>-186.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>179.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.0%</t>
+          <t>-66.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-191.9%</t>
+          <t>-203.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-54.7%</t>
+          <t>-69.4%</t>
         </is>
       </c>
     </row>
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.629345760543032</v>
+        <v>-2.745161240850168</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.415450128890259</v>
+        <v>2.369123936767405</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.102158436940012</v>
+        <v>0.9869758482487526</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.128839919585227</v>
+        <v>4.059730366370471</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.681619367878674</v>
+        <v>-2.79743484818581</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.397431780501303</v>
+        <v>2.351105588378449</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.049884829604371</v>
+        <v>0.9347022409131114</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.100366849729143</v>
+        <v>4.031257296514387</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.75794934547958</v>
+        <v>-2.873764825786715</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.365011602354716</v>
+        <v>2.318685410231862</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.049884829604371</v>
+        <v>0.9347022409131114</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.098478662622918</v>
+        <v>4.029369109408163</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.960203065803933</v>
+        <v>-3.076018546111069</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.278930343827837</v>
+        <v>2.232604151704983</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8476311092800175</v>
+        <v>0.7324485205887579</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.971946660031168</v>
+        <v>3.902837106816412</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.121771491331188</v>
+        <v>-3.237586971638324</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.212736983827087</v>
+        <v>2.166410791704233</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7208481854821381</v>
+        <v>0.6056655967908785</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.894310915962593</v>
+        <v>3.825201362747837</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.254072783428741</v>
+        <v>-3.369888263735877</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.172889873853984</v>
+        <v>2.12656368173113</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7208481854821381</v>
+        <v>0.6056655967908785</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.907384322828511</v>
+        <v>3.838274769613756</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.439941094267971</v>
+        <v>-3.555756574575107</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.090547746301232</v>
+        <v>2.044221554178378</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5622825921621905</v>
+        <v>0.4471000034709308</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.804250163619483</v>
+        <v>3.735140610404727</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.467841881377444</v>
+        <v>-3.58365736168458</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.077911472584446</v>
+        <v>2.031585280461591</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5276856680192556</v>
+        <v>0.412503079327996</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.782016050260724</v>
+        <v>3.712906497045968</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.590367984080338</v>
+        <v>-3.706183464387474</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.025665475480487</v>
+        <v>1.979339283357632</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4051595653163618</v>
+        <v>0.2899769766251021</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.705264832616186</v>
+        <v>3.63615527940143</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.820882480265927</v>
+        <v>-3.936697960573063</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.000165636596755</v>
+        <v>1.953839444473901</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.174645069130773</v>
+        <v>0.05946248043951341</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.633662094495337</v>
+        <v>3.564552541280581</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.077603298260751</v>
+        <v>-4.193418778567887</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.037789028400672</v>
+        <v>1.991462836277818</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.06623049498695821</v>
+        <v>-0.04895209370430142</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.708925069010895</v>
+        <v>3.639815515796139</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.231589716036892</v>
+        <v>-4.347405196344027</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.045174730435856</v>
+        <v>1.998848538313001</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.06623049498695821</v>
+        <v>-0.04895209370430142</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.777905338156535</v>
+        <v>3.708795784941779</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.181067812209226</v>
+        <v>-4.296883292516362</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.051434694087043</v>
+        <v>2.005108501964189</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.06623049498695821</v>
+        <v>-0.04895209370430142</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.763956540276656</v>
+        <v>3.6948469870619</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.43354296621695</v>
+        <v>-4.549358446524086</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.962315121539367</v>
+        <v>1.915988929416513</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.06623049498695821</v>
+        <v>-0.04895209370430142</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.77582702933207</v>
+        <v>3.706717476117314</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.726438722696362</v>
+        <v>-4.842254203003498</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.846367353466546</v>
+        <v>1.800041161343692</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.06623049498695821</v>
+        <v>-0.04895209370430142</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.777037563851013</v>
+        <v>3.707928010636258</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.883982794425804</v>
+        <v>-4.99979827473294</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.787471467002091</v>
+        <v>1.741145274879237</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.0006713101533162846</v>
+        <v>-0.1158538988445759</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.74101822299417</v>
+        <v>3.671908669779414</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.161947190009077</v>
+        <v>-5.277762670316213</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.671363561504971</v>
+        <v>1.625037369382117</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.09029104443880054</v>
+        <v>-0.2054736331300602</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.682324235159069</v>
+        <v>3.613214681944313</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.278914882647968</v>
+        <v>-5.394730362955104</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.786780541148459</v>
+        <v>1.740454349025604</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.09029104443880054</v>
+        <v>-0.2054736331300602</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.844528291858113</v>
+        <v>3.775418738643357</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.363632824868922</v>
+        <v>-5.479448305176057</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.747740002223892</v>
+        <v>1.701413810101037</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1754070733668469</v>
+        <v>-0.2905896620581065</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.788305312465099</v>
+        <v>3.719195759250344</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.445567643137805</v>
+        <v>-5.561383123444941</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.725195492484829</v>
+        <v>1.678869300361975</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1853418189539271</v>
+        <v>-0.3005244076451867</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.792573882681343</v>
+        <v>3.723464329466587</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.547543765386212</v>
+        <v>-5.663359245693348</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.693330682041369</v>
+        <v>1.647004489918515</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2873179412023347</v>
+        <v>-0.4025005298935943</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.740313847788201</v>
+        <v>3.671204294573445</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.437537481908991</v>
+        <v>-5.553352962216127</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.729486082676433</v>
+        <v>1.683159890553578</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2641133692850595</v>
+        <v>-0.3792959579763191</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.746389478182741</v>
+        <v>3.677279924967985</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.294477906168066</v>
+        <v>-5.410293386475201</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.790959923694777</v>
+        <v>1.744633731571923</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2560999426950802</v>
+        <v>-0.3712825313863398</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.755447544858703</v>
+        <v>3.686337991643947</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.993031180696228</v>
+        <v>-5.108846661003364</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.918799496766048</v>
+        <v>1.872473304643194</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.04534678277675708</v>
+        <v>-0.06983580591450256</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.943576463024341</v>
+        <v>3.874466909809585</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.017621424931412</v>
+        <v>-5.133436905238548</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.909934576824685</v>
+        <v>1.863608384701831</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.04534678277675708</v>
+        <v>-0.06983580591450256</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.944547640777052</v>
+        <v>3.875438087562296</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.966583048924892</v>
+        <v>-5.082398529232028</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.931192831607048</v>
+        <v>1.884866639484194</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.04534678277675708</v>
+        <v>-0.06983580591450256</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.945390545156807</v>
+        <v>3.876280991942051</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.925443754058261</v>
+        <v>-5.041259234365397</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.966686648427846</v>
+        <v>1.920360456304992</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.08648607764338789</v>
+        <v>-0.02869651104787174</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.989112220950931</v>
+        <v>3.920002667736175</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.814837613978659</v>
+        <v>-4.930653094285795</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.827113100583622</v>
+        <v>1.780786908460767</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1970922177229899</v>
+        <v>0.08190962903173027</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.871659901122626</v>
+        <v>3.802550347907871</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.945418348509501</v>
+        <v>-5.061233828816637</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.778382850845248</v>
+        <v>1.732056658722394</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.06651148319214739</v>
+        <v>-0.04867110549911224</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.796813504478085</v>
+        <v>3.727703951263329</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.78092201431854</v>
+        <v>-4.896737494625675</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.828608203597716</v>
+        <v>1.782282011474861</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.06651148319214739</v>
+        <v>-0.04867110549911224</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.781240323554167</v>
+        <v>3.712130770339412</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.808291947002972</v>
+        <v>-4.924107427310108</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.816847940960372</v>
+        <v>1.770521748837518</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.06651148319214739</v>
+        <v>-0.04867110549911224</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.780428033990597</v>
+        <v>3.711318480775841</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.818677141892861</v>
+        <v>-4.934492622199997</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.822562642129489</v>
+        <v>1.776236450006635</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.05612628830225808</v>
+        <v>-0.05905630038900156</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.784065696181736</v>
+        <v>3.71495614296698</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.837265300615086</v>
+        <v>-4.953080780922222</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.885964384417024</v>
+        <v>1.83963819229417</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.03753812958003272</v>
+        <v>-0.07764445911122692</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.843749806724826</v>
+        <v>3.77464025351007</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.837563847311122</v>
+        <v>-4.953379327618258</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.882713976556908</v>
+        <v>1.836387784434054</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.03753812958003272</v>
+        <v>-0.07764445911122692</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.840618817543124</v>
+        <v>3.771509264328369</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.736740713620694</v>
+        <v>-4.85255619392783</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.927574124972471</v>
+        <v>1.881247932849617</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.05000234506438656</v>
+        <v>-0.06518024362687308</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.852628241773128</v>
+        <v>3.783518688558372</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.545959352868287</v>
+        <v>-4.661774833175423</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.004015922751977</v>
+        <v>1.957689730629123</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.2407837058167939</v>
+        <v>0.1256011171255343</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.967226311703116</v>
+        <v>3.89811675848836</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.527442498826467</v>
+        <v>-4.643257979133603</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.991259510106302</v>
+        <v>1.944933317983447</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.2537138352420021</v>
+        <v>0.1385312465507425</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.954821235095837</v>
+        <v>3.885711681881082</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.502249314325149</v>
+        <v>-4.618064794632285</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.036303720518887</v>
+        <v>1.989977528396033</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.2789070197433205</v>
+        <v>0.1637244310520609</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.004904082408687</v>
+        <v>3.935794529193931</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.490195187412186</v>
+        <v>-4.606010667719322</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.03481193918551</v>
+        <v>1.988485747062656</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.2909611466562833</v>
+        <v>0.1757785579650237</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.005823126457902</v>
+        <v>3.936713573243146</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.496818434102544</v>
+        <v>-4.61263391440968</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.034043270693503</v>
+        <v>1.987717078570649</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.284337899965925</v>
+        <v>0.1691553112746653</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.003729808627823</v>
+        <v>3.934620255413067</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.393937844573951</v>
+        <v>-4.509753324881087</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.088046532382823</v>
+        <v>2.041720340259968</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.3872184894945179</v>
+        <v>0.2720359008032582</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.078309188222861</v>
+        <v>4.009199635008105</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.417379883754038</v>
+        <v>-4.533195364061174</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.098872386884381</v>
+        <v>2.052546194761527</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.3872184894945179</v>
+        <v>0.2720359008032582</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.098511858396455</v>
+        <v>4.0294023051817</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.43545239204565</v>
+        <v>-4.551267872352786</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.091643383567737</v>
+        <v>2.045317191444883</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.3872184894945179</v>
+        <v>0.2720359008032582</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.098511858396455</v>
+        <v>4.0294023051817</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.666626185922282</v>
+        <v>-4.782441666229418</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.959425779610551</v>
+        <v>1.913099587487697</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.3872184894945179</v>
+        <v>0.2720359008032582</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.058763771989922</v>
+        <v>3.989654218775166</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.732847467393282</v>
+        <v>-4.848662947700418</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.939959886019091</v>
+        <v>1.893633693896237</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.3209972080235182</v>
+        <v>0.2058146193322585</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.026053622104262</v>
+        <v>3.956944068889507</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.787370342760144</v>
+        <v>3.505945748666329</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.920651892801788</v>
+        <v>3.773222716356545</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.732847467393282</v>
+        <v>-4.848662947700418</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.939959886019091</v>
+        <v>1.893633693896237</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.3209972080235182</v>
+        <v>0.2058146193322585</v>
       </c>
       <c r="G2051" t="n">
-        <v>3.913715689788156</v>
+        <v>3.766286513342913</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240809.xlsx
+++ b/tame_output/ON/bt/strategyON_20240809.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.3%</t>
+          <t>125.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.1%</t>
+          <t>419.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-646.4%</t>
+          <t>-639.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-186.9%</t>
+          <t>-184.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>179.7%</t>
+          <t>-638.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-66.1%</t>
+          <t>-191.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-203.4%</t>
+          <t>-195.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.716749561582301</v>
+        <v>-6.626458215463892</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4669853123369005</v>
+        <v>0.5031018507842644</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4022602419628756</v>
+        <v>-0.3119688958444667</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.912685416105843</v>
+        <v>2.966860223776889</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.46774976289872</v>
+        <v>-6.377458416780311</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5794915730339918</v>
+        <v>0.6156081114813556</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1532604432792949</v>
+        <v>-0.06296909716088606</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.074991636539651</v>
+        <v>3.129166444210696</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.573339752671824</v>
+        <v>-6.483048406553415</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4092796475255316</v>
+        <v>0.445396185972895</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2588504330523992</v>
+        <v>-0.1685590869339904</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.883661713076569</v>
+        <v>2.937836520747615</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.592074654790421</v>
+        <v>-6.501783308672012</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4503300285551788</v>
+        <v>0.4864465670025426</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2644464427125305</v>
+        <v>-0.1741550965941217</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.928848449157577</v>
+        <v>2.983023256828622</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.444134613382822</v>
+        <v>-6.353843267264413</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3896271224300509</v>
+        <v>0.4257436608774148</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.244125526803973</v>
+        <v>-0.1538341806855641</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.821162076014544</v>
+        <v>2.875336883685589</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.391165091128833</v>
+        <v>-6.300873745010424</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4021009450781685</v>
+        <v>0.4382174835255319</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1911560045499841</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.844229803113459</v>
+        <v>2.898404610784504</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.225376895168543</v>
+        <v>-6.135085549050133</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4614556113671915</v>
+        <v>0.4975721498145553</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1911560045499841</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.837269191018366</v>
+        <v>2.891443998689411</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.192013688689774</v>
+        <v>-6.101722342571365</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4892632483398422</v>
+        <v>0.5253797867872056</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1911560045499841</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.851731545399509</v>
+        <v>2.905906353070554</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.083754551567252</v>
+        <v>-5.993463205448843</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.527099023648046</v>
+        <v>0.5632155620954094</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1911560045499841</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.846263665858704</v>
+        <v>2.900438473529749</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.960463416750121</v>
+        <v>-5.870172070631712</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5739135715854751</v>
+        <v>0.6100301100328389</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.06786486973285361</v>
+        <v>0.02242647638555523</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.917736440759559</v>
+        <v>2.971911248430605</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.939314217846678</v>
+        <v>-5.849022871728269</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5900742293841774</v>
+        <v>0.6261907678315413</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.04671567082941025</v>
+        <v>0.04357567528899858</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.93812693833895</v>
+        <v>2.992301746009995</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.695548775863234</v>
+        <v>-5.605257429744825</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6833611145246059</v>
+        <v>0.7194776529719697</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.04671567082941025</v>
+        <v>0.04357567528899858</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.933907646686001</v>
+        <v>2.988082454357046</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.593785955585939</v>
+        <v>-5.50349460946753</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7261905565555398</v>
+        <v>0.7623070950029036</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.03349660243698155</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.943963401641474</v>
+        <v>2.998138209312519</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.343935561636864</v>
+        <v>-5.253644215518455</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8188727891188718</v>
+        <v>0.8549893275662357</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.03349660243698155</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.936705476625176</v>
+        <v>2.990880284296221</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.168043469169431</v>
+        <v>-5.077752123051022</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8928287496264939</v>
+        <v>0.9289452880738573</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.03349660243698155</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.940304600145825</v>
+        <v>2.99447940781687</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.996597006146968</v>
+        <v>-4.906305660028559</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9747348408900329</v>
+        <v>1.010851379337397</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1379498605854816</v>
+        <v>0.2282412067038904</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.056499984013857</v>
+        <v>3.110674791684902</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.922307440408629</v>
+        <v>-4.832016094290219</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.003471144801666</v>
+        <v>1.039587683249029</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2122394263238209</v>
+        <v>0.3025307724422297</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.100094201073157</v>
+        <v>3.154269008744202</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.858671698174694</v>
+        <v>-4.768380352056285</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.033620242749557</v>
+        <v>1.06973678119692</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2758751685577554</v>
+        <v>0.3661665146761642</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.142970447467835</v>
+        <v>3.197145255138881</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.747244938848774</v>
+        <v>-4.656953592730365</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.05938520526372</v>
+        <v>1.095501743711084</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2758751685577554</v>
+        <v>0.3661665146761642</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.124164706251631</v>
+        <v>3.178339513922676</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.757747561914063</v>
+        <v>-4.667456215795654</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.056927232662482</v>
+        <v>1.093043771109846</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2653725454924665</v>
+        <v>0.3556638916108754</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.119606209037335</v>
+        <v>3.17378101670838</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.685504993742868</v>
+        <v>-4.595213647624459</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.08975357376578</v>
+        <v>1.125870112213144</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2653725454924665</v>
+        <v>0.3556638916108754</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.123535522872155</v>
+        <v>3.1777103305432</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879963</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.667791306865003</v>
+        <v>-4.577499960746594</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.097517632434266</v>
+        <v>1.13363417088163</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2685538743893833</v>
+        <v>0.3588452205077922</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.126122904127645</v>
+        <v>3.18029771179869</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.558986421385276</v>
+        <v>-4.468695075266867</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.138037657846151</v>
+        <v>1.174154196293514</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2685538743893833</v>
+        <v>0.3588452205077922</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.123120975347638</v>
+        <v>3.177295783018684</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.338965623348265</v>
+        <v>-4.248674277229856</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.227625014071569</v>
+        <v>1.263741552518933</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4097737194573636</v>
+        <v>0.5000650655757723</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.209431919399041</v>
+        <v>3.263606727070086</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.206097934284988</v>
+        <v>-4.115806588166579</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.296666272498703</v>
+        <v>1.332782810946067</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4097737194573636</v>
+        <v>0.5000650655757723</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.225326102200864</v>
+        <v>3.279500909871909</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.085924850920489</v>
+        <v>-3.99563350480208</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.345881350284805</v>
+        <v>1.381997888732168</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5299468028218626</v>
+        <v>0.6202381489402713</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.298575796659865</v>
+        <v>3.352750604330911</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.950671489590512</v>
+        <v>-3.860380143472103</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.410070797378235</v>
+        <v>1.446187335825599</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6652001641518397</v>
+        <v>0.7554915102702484</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.389815916019292</v>
+        <v>3.443990723690337</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.010546316948204</v>
+        <v>-3.920254970829795</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.372158357836584</v>
+        <v>1.408274896283948</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6053253367941476</v>
+        <v>0.6956166829125563</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.339928511006102</v>
+        <v>3.394103318677147</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.890726086037367</v>
+        <v>-3.800434739918958</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.435375619435128</v>
+        <v>1.471492157882492</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6053253367941476</v>
+        <v>0.6956166829125563</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.355217680240311</v>
+        <v>3.409392487911356</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.893195792499173</v>
+        <v>-3.802904446380764</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.342031936172847</v>
+        <v>1.378148474620211</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6028556303323414</v>
+        <v>0.6931469764507501</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.261380055685668</v>
+        <v>3.315554863356714</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.961565978823183</v>
+        <v>-3.871274632704774</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.233945723128544</v>
+        <v>1.270062261575908</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6121313293685563</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.186207336592699</v>
+        <v>3.240382144263744</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.975354031670229</v>
+        <v>-3.88506268555182</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.218867210621617</v>
+        <v>1.254983749068981</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6121313293685563</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.17664404522459</v>
+        <v>3.230818852895635</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.030874107562819</v>
+        <v>-3.94058276144441</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.333690016956784</v>
+        <v>1.369806555404147</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6121313293685563</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.313674881916793</v>
+        <v>3.367849689587838</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.85539984777035</v>
+        <v>-3.765108501651941</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.408446952865559</v>
+        <v>1.444563491312923</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6121313293685563</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.31824211390858</v>
+        <v>3.372416921579625</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.966336100411598</v>
+        <v>-3.876044754293189</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.339814480570267</v>
+        <v>1.37593101901763</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6121313293685563</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.293984142669787</v>
+        <v>3.348158950340832</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.932672554939316</v>
+        <v>-3.842381208820907</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.281818212160629</v>
+        <v>1.317934750607993</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6457948748408382</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.242720583354606</v>
+        <v>3.296895391025652</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.872819935735593</v>
+        <v>-3.782528589617184</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.315931646274251</v>
+        <v>1.352048184721615</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6457948748408382</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.252892969786739</v>
+        <v>3.307067777457784</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.786576472709216</v>
+        <v>-3.696285126590807</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.345375302058662</v>
+        <v>1.381491840506026</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6457948748408382</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.247839240360599</v>
+        <v>3.302014048031644</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.831883292108196</v>
+        <v>-3.741591945989787</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.319028349743596</v>
+        <v>1.355144888190959</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6049847118316074</v>
+        <v>0.6952760579500161</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.215128917999586</v>
+        <v>3.269303725670631</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.860916396810497</v>
+        <v>-3.770625050692088</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.307966980895777</v>
+        <v>1.34408351934314</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6049847118316074</v>
+        <v>0.6952760579500161</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.215680791032688</v>
+        <v>3.269855598703733</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.768105915359638</v>
+        <v>-3.677814569241229</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.274363865367486</v>
+        <v>1.31048040381485</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6977951932824668</v>
+        <v>0.7880865394008755</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.200639771794569</v>
+        <v>3.254814579465614</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.812495384689066</v>
+        <v>-3.722204038570657</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.258481553560316</v>
+        <v>1.294598092007679</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6534057239530391</v>
+        <v>0.7436970700714478</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.175879566121513</v>
+        <v>3.230054373792558</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.929036989794409</v>
+        <v>-3.838745643675999</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.206940620029902</v>
+        <v>1.243057158477265</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5368641188476964</v>
+        <v>0.6271554649661051</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.10103031157003</v>
+        <v>3.155205119241076</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.816659988611736</v>
+        <v>-3.726368642493327</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.257382716333638</v>
+        <v>1.293499254781002</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5368641188476964</v>
+        <v>0.6271554649661051</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.106521607400698</v>
+        <v>3.160696415071743</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.844440386513089</v>
+        <v>-3.75414904039468</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.257767758941636</v>
+        <v>1.293884297388999</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5090837209463432</v>
+        <v>0.599375067064752</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.101350570428425</v>
+        <v>3.15552537809947</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.962821059243228</v>
+        <v>-3.872529713124818</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.048771209850234</v>
+        <v>1.084887748297597</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.441865868795367</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.899375579138492</v>
+        <v>2.953550386809538</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.071435137686558</v>
+        <v>-3.98114379156815</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.125475239192107</v>
+        <v>1.16159177763947</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.441865868795367</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.019525239857698</v>
+        <v>3.073700047528743</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.036026099438415</v>
+        <v>-3.945734753320007</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.154151880593687</v>
+        <v>1.190268419041051</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.441865868795367</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.034038265960021</v>
+        <v>3.088213073631066</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.997642436880264</v>
+        <v>-3.907351090761856</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.166924786959316</v>
+        <v>1.20304132540668</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4802495313535182</v>
+        <v>0.5705408774719269</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.054487904837281</v>
+        <v>3.108662712508325</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.820526106845098</v>
+        <v>-3.730234760726689</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.234500347818685</v>
+        <v>1.270616886266048</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4802495313535182</v>
+        <v>0.5705408774719269</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.051216933682583</v>
+        <v>3.105391741353627</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.865618351678644</v>
+        <v>-3.775327005560235</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.217146841647179</v>
+        <v>1.253263380094543</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4183534881841284</v>
+        <v>0.5086448343025372</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.014762699542862</v>
+        <v>3.068937507213907</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.686242930439876</v>
+        <v>-3.595951584321467</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.282683985449101</v>
+        <v>1.318800523896464</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5751302463548471</v>
+        <v>0.6654215924732558</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.102615729751707</v>
+        <v>3.156790537422753</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.731257143960482</v>
+        <v>-3.640965797842073</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.245485755372448</v>
+        <v>1.281602293819812</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5447813510402425</v>
+        <v>0.6350726971586512</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.065213847894534</v>
+        <v>3.119388655565579</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.998261654232918</v>
+        <v>-3.907970308114509</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.14437551360242</v>
+        <v>1.180492052049783</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3504183129972939</v>
+        <v>0.4407096591157026</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.954287587407711</v>
+        <v>3.008462395078756</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.099459435670091</v>
+        <v>-4.009168089551681</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.103100322924052</v>
+        <v>1.139216861371416</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2820094994519747</v>
+        <v>0.3723008455703835</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.912446221177021</v>
+        <v>2.966621028848066</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.092948469055778</v>
+        <v>-4.002657122937369</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.103304671124094</v>
+        <v>1.139421209571458</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2820094994519747</v>
+        <v>0.3723008455703835</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.910046182731338</v>
+        <v>2.964220990402382</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.073910341348481</v>
+        <v>-3.983618995230072</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.107444641415258</v>
+        <v>1.143561179862621</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2238258881207802</v>
+        <v>0.3141172342391889</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.871660735140865</v>
+        <v>2.925835542811911</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.105036972499099</v>
+        <v>-4.01474562638069</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.214288390589201</v>
+        <v>1.250404929036564</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2238258881207802</v>
+        <v>0.3141172342391889</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.990955136775056</v>
+        <v>3.045129944446101</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.118903733833017</v>
+        <v>-4.028612387714608</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.209575015041767</v>
+        <v>1.245691553489131</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1859679713869573</v>
+        <v>0.276259317505366</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.969073715720896</v>
+        <v>3.023248523391941</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.074099562293087</v>
+        <v>-3.983808216174678</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.233505214054665</v>
+        <v>1.269621752502029</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1859679713869573</v>
+        <v>0.276259317505366</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.975082246117822</v>
+        <v>3.029257053788867</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.926356592058085</v>
+        <v>-3.836065245939676</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.190552623425865</v>
+        <v>1.226669161873229</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3537753286218404</v>
+        <v>0.4440666747402491</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.973716881735951</v>
+        <v>3.027891689406996</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.010177813332783</v>
+        <v>-3.919886467214374</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.159817756447467</v>
+        <v>1.195934294894831</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3537753286218404</v>
+        <v>0.4440666747402491</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.976510503267432</v>
+        <v>3.030685310938477</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.004025107279999</v>
+        <v>-3.913733761161589</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.162941187260239</v>
+        <v>1.199057725707603</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3599280346746247</v>
+        <v>0.4502193807930334</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.980864475290761</v>
+        <v>3.035039282961806</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.020834405430501</v>
+        <v>-3.930543059312091</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.155297944740149</v>
+        <v>1.191414483187512</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3431187365241231</v>
+        <v>0.4334100826425318</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.96985937314057</v>
+        <v>3.024034180811615</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.958536406654379</v>
+        <v>-3.868245060535969</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.246552698047418</v>
+        <v>1.282669236494782</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3431187365241231</v>
+        <v>0.4334100826425318</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.036194926937391</v>
+        <v>3.090369734608436</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.756746208989221</v>
+        <v>-3.666454862870811</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.129560778827609</v>
+        <v>1.165677317274972</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5411369286932775</v>
+        <v>0.6314282748116862</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.957297843953011</v>
+        <v>3.011472651624056</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.807632921675415</v>
+        <v>-3.717341575557006</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.179496326075306</v>
+        <v>1.21561286452267</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.490250216007083</v>
+        <v>0.5805415621254917</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.997056048663469</v>
+        <v>3.051230856334515</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.721022179025608</v>
+        <v>-3.630730832907199</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.228768359251272</v>
+        <v>1.264884897698636</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5688759472122412</v>
+        <v>0.6591672933306499</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.058859223502608</v>
+        <v>3.113034031173653</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.781231477030893</v>
+        <v>-3.690940130912483</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.20322062087383</v>
+        <v>1.239337159321194</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5086666492069567</v>
+        <v>0.5989579953253654</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.021269625524109</v>
+        <v>3.075444433195154</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.704809430598966</v>
+        <v>-3.614518084480556</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.232281057486529</v>
+        <v>1.268397595933893</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5086666492069567</v>
+        <v>0.5989579953253654</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.019761243564037</v>
+        <v>3.073936051235083</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.660436298960397</v>
+        <v>-3.570144952841988</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.249893177577393</v>
+        <v>1.286009716024757</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5530397808455253</v>
+        <v>0.643331126963934</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.046247989982615</v>
+        <v>3.10042279765366</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.682916649819282</v>
+        <v>-3.592625303700872</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.23529483137243</v>
+        <v>1.271411369819794</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5530397808455253</v>
+        <v>0.643331126963934</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.040641784121205</v>
+        <v>3.094816591792251</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.635260919258227</v>
+        <v>-3.544969573139817</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.260738880624657</v>
+        <v>1.296855419072021</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.600695511406581</v>
+        <v>0.6909868575249897</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.075616979485643</v>
+        <v>3.129791787156689</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.534742760759472</v>
+        <v>-3.444451414641062</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.305838517398883</v>
+        <v>1.341955055846247</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7012136699053355</v>
+        <v>0.7915050160237442</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.140820247959621</v>
+        <v>3.194995055630666</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.518837431327119</v>
+        <v>-3.428546085208709</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.298955321647697</v>
+        <v>1.335071860095061</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6221010091960966</v>
+        <v>0.7123923553145053</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.08010732400995</v>
+        <v>3.134282131680995</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.81683703393277</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.473999029718721</v>
+        <v>-3.383707683600311</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.320988384901684</v>
+        <v>1.357104923349048</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.626644442140966</v>
+        <v>0.7169357882593748</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.0869310863875</v>
+        <v>3.141105894058545</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.49349748596073</v>
+        <v>-3.403206139842319</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.317349942035959</v>
+        <v>1.353466480483323</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5785598008610617</v>
+        <v>0.6688511469794705</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.062241241250635</v>
+        <v>3.116416048921681</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.449294648874829</v>
+        <v>-3.359003302756419</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.340910679398156</v>
+        <v>1.37702721784552</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6227626379469622</v>
+        <v>0.7130539840653709</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.094642546030013</v>
+        <v>3.148817353701058</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.486273676538272</v>
+        <v>-3.395982330419862</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.324529068802027</v>
+        <v>1.360645607249391</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6597365397382927</v>
+        <v>0.7500278858567014</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.115236887574059</v>
+        <v>3.169411695245104</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.327982258999</v>
+        <v>-3.23769091288059</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.439093401000775</v>
+        <v>1.475209939448139</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6597365397382927</v>
+        <v>0.7500278858567014</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.166484652757098</v>
+        <v>3.220659460428144</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.120340255364524</v>
+        <v>-3.030048909246114</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.520590907048819</v>
+        <v>1.556707445496183</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8673785433727689</v>
+        <v>0.9576698894911776</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.289510559532037</v>
+        <v>3.343685367203082</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.069308162641996</v>
+        <v>-2.979016816523586</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.5359519723761</v>
+        <v>1.572068510823464</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9184106360952968</v>
+        <v>1.008701982213706</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.315078043403824</v>
+        <v>3.369252851074869</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.00408398151479</v>
+        <v>-2.91379263539638</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.579229048919687</v>
+        <v>1.615345587367051</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9836348172225025</v>
+        <v>1.073926163340911</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.371399956172852</v>
+        <v>3.425574763843898</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.966656961443656</v>
+        <v>-2.876365615325246</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.590160829247421</v>
+        <v>1.626277367694785</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.988886355251684</v>
+        <v>1.079177701370093</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.370511851289641</v>
+        <v>3.424686658960687</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.986768617478365</v>
+        <v>-2.896477271359954</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.583372959164778</v>
+        <v>1.619489497612142</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9999137002491032</v>
+        <v>1.090205046367512</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.378385050619333</v>
+        <v>3.432559858290379</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.93302380305116</v>
+        <v>-2.84273245693275</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.765428655956871</v>
+        <v>1.801545194404235</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.009977009689565</v>
+        <v>1.100268355807974</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.544980807304821</v>
+        <v>3.599155614975866</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.858241542026147</v>
+        <v>-2.767950195907737</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.915454469584693</v>
+        <v>1.951571008032057</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.084759270714578</v>
+        <v>1.175050616832987</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.709963073137646</v>
+        <v>3.764137880808692</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.832157457762339</v>
+        <v>-2.741866111643929</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.917596079304075</v>
+        <v>1.953712617751439</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.084759270714578</v>
+        <v>1.175050616832987</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.701671049151505</v>
+        <v>3.755845856822551</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.744279544653219</v>
+        <v>-2.653988198534809</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.950940440131503</v>
+        <v>1.987056978578867</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.200684913137929</v>
+        <v>1.290976259256338</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.769419630189295</v>
+        <v>3.823594437860341</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.735387083259935</v>
+        <v>-2.645095737141525</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.972051830415608</v>
+        <v>2.008168368862972</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.200684913137929</v>
+        <v>1.290976259256338</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.786974035916087</v>
+        <v>3.841148843587132</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.903863200229813</v>
+        <v>-2.813571854111403</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.89651643103224</v>
+        <v>1.932632969479605</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.172737077421348</v>
+        <v>1.263028423539757</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.762060381890722</v>
+        <v>3.816235189561767</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.20606367136823</v>
+        <v>-2.11577232524982</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.156905939764735</v>
+        <v>2.1930224782121</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.102389018050938</v>
+        <v>1.192680364169346</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.701121243456337</v>
+        <v>3.755296051127383</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.183342567685077</v>
+        <v>-2.093051221566667</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.156658403734901</v>
+        <v>2.192774942182265</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.102389018050938</v>
+        <v>1.192680364169346</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.691785265953242</v>
+        <v>3.745960073624287</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.31254438097912</v>
+        <v>-2.22225303486071</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.263883804268453</v>
+        <v>2.300000342715817</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9731872047568955</v>
+        <v>1.063478550875304</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.773170303827986</v>
+        <v>3.827345111499031</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.467325387757375</v>
+        <v>-2.377034041638965</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.239049224050798</v>
+        <v>2.275165762498162</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9398195307024193</v>
+        <v>1.030110876820828</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.790227521888947</v>
+        <v>3.844402329559992</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.460270697542202</v>
+        <v>-2.369979351423792</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.238546456126412</v>
+        <v>2.274662994573776</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9468742209175931</v>
+        <v>1.037165567036002</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.791135692007596</v>
+        <v>3.845310499678642</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.433319473215714</v>
+        <v>-2.343028127097304</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.259333099501749</v>
+        <v>2.295449637949113</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9617545669453123</v>
+        <v>1.052045913063721</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.810070053268969</v>
+        <v>3.864244860940015</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.56927248127203</v>
+        <v>-2.47898113515362</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.389055028424182</v>
+        <v>2.425171566871546</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9617545669453123</v>
+        <v>1.052045913063721</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.994173185413929</v>
+        <v>4.048347993084974</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.591680599076902</v>
+        <v>-2.501389252958492</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.372208476205226</v>
+        <v>2.408325014652591</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9617545669453123</v>
+        <v>1.052045913063721</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.986289880316922</v>
+        <v>4.040464687987967</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.619904834654502</v>
+        <v>-2.529613488536092</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.362972781523824</v>
+        <v>2.399089319971188</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9797313193966208</v>
+        <v>1.07002266551503</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.999129931337345</v>
+        <v>4.05330473900839</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.745161240850168</v>
+        <v>-2.677617538147089</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.369123936767405</v>
+        <v>2.396141417848637</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9869758482487526</v>
+        <v>1.070552805220698</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.059730366370471</v>
+        <v>4.109876540553638</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.79743484818581</v>
+        <v>-2.72989114548273</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.351105588378449</v>
+        <v>2.378123069459681</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9347022409131114</v>
+        <v>1.018279197885057</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.031257296514387</v>
+        <v>4.081403470697555</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.873764825786715</v>
+        <v>-2.806221123083636</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.318685410231862</v>
+        <v>2.345702891313094</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9347022409131114</v>
+        <v>1.018279197885057</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.029369109408163</v>
+        <v>4.07951528359133</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.076018546111069</v>
+        <v>-3.008474843407989</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.232604151704983</v>
+        <v>2.259621632786215</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7324485205887579</v>
+        <v>0.8160254775607034</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.902837106816412</v>
+        <v>3.95298328099958</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.237586971638324</v>
+        <v>-3.170043268935244</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.166410791704233</v>
+        <v>2.193428272785465</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6056655967908785</v>
+        <v>0.6892425537628241</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.825201362747837</v>
+        <v>3.875347536931005</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389346</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.369888263735877</v>
+        <v>-3.302344561032798</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.12656368173113</v>
+        <v>2.153581162812362</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6056655967908785</v>
+        <v>0.6892425537628241</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.838274769613756</v>
+        <v>3.888420943796923</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.555756574575107</v>
+        <v>-3.488212871872028</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.044221554178378</v>
+        <v>2.07123903525961</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4471000034709308</v>
+        <v>0.5306769604428764</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.735140610404727</v>
+        <v>3.785286784587894</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.58365736168458</v>
+        <v>-3.516113658981501</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.031585280461591</v>
+        <v>2.058602761542823</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.412503079327996</v>
+        <v>0.4960800362999416</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.712906497045968</v>
+        <v>3.763052671229135</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.706183464387474</v>
+        <v>-3.638639761684395</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.979339283357632</v>
+        <v>2.006356764438864</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2899769766251021</v>
+        <v>0.3735539335970477</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.63615527940143</v>
+        <v>3.686301453584598</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.936697960573063</v>
+        <v>-3.869154257869983</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.953839444473901</v>
+        <v>1.980856925555132</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.05946248043951341</v>
+        <v>0.143039437411459</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.564552541280581</v>
+        <v>3.614698715463748</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.193418778567887</v>
+        <v>-4.125875075864807</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.991462836277818</v>
+        <v>2.01848031735905</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.04895209370430142</v>
+        <v>0.03462486326764413</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.639815515796139</v>
+        <v>3.689961689979307</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.347405196344027</v>
+        <v>-4.279861493640947</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.998848538313001</v>
+        <v>2.025866019394233</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.04895209370430142</v>
+        <v>0.03462486326764413</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.708795784941779</v>
+        <v>3.758941959124947</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.296883292516362</v>
+        <v>-4.229339589813281</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.005108501964189</v>
+        <v>2.032125983045421</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.04895209370430142</v>
+        <v>0.03462486326764413</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.6948469870619</v>
+        <v>3.744993161245068</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.549358446524086</v>
+        <v>-4.481814743821006</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.915988929416513</v>
+        <v>1.943006410497745</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.04895209370430142</v>
+        <v>0.03462486326764413</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.706717476117314</v>
+        <v>3.756863650300482</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.842254203003498</v>
+        <v>-4.774710500300418</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.800041161343692</v>
+        <v>1.827058642424924</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.04895209370430142</v>
+        <v>0.03462486326764413</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.707928010636258</v>
+        <v>3.758074184819425</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.99979827473294</v>
+        <v>-4.932254572029859</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.741145274879237</v>
+        <v>1.768162755960469</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1158538988445759</v>
+        <v>-0.03227694187263036</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.671908669779414</v>
+        <v>3.722054843962582</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.277762670316213</v>
+        <v>-5.210218967613133</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.625037369382117</v>
+        <v>1.652054850463349</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2054736331300602</v>
+        <v>-0.1218966761581146</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.613214681944313</v>
+        <v>3.663360856127481</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.394730362955104</v>
+        <v>-5.327186660252024</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.740454349025604</v>
+        <v>1.767471830106837</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2054736331300602</v>
+        <v>-0.1218966761581146</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.775418738643357</v>
+        <v>3.825564912826525</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.479448305176057</v>
+        <v>-5.411904602472977</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.701413810101037</v>
+        <v>1.728431291182269</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.2905896620581065</v>
+        <v>-0.207012705086161</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.719195759250344</v>
+        <v>3.769341933433511</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.561383123444941</v>
+        <v>-5.49383942074186</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.678869300361975</v>
+        <v>1.705886781443207</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3005244076451867</v>
+        <v>-0.2169474506732412</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.723464329466587</v>
+        <v>3.773610503649754</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.663359245693348</v>
+        <v>-5.595815542990268</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.647004489918515</v>
+        <v>1.674021970999747</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4025005298935943</v>
+        <v>-0.3189235729216487</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.671204294573445</v>
+        <v>3.721350468756612</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.553352962216127</v>
+        <v>-5.485809259513046</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.683159890553578</v>
+        <v>1.710177371634811</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.3792959579763191</v>
+        <v>-0.2957190010043735</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.677279924967985</v>
+        <v>3.727426099151153</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.410293386475201</v>
+        <v>-5.342749683772121</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.744633731571923</v>
+        <v>1.771651212653155</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.3712825313863398</v>
+        <v>-0.2877055744143943</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.686337991643947</v>
+        <v>3.736484165827114</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.108846661003364</v>
+        <v>-5.041302958300284</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.872473304643194</v>
+        <v>1.899490785724426</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.06983580591450256</v>
+        <v>0.013741151057443</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.874466909809585</v>
+        <v>3.924613083992753</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.133436905238548</v>
+        <v>-5.065893202535467</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.863608384701831</v>
+        <v>1.890625865783063</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.06983580591450256</v>
+        <v>0.013741151057443</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.875438087562296</v>
+        <v>3.925584261745463</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.082398529232028</v>
+        <v>-5.014854826528947</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.884866639484194</v>
+        <v>1.911884120565426</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.06983580591450256</v>
+        <v>0.013741151057443</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.876280991942051</v>
+        <v>3.926427166125219</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.041259234365397</v>
+        <v>-4.973715531662316</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.920360456304992</v>
+        <v>1.947377937386224</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.02869651104787174</v>
+        <v>0.05488044592407382</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.920002667736175</v>
+        <v>3.970148841919342</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.930653094285795</v>
+        <v>-4.863109391582714</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.780786908460767</v>
+        <v>1.807804389541999</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.08190962903173027</v>
+        <v>0.1654865860036758</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.802550347907871</v>
+        <v>3.852696522091038</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.061233828816637</v>
+        <v>-4.993690126113557</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.732056658722394</v>
+        <v>1.759074139803626</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.04867110549911224</v>
+        <v>0.03490585147283332</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.727703951263329</v>
+        <v>3.777850125446496</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.896737494625675</v>
+        <v>-4.829193791922595</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.782282011474861</v>
+        <v>1.809299492556093</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.04867110549911224</v>
+        <v>0.03490585147283332</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.712130770339412</v>
+        <v>3.762276944522579</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.924107427310108</v>
+        <v>-4.856563724607027</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.770521748837518</v>
+        <v>1.79753922991875</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.04867110549911224</v>
+        <v>0.03490585147283332</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.711318480775841</v>
+        <v>3.761464654959009</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.934492622199997</v>
+        <v>-4.866948919496917</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.776236450006635</v>
+        <v>1.803253931087867</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.05905630038900156</v>
+        <v>0.024520656582944</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.71495614296698</v>
+        <v>3.765102317150148</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735279</v>
+        <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.953080780922222</v>
+        <v>-4.885537078219142</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.83963819229417</v>
+        <v>1.866655673375402</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.07764445911122692</v>
+        <v>0.005932497860718644</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.77464025351007</v>
+        <v>3.824786427693237</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.953379327618258</v>
+        <v>-4.885835624915178</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.836387784434054</v>
+        <v>1.863405265515286</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.07764445911122692</v>
+        <v>0.005932497860718644</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.771509264328369</v>
+        <v>3.821655438511536</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.85255619392783</v>
+        <v>-4.78501249122475</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.881247932849617</v>
+        <v>1.908265413930849</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.06518024362687308</v>
+        <v>0.01839671334507248</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.783518688558372</v>
+        <v>3.83366486274154</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.661774833175423</v>
+        <v>-4.594231130472343</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.957689730629123</v>
+        <v>1.984707211710355</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.1256011171255343</v>
+        <v>0.2091780740974798</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.89811675848836</v>
+        <v>3.948262932671527</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.643257979133603</v>
+        <v>-4.575714276430523</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.944933317983447</v>
+        <v>1.971950799064679</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.1385312465507425</v>
+        <v>0.2221082035226881</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.885711681881082</v>
+        <v>3.935857856064249</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.618064794632285</v>
+        <v>-4.550521091929205</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.989977528396033</v>
+        <v>2.016995009477265</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.1637244310520609</v>
+        <v>0.2473013880240064</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.935794529193931</v>
+        <v>3.985940703377098</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.606010667719322</v>
+        <v>-4.538466965016242</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.988485747062656</v>
+        <v>2.015503228143888</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.1757785579650237</v>
+        <v>0.2593555149369692</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.936713573243146</v>
+        <v>3.986859747426314</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.61263391440968</v>
+        <v>-4.5450902117066</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.987717078570649</v>
+        <v>2.01473455965188</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.1691553112746653</v>
+        <v>0.2527322682466109</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.934620255413067</v>
+        <v>3.984766429596235</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.509753324881087</v>
+        <v>-4.442209622178007</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.041720340259968</v>
+        <v>2.0687378213412</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.2720359008032582</v>
+        <v>0.3556128577752038</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.009199635008105</v>
+        <v>4.059345809191273</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760311</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.533195364061174</v>
+        <v>-4.465651661358094</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.052546194761527</v>
+        <v>2.07956367584276</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.2720359008032582</v>
+        <v>0.3556128577752038</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.0294023051817</v>
+        <v>4.079548479364867</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781701</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.551267872352786</v>
+        <v>-4.483724169649705</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.045317191444883</v>
+        <v>2.072334672526115</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.2720359008032582</v>
+        <v>0.3556128577752038</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.0294023051817</v>
+        <v>4.079548479364867</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.67006888808283</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.782441666229418</v>
+        <v>-4.714897963526337</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.913099587487697</v>
+        <v>1.940117068568929</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.2720359008032582</v>
+        <v>0.3556128577752038</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.989654218775166</v>
+        <v>4.039800392958334</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943584</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.848662947700418</v>
+        <v>-4.781119244997337</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.893633693896237</v>
+        <v>1.920651174977469</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.2058146193322585</v>
+        <v>0.2893915763042041</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.956944068889507</v>
+        <v>4.007090243072674</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,19 +48718,19 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.505945748666329</v>
+        <v>3.50594574866633</v>
       </c>
       <c r="C2051" t="n">
         <v>3.773222716356545</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.848662947700418</v>
+        <v>-4.781119244997337</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.893633693896237</v>
+        <v>1.920651174977469</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.2058146193322585</v>
+        <v>0.2893915763042041</v>
       </c>
       <c r="G2051" t="n">
         <v>3.766286513342913</v>

--- a/tame_output/ON/bt/strategyON_20240809.xlsx
+++ b/tame_output/ON/bt/strategyON_20240809.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.4%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.2%</t>
+          <t>421.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-639.7%</t>
+          <t>-635.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-184.2%</t>
+          <t>-182.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-638.0%</t>
+          <t>209.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-191.7%</t>
+          <t>-62.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-195.1%</t>
+          <t>-190.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-69.4%</t>
+          <t>-54.0%</t>
         </is>
       </c>
     </row>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.074430410226055</v>
+        <v>-9.156532694792446</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4692903750991206</v>
+        <v>-0.502131288925677</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.614615799644703</v>
+        <v>-1.696718084211095</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.192068733518227</v>
+        <v>2.142807362778393</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.127216565826382</v>
+        <v>-9.209318850392773</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4892890475006952</v>
+        <v>-0.5221299613272512</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.7102912862271</v>
+        <v>-1.792393570793492</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.135779231407345</v>
+        <v>2.08651786066751</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.253253359194671</v>
+        <v>-9.335355643761062</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5370100362188963</v>
+        <v>-0.5698509500454523</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.685039663417358</v>
+        <v>-1.767141947983749</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.153623933722305</v>
+        <v>2.10436256298247</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.19618158729874</v>
+        <v>-9.278283871865131</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.510190991774123</v>
+        <v>-0.5430319056006794</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.685039663417358</v>
+        <v>-1.767141947983749</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.157614269408707</v>
+        <v>2.108352898668871</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.337853429022861</v>
+        <v>-9.419955713589252</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5683349553625128</v>
+        <v>-0.6011758691890692</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.685039663417358</v>
+        <v>-1.767141947983749</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.156139042509965</v>
+        <v>2.10687767177013</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.288262584598026</v>
+        <v>-9.370364869164417</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.533445207427707</v>
+        <v>-0.5662861212542629</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.635448818992524</v>
+        <v>-1.717551103558915</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.200946959329737</v>
+        <v>2.151685588589902</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.13934425012617</v>
+        <v>-9.221446534692561</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4869290072856471</v>
+        <v>-0.5197699211122035</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.604199228257351</v>
+        <v>-1.686301512823742</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.206645580124158</v>
+        <v>2.157384209384323</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.91349909740676</v>
+        <v>-8.995601381973149</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3870118731616743</v>
+        <v>-0.4198527869882303</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.562272552670187</v>
+        <v>-1.644374837236579</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.241380658512665</v>
+        <v>2.19211928777283</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.788920441069168</v>
+        <v>-8.871022725635557</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3360412660705787</v>
+        <v>-0.3688821798971342</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.562272552670187</v>
+        <v>-1.644374837236579</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.242519803068724</v>
+        <v>2.193258432328889</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.841815729113454</v>
+        <v>-8.923918013679843</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3545656071261858</v>
+        <v>-0.3874065209527413</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.557317206581741</v>
+        <v>-1.639419491148133</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.248126784883899</v>
+        <v>2.198865414144064</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.769682553825573</v>
+        <v>-8.851784838391962</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.319978632772397</v>
+        <v>-0.3528195465989525</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.557317206581741</v>
+        <v>-1.639419491148133</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.253860489122536</v>
+        <v>2.204599118382701</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.698316161215926</v>
+        <v>-8.780418445782315</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3011693381224032</v>
+        <v>-0.3340102519489587</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.485950813972093</v>
+        <v>-1.568053098538485</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.286943062294459</v>
+        <v>2.237681691554624</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.604857127230702</v>
+        <v>-8.686959411797091</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2736692058412209</v>
+        <v>-0.3065101196677764</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.485950813972093</v>
+        <v>-1.568053098538485</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.277059580981552</v>
+        <v>2.227798210241716</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.59420394567727</v>
+        <v>-8.676306230243659</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2712424937192219</v>
+        <v>-0.3040834075457775</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.485950813972093</v>
+        <v>-1.568053098538485</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.275225020482178</v>
+        <v>2.225963649742343</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.496296907000779</v>
+        <v>-8.578399191567168</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2323799932220867</v>
+        <v>-0.2652209070486422</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.417965064111537</v>
+        <v>-1.500067348677928</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.315716155425051</v>
+        <v>2.266454784685216</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.472343366024822</v>
+        <v>-8.554445650591211</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2221300706862097</v>
+        <v>-0.2549709845127652</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.394011523135579</v>
+        <v>-1.476113807701971</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.330756786156119</v>
+        <v>2.281495415416284</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.208283427702025</v>
+        <v>-8.290385712268414</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1297664115188431</v>
+        <v>-0.162607325345399</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.129951584812783</v>
+        <v>-1.212053869379174</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.475932432988045</v>
+        <v>2.426671062248209</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.501203804197186</v>
+        <v>-7.583306088763575</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1502784042227914</v>
+        <v>0.1174374903962354</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.129951584812783</v>
+        <v>-1.212053869379174</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.473145399327744</v>
+        <v>2.423884028587909</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.461019505830996</v>
+        <v>-7.543121790397385</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1666957474571089</v>
+        <v>0.1338548336305529</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.089767286446592</v>
+        <v>-1.171869571012984</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.4975996022353</v>
+        <v>2.448338231495465</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.297619634891634</v>
+        <v>-7.379721919458023</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2314225170536108</v>
+        <v>0.1985816032270549</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9263674155072295</v>
+        <v>-1.008469700073621</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.595006346019674</v>
+        <v>2.545744975279839</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.064138412662035</v>
+        <v>-7.146240697228424</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3327394347833024</v>
+        <v>0.2998985209567469</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6928861932776309</v>
+        <v>-0.7749884778440226</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.743019508195286</v>
+        <v>2.69375813745545</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.91447202165452</v>
+        <v>-6.996574306220909</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3897137808733495</v>
+        <v>0.3568728670467936</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.599982702035095</v>
+        <v>-0.6820849866014866</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.795869392627848</v>
+        <v>2.746608021888013</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.782196548023633</v>
+        <v>-6.864298832590022</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.437991457072731</v>
+        <v>0.4051505432461755</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4677072284042083</v>
+        <v>-0.5498095129706</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.870602163553407</v>
+        <v>2.821340792813572</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.626458215463892</v>
+        <v>-6.708560500030281</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5031018507842644</v>
+        <v>0.4702609369577089</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3119688958444667</v>
+        <v>-0.3940711804108584</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.966860223776889</v>
+        <v>2.917598853037054</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.377458416780311</v>
+        <v>-6.4595607013467</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6156081114813556</v>
+        <v>0.5827671976548001</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06296909716088606</v>
+        <v>-0.1450713817272777</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.129166444210696</v>
+        <v>3.079905073470861</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.483048406553415</v>
+        <v>-6.565150691119804</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.445396185972895</v>
+        <v>0.4125552721463395</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1685590869339904</v>
+        <v>-0.2506613715003821</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937836520747615</v>
+        <v>2.888575150007779</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.501783308672012</v>
+        <v>-6.583885593238401</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4864465670025426</v>
+        <v>0.4536056531759871</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1741550965941217</v>
+        <v>-0.2562573811605134</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.983023256828622</v>
+        <v>2.933761886088787</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.353843267264413</v>
+        <v>-6.435945551830802</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4257436608774148</v>
+        <v>0.3929027470508593</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1538341806855641</v>
+        <v>-0.2359364652519558</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.875336883685589</v>
+        <v>2.826075512945754</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.300873745010424</v>
+        <v>-6.382976029576813</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4382174835255319</v>
+        <v>0.4053765696989764</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.182966942997967</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.898404610784504</v>
+        <v>2.849143240044669</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.135085549050133</v>
+        <v>-6.217187833616522</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4975721498145553</v>
+        <v>0.4647312359879994</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.182966942997967</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.891443998689411</v>
+        <v>2.842182627949576</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.101722342571365</v>
+        <v>-6.183824627137754</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5253797867872056</v>
+        <v>0.4925388729606501</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.182966942997967</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.905906353070554</v>
+        <v>2.856644982330719</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.993463205448843</v>
+        <v>-6.075565490015232</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5632155620954094</v>
+        <v>0.5303746482688538</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.182966942997967</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.900438473529749</v>
+        <v>2.851177102789914</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.870172070631712</v>
+        <v>-5.952274355198101</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6100301100328389</v>
+        <v>0.577189196206283</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.02242647638555523</v>
+        <v>-0.05967580818083645</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.971911248430605</v>
+        <v>2.922649877690769</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.849022871728269</v>
+        <v>-5.931125156294658</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6261907678315413</v>
+        <v>0.5933498540049857</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.04357567528899858</v>
+        <v>-0.0385266092773931</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.992301746009995</v>
+        <v>2.943040375270161</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.605257429744825</v>
+        <v>-5.687359714311214</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7194776529719697</v>
+        <v>0.6866367391454142</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.04357567528899858</v>
+        <v>-0.0385266092773931</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.988082454357046</v>
+        <v>2.938821083617211</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.50349460946753</v>
+        <v>-5.585596894033919</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7623070950029036</v>
+        <v>0.7294661811763481</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.0253075408849644</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.998138209312519</v>
+        <v>2.948876838572684</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.253644215518455</v>
+        <v>-5.335746500084844</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8549893275662357</v>
+        <v>0.8221484137396802</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.0253075408849644</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.990880284296221</v>
+        <v>2.941618913556387</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.077752123051022</v>
+        <v>-5.159854407617411</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9289452880738573</v>
+        <v>0.8961043742473018</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.0253075408849644</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.99447940781687</v>
+        <v>2.945218037077035</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.906305660028559</v>
+        <v>-4.988407944594948</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.010851379337397</v>
+        <v>0.978010465510841</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2282412067038904</v>
+        <v>0.1461389221374987</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.110674791684902</v>
+        <v>3.061413420945067</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.832016094290219</v>
+        <v>-4.914118378856609</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.039587683249029</v>
+        <v>1.006746769422474</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3025307724422297</v>
+        <v>0.220428487875838</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.154269008744202</v>
+        <v>3.105007638004367</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.768380352056285</v>
+        <v>-4.850482636622674</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.06973678119692</v>
+        <v>1.036895867370365</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.2840642301097726</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.197145255138881</v>
+        <v>3.147883884399045</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.656953592730365</v>
+        <v>-4.739055877296754</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.095501743711084</v>
+        <v>1.062660829884528</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.2840642301097726</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.178339513922676</v>
+        <v>3.129078143182841</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.667456215795654</v>
+        <v>-4.749558500362043</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.093043771109846</v>
+        <v>1.06020285728329</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.2735616070444837</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.17378101670838</v>
+        <v>3.124519645968545</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.595213647624459</v>
+        <v>-4.677315932190848</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.125870112213144</v>
+        <v>1.093029198386588</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.2735616070444837</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.1777103305432</v>
+        <v>3.128448959803365</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.577499960746594</v>
+        <v>-4.659602245312983</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.13363417088163</v>
+        <v>1.100793257055074</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.2767429359414005</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.18029771179869</v>
+        <v>3.131036341058855</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.468695075266867</v>
+        <v>-4.550797359833256</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.174154196293514</v>
+        <v>1.141313282466959</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.2767429359414005</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.177295783018684</v>
+        <v>3.128034412278849</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.248674277229856</v>
+        <v>-4.330776561796245</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.263741552518933</v>
+        <v>1.230900638692377</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.4179627810093807</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.263606727070086</v>
+        <v>3.214345356330251</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.115806588166579</v>
+        <v>-4.197908872732968</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.332782810946067</v>
+        <v>1.299941897119511</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.4179627810093807</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.279500909871909</v>
+        <v>3.230239539132074</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.99563350480208</v>
+        <v>-4.077735789368469</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.381997888732168</v>
+        <v>1.349156974905613</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6202381489402713</v>
+        <v>0.5381358643738796</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.352750604330911</v>
+        <v>3.303489233591076</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.860380143472103</v>
+        <v>-3.942482428038492</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.446187335825599</v>
+        <v>1.413346421999043</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7554915102702484</v>
+        <v>0.6733892257038567</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.443990723690337</v>
+        <v>3.394729352950502</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.920254970829795</v>
+        <v>-4.002357255396184</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.408274896283948</v>
+        <v>1.375433982457392</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.6135143983461646</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.394103318677147</v>
+        <v>3.344841947937312</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.800434739918958</v>
+        <v>-3.882537024485347</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.471492157882492</v>
+        <v>1.438651244055936</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.6135143983461646</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.409392487911356</v>
+        <v>3.360131117171521</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.802904446380764</v>
+        <v>-3.885006730947153</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.378148474620211</v>
+        <v>1.345307560793655</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6931469764507501</v>
+        <v>0.6110446918843584</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.315554863356714</v>
+        <v>3.266293492616879</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.871274632704774</v>
+        <v>-3.953376917271163</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.270062261575908</v>
+        <v>1.237221347749353</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6203203909205733</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.240382144263744</v>
+        <v>3.191120773523909</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.88506268555182</v>
+        <v>-3.967164970118209</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.254983749068981</v>
+        <v>1.222142835242425</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6203203909205733</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.230818852895635</v>
+        <v>3.1815574821558</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.94058276144441</v>
+        <v>-4.022685046010799</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.369806555404147</v>
+        <v>1.336965641577592</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6203203909205733</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.367849689587838</v>
+        <v>3.318588318848003</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.765108501651941</v>
+        <v>-3.84721078621833</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.444563491312923</v>
+        <v>1.411722577486367</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6203203909205733</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.372416921579625</v>
+        <v>3.323155550839791</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.876044754293189</v>
+        <v>-3.958147038859578</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.37593101901763</v>
+        <v>1.343090105191075</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6203203909205733</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.348158950340832</v>
+        <v>3.298897579600998</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.842381208820907</v>
+        <v>-3.924483493387296</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.317934750607993</v>
+        <v>1.285093836781437</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6539839363928552</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.296895391025652</v>
+        <v>3.247634020285816</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.782528589617184</v>
+        <v>-3.864630874183573</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.352048184721615</v>
+        <v>1.319207270895059</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6539839363928552</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.307067777457784</v>
+        <v>3.257806406717949</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.696285126590807</v>
+        <v>-3.778387411157196</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.381491840506026</v>
+        <v>1.34865092667947</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6539839363928552</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.302014048031644</v>
+        <v>3.252752677291809</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.741591945989787</v>
+        <v>-3.823694230556176</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.355144888190959</v>
+        <v>1.322303974364404</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.6131737733836244</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.269303725670631</v>
+        <v>3.220042354930796</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.770625050692088</v>
+        <v>-3.852727335258477</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.34408351934314</v>
+        <v>1.311242605516585</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.6131737733836244</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.269855598703733</v>
+        <v>3.220594227963898</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.677814569241229</v>
+        <v>-3.759916853807618</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.31048040381485</v>
+        <v>1.277639489988294</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7880865394008755</v>
+        <v>0.7059842548344838</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.254814579465614</v>
+        <v>3.205553208725779</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.722204038570657</v>
+        <v>-3.804306323137046</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.294598092007679</v>
+        <v>1.261757178181124</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7436970700714478</v>
+        <v>0.6615947855050561</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.230054373792558</v>
+        <v>3.180793003052723</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.838745643675999</v>
+        <v>-3.920847928242388</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.243057158477265</v>
+        <v>1.21021624465071</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.5450531803997134</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.155205119241076</v>
+        <v>3.10594374850124</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.726368642493327</v>
+        <v>-3.808470927059716</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.293499254781002</v>
+        <v>1.260658340954446</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.5450531803997134</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.160696415071743</v>
+        <v>3.111435044331908</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.75414904039468</v>
+        <v>-3.836251324961069</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.293884297388999</v>
+        <v>1.261043383562444</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.599375067064752</v>
+        <v>0.5172727824983603</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.15552537809947</v>
+        <v>3.106264007359635</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.872529713124818</v>
+        <v>-3.954631997691207</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.084887748297597</v>
+        <v>1.052046834471042</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.4500549303473841</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.953550386809538</v>
+        <v>2.904289016069703</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.98114379156815</v>
+        <v>-4.063246076134538</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.16159177763947</v>
+        <v>1.128750863812915</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.4500549303473841</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.073700047528743</v>
+        <v>3.024438676788908</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.945734753320007</v>
+        <v>-4.027837037886395</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.190268419041051</v>
+        <v>1.157427505214495</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.4500549303473841</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.088213073631066</v>
+        <v>3.038951702891231</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.907351090761856</v>
+        <v>-3.989453375328244</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.20304132540668</v>
+        <v>1.170200411580124</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.4884385929055353</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.108662712508325</v>
+        <v>3.059401341768491</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.730234760726689</v>
+        <v>-3.812337045293078</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.270616886266048</v>
+        <v>1.237775972439493</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.4884385929055353</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.105391741353627</v>
+        <v>3.056130370613793</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.775327005560235</v>
+        <v>-3.857429290126624</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.253263380094543</v>
+        <v>1.220422466267987</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5086448343025372</v>
+        <v>0.4265425497361455</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.068937507213907</v>
+        <v>3.019676136474072</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.595951584321467</v>
+        <v>-3.678053868887856</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.318800523896464</v>
+        <v>1.285959610069909</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6654215924732558</v>
+        <v>0.5833193079068641</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.156790537422753</v>
+        <v>3.107529166682917</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.640965797842073</v>
+        <v>-3.723068082408462</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.281602293819812</v>
+        <v>1.248761379993256</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6350726971586512</v>
+        <v>0.5529704125922595</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.119388655565579</v>
+        <v>3.070127284825744</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.907970308114509</v>
+        <v>-3.990072592680898</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.180492052049783</v>
+        <v>1.147651138223228</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4407096591157026</v>
+        <v>0.358607374549311</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.008462395078756</v>
+        <v>2.959201024338921</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.009168089551681</v>
+        <v>-4.09127037411807</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.139216861371416</v>
+        <v>1.10637594754486</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.2901985610039918</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.966621028848066</v>
+        <v>2.917359658108231</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.002657122937369</v>
+        <v>-4.084759407503758</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.139421209571458</v>
+        <v>1.106580295744902</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.2901985610039918</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.964220990402382</v>
+        <v>2.914959619662548</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.983618995230072</v>
+        <v>-4.065721279796461</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.143561179862621</v>
+        <v>1.110720266036066</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.2320149496727972</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.925835542811911</v>
+        <v>2.876574172072076</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.01474562638069</v>
+        <v>-4.096847910947079</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.250404929036564</v>
+        <v>1.217564015210009</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.2320149496727972</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.045129944446101</v>
+        <v>2.995868573706266</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.028612387714608</v>
+        <v>-4.110714672280997</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.245691553489131</v>
+        <v>1.212850639662575</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.276259317505366</v>
+        <v>0.1941570329389743</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.023248523391941</v>
+        <v>2.973987152652106</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.983808216174678</v>
+        <v>-4.065910500741067</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.269621752502029</v>
+        <v>1.236780838675473</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.276259317505366</v>
+        <v>0.1941570329389743</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.029257053788867</v>
+        <v>2.979995683049032</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.836065245939676</v>
+        <v>-3.918167530506065</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.226669161873229</v>
+        <v>1.193828248046673</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.3619643901738575</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.027891689406996</v>
+        <v>2.978630318667161</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.919886467214374</v>
+        <v>-4.001988751780763</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.195934294894831</v>
+        <v>1.163093381068275</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.3619643901738575</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.030685310938477</v>
+        <v>2.981423940198642</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.913733761161589</v>
+        <v>-3.995836045727978</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.199057725707603</v>
+        <v>1.166216811881047</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4502193807930334</v>
+        <v>0.3681170962266417</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.035039282961806</v>
+        <v>2.985777912221971</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.930543059312091</v>
+        <v>-4.01264534387848</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.191414483187512</v>
+        <v>1.158573569360957</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.3513077980761401</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.024034180811615</v>
+        <v>2.974772810071781</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.868245060535969</v>
+        <v>-3.950347345102359</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.282669236494782</v>
+        <v>1.249828322668226</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.3513077980761401</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.090369734608436</v>
+        <v>3.041108363868601</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.666454862870811</v>
+        <v>-3.748557147437201</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.165677317274972</v>
+        <v>1.132836403448417</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6314282748116862</v>
+        <v>0.5493259902452945</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.011472651624056</v>
+        <v>2.962211280884221</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.717341575557006</v>
+        <v>-3.799443860123395</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.21561286452267</v>
+        <v>1.182771950696114</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5805415621254917</v>
+        <v>0.4984392775591</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.051230856334515</v>
+        <v>3.001969485594679</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.630730832907199</v>
+        <v>-3.712833117473588</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.264884897698636</v>
+        <v>1.23204398387208</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6591672933306499</v>
+        <v>0.5770650087642583</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.113034031173653</v>
+        <v>3.063772660433818</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.690940130912483</v>
+        <v>-3.773042415478872</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.239337159321194</v>
+        <v>1.206496245494638</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.5168557107589737</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.075444433195154</v>
+        <v>3.026183062455319</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.614518084480556</v>
+        <v>-3.696620369046946</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.268397595933893</v>
+        <v>1.235556682107338</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.5168557107589737</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.073936051235083</v>
+        <v>3.024674680495248</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.570144952841988</v>
+        <v>-3.652247237408377</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.286009716024757</v>
+        <v>1.253168802198201</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.643331126963934</v>
+        <v>0.5612288423975423</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.10042279765366</v>
+        <v>3.051161426913825</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.592625303700872</v>
+        <v>-3.674727588267262</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.271411369819794</v>
+        <v>1.238570455993238</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.643331126963934</v>
+        <v>0.5612288423975423</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.094816591792251</v>
+        <v>3.045555221052416</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.544969573139817</v>
+        <v>-3.627071857706206</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.296855419072021</v>
+        <v>1.264014505245465</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6909868575249897</v>
+        <v>0.608884572958598</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.129791787156689</v>
+        <v>3.080530416416853</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.444451414641062</v>
+        <v>-3.526553699207452</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.341955055846247</v>
+        <v>1.309114142019691</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7915050160237442</v>
+        <v>0.7094027314573526</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.194995055630666</v>
+        <v>3.145733684890831</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.428546085208709</v>
+        <v>-3.510648369775099</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.335071860095061</v>
+        <v>1.302230946268505</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7123923553145053</v>
+        <v>0.6302900707481136</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.134282131680995</v>
+        <v>3.08502076094116</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81683703393277</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.383707683600311</v>
+        <v>-3.465809968166701</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.357104923349048</v>
+        <v>1.324264009522492</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7169357882593748</v>
+        <v>0.6348335036929831</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.141105894058545</v>
+        <v>3.09184452331871</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.403206139842319</v>
+        <v>-3.485308424408709</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.353466480483323</v>
+        <v>1.320625566656767</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6688511469794705</v>
+        <v>0.5867488624130788</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.116416048921681</v>
+        <v>3.067154678181846</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.359003302756419</v>
+        <v>-3.441105587322809</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.37702721784552</v>
+        <v>1.344186304018964</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7130539840653709</v>
+        <v>0.6309516994989792</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.148817353701058</v>
+        <v>3.099555982961223</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.395982330419862</v>
+        <v>-3.478084614986252</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.360645607249391</v>
+        <v>1.327804693422835</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7500278858567014</v>
+        <v>0.6679256012903098</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.169411695245104</v>
+        <v>3.120150324505269</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.23769091288059</v>
+        <v>-3.31979319744698</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.475209939448139</v>
+        <v>1.442369025621583</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7500278858567014</v>
+        <v>0.6679256012903098</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.220659460428144</v>
+        <v>3.171398089688309</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.030048909246114</v>
+        <v>-3.112151193812504</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.556707445496183</v>
+        <v>1.523866531669627</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9576698894911776</v>
+        <v>0.8755676049247859</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.343685367203082</v>
+        <v>3.294423996463247</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.979016816523586</v>
+        <v>-3.061119101089976</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.572068510823464</v>
+        <v>1.539227596996908</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.008701982213706</v>
+        <v>0.9265996976473139</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.369252851074869</v>
+        <v>3.319991480335034</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.91379263539638</v>
+        <v>-2.99589491996277</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.615345587367051</v>
+        <v>1.582504673540495</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.073926163340911</v>
+        <v>0.9918238787745195</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.425574763843898</v>
+        <v>3.376313393104062</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.876365615325246</v>
+        <v>-2.958467899891636</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.626277367694785</v>
+        <v>1.593436453868229</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.079177701370093</v>
+        <v>0.997075416803701</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.424686658960687</v>
+        <v>3.375425288220852</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.896477271359954</v>
+        <v>-2.978579555926344</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.619489497612142</v>
+        <v>1.586648583785586</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.090205046367512</v>
+        <v>1.00810276180112</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.432559858290379</v>
+        <v>3.383298487550544</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.84273245693275</v>
+        <v>-2.92483474149914</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.801545194404235</v>
+        <v>1.768704280577679</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.100268355807974</v>
+        <v>1.018166071241582</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.599155614975866</v>
+        <v>3.549894244236032</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.767950195907737</v>
+        <v>-2.850052480474127</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.951571008032057</v>
+        <v>1.918730094205501</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.175050616832987</v>
+        <v>1.092948332266595</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.764137880808692</v>
+        <v>3.714876510068856</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.741866111643929</v>
+        <v>-2.823968396210319</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.953712617751439</v>
+        <v>1.920871703924883</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.175050616832987</v>
+        <v>1.092948332266595</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.755845856822551</v>
+        <v>3.706584486082715</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.653988198534809</v>
+        <v>-2.736090483101199</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.987056978578867</v>
+        <v>1.954216064752311</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.290976259256338</v>
+        <v>1.208873974689946</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.823594437860341</v>
+        <v>3.774333067120506</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.645095737141525</v>
+        <v>-2.727198021707915</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.008168368862972</v>
+        <v>1.975327455036416</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.290976259256338</v>
+        <v>1.208873974689946</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.841148843587132</v>
+        <v>3.791887472847297</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.813571854111403</v>
+        <v>-2.895674138677793</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.932632969479605</v>
+        <v>1.899792055653049</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.263028423539757</v>
+        <v>1.180926138973365</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.816235189561767</v>
+        <v>3.766973818821933</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.11577232524982</v>
+        <v>-2.19787460981621</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.1930224782121</v>
+        <v>2.160181564385544</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.192680364169346</v>
+        <v>1.110578079602955</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.755296051127383</v>
+        <v>3.706034680387548</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.093051221566667</v>
+        <v>-2.175153506133057</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.192774942182265</v>
+        <v>2.159934028355709</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.192680364169346</v>
+        <v>1.110578079602955</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.745960073624287</v>
+        <v>3.696698702884452</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.22225303486071</v>
+        <v>-2.3043553194271</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.300000342715817</v>
+        <v>2.267159428889261</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.063478550875304</v>
+        <v>0.9813762663089125</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.827345111499031</v>
+        <v>3.778083740759196</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.377034041638965</v>
+        <v>-2.459136326205355</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.275165762498162</v>
+        <v>2.242324848671606</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.030110876820828</v>
+        <v>0.9480085922544363</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.844402329559992</v>
+        <v>3.795140958820157</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.369979351423792</v>
+        <v>-2.452081635990182</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.274662994573776</v>
+        <v>2.24182208074722</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.037165567036002</v>
+        <v>0.9550632824696101</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.845310499678642</v>
+        <v>3.796049128938806</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.343028127097304</v>
+        <v>-2.425130411663694</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.295449637949113</v>
+        <v>2.262608724122557</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.052045913063721</v>
+        <v>0.9699436284973293</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.864244860940015</v>
+        <v>3.814983490200179</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.47898113515362</v>
+        <v>-2.56108341972001</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.425171566871546</v>
+        <v>2.39233065304499</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.052045913063721</v>
+        <v>0.9699436284973293</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.048347993084974</v>
+        <v>3.999086622345139</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.501389252958492</v>
+        <v>-2.583491537524882</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.408325014652591</v>
+        <v>2.375484100826035</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.052045913063721</v>
+        <v>0.9699436284973293</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.040464687987967</v>
+        <v>3.991203317248132</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.529613488536092</v>
+        <v>-2.611715773102482</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.399089319971188</v>
+        <v>2.366248406144632</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.07002266551503</v>
+        <v>0.9879203809486379</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.05330473900839</v>
+        <v>4.004043368268555</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.677617538147089</v>
+        <v>-2.759719822713479</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.396141417848637</v>
+        <v>2.363300504022081</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.070552805220698</v>
+        <v>0.9884505206543066</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.109876540553638</v>
+        <v>4.060615169813803</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.72989114548273</v>
+        <v>-2.81199343004912</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.378123069459681</v>
+        <v>2.345282155633125</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.018279197885057</v>
+        <v>0.9361769133186654</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.081403470697555</v>
+        <v>4.03214209995772</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.806221123083636</v>
+        <v>-2.888323407650026</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.345702891313094</v>
+        <v>2.312861977486538</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.018279197885057</v>
+        <v>0.9361769133186654</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.07951528359133</v>
+        <v>4.030253912851495</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.008474843407989</v>
+        <v>-3.090577127974379</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.259621632786215</v>
+        <v>2.226780718959659</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8160254775607034</v>
+        <v>0.733923192994312</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.95298328099958</v>
+        <v>3.903721910259745</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.170043268935244</v>
+        <v>-3.252145553501634</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.193428272785465</v>
+        <v>2.160587358958909</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6892425537628241</v>
+        <v>0.6071402691964326</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.875347536931005</v>
+        <v>3.826086166191169</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.302344561032798</v>
+        <v>-3.384446845599188</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.153581162812362</v>
+        <v>2.120740248985806</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6892425537628241</v>
+        <v>0.6071402691964326</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.888420943796923</v>
+        <v>3.839159573057088</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.488212871872028</v>
+        <v>-3.570315156438418</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.07123903525961</v>
+        <v>2.038398121433054</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5306769604428764</v>
+        <v>0.4485746758764849</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.785286784587894</v>
+        <v>3.73602541384806</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.516113658981501</v>
+        <v>-3.598215943547891</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.058602761542823</v>
+        <v>2.025761847716267</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4960800362999416</v>
+        <v>0.4139777517335501</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.763052671229135</v>
+        <v>3.713791300489301</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.638639761684395</v>
+        <v>-3.720742046250785</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.006356764438864</v>
+        <v>1.973515850612308</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3735539335970477</v>
+        <v>0.2914516490306562</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.686301453584598</v>
+        <v>3.637040082844763</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.869154257869983</v>
+        <v>-3.951256542436373</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.980856925555132</v>
+        <v>1.948016011728576</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.143039437411459</v>
+        <v>0.06093715284506751</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.614698715463748</v>
+        <v>3.565437344723914</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.125875075864807</v>
+        <v>-4.207977360431197</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.01848031735905</v>
+        <v>1.985639403532494</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.03462486326764413</v>
+        <v>-0.04747742129874732</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.689961689979307</v>
+        <v>3.640700319239472</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.279861493640947</v>
+        <v>-4.361963778207338</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.025866019394233</v>
+        <v>1.993025105567678</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.03462486326764413</v>
+        <v>-0.04747742129874732</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.758941959124947</v>
+        <v>3.709680588385111</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.229339589813281</v>
+        <v>-4.311441874379672</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.032125983045421</v>
+        <v>1.999285069218864</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.03462486326764413</v>
+        <v>-0.04747742129874732</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.744993161245068</v>
+        <v>3.695731790505232</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.481814743821006</v>
+        <v>-4.563917028387396</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.943006410497745</v>
+        <v>1.910165496671189</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.03462486326764413</v>
+        <v>-0.04747742129874732</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.756863650300482</v>
+        <v>3.707602279560646</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.774710500300418</v>
+        <v>-4.856812784866809</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.827058642424924</v>
+        <v>1.794217728598368</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.03462486326764413</v>
+        <v>-0.04747742129874732</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.758074184819425</v>
+        <v>3.70881281407959</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.932254572029859</v>
+        <v>-5.01435685659625</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.768162755960469</v>
+        <v>1.735321842133912</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.03227694187263036</v>
+        <v>-0.1143792264390218</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.722054843962582</v>
+        <v>3.672793473222747</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.210218967613133</v>
+        <v>-5.292321252179524</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.652054850463349</v>
+        <v>1.619213936636792</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.1218966761581146</v>
+        <v>-0.2039989607245061</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.663360856127481</v>
+        <v>3.614099485387646</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.327186660252024</v>
+        <v>-5.409288944818415</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.767471830106837</v>
+        <v>1.73463091628028</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.1218966761581146</v>
+        <v>-0.2039989607245061</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.825564912826525</v>
+        <v>3.77630354208669</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.411904602472977</v>
+        <v>-5.494006887039368</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.728431291182269</v>
+        <v>1.695590377355713</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.207012705086161</v>
+        <v>-0.2891149896525524</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.769341933433511</v>
+        <v>3.720080562693676</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.49383942074186</v>
+        <v>-5.575941705308251</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.705886781443207</v>
+        <v>1.673045867616651</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.2169474506732412</v>
+        <v>-0.2990497352396326</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.773610503649754</v>
+        <v>3.724349132909919</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.595815542990268</v>
+        <v>-5.677917827556659</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.674021970999747</v>
+        <v>1.64118105717319</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.3189235729216487</v>
+        <v>-0.4010258574880402</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.721350468756612</v>
+        <v>3.672089098016777</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.485809259513046</v>
+        <v>-5.567911544079437</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.710177371634811</v>
+        <v>1.677336457808254</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2957190010043735</v>
+        <v>-0.377821285570765</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.727426099151153</v>
+        <v>3.678164728411318</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.342749683772121</v>
+        <v>-5.424851968338512</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.771651212653155</v>
+        <v>1.738810298826599</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2877055744143943</v>
+        <v>-0.3698078589807857</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.736484165827114</v>
+        <v>3.687222795087279</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.041302958300284</v>
+        <v>-5.123405242866674</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.899490785724426</v>
+        <v>1.86664987189787</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.013741151057443</v>
+        <v>-0.06836113350894846</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.924613083992753</v>
+        <v>3.875351713252918</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.065893202535467</v>
+        <v>-5.147995487101858</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.890625865783063</v>
+        <v>1.857784951956507</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.013741151057443</v>
+        <v>-0.06836113350894846</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.925584261745463</v>
+        <v>3.876322891005628</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.014854826528947</v>
+        <v>-5.096957111095338</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.911884120565426</v>
+        <v>1.87904320673887</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.013741151057443</v>
+        <v>-0.06836113350894846</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.926427166125219</v>
+        <v>3.877165795385384</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.973715531662316</v>
+        <v>-5.055817816228707</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.947377937386224</v>
+        <v>1.914537023559668</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.05488044592407382</v>
+        <v>-0.02722183864231764</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.970148841919342</v>
+        <v>3.920887471179507</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.863109391582714</v>
+        <v>-4.945211676149105</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.807804389541999</v>
+        <v>1.774963475715443</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1654865860036758</v>
+        <v>0.08338430143728437</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.852696522091038</v>
+        <v>3.803435151351203</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.993690126113557</v>
+        <v>-5.075792410679948</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.759074139803626</v>
+        <v>1.72623322597707</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.03490585147283332</v>
+        <v>-0.04719643309355814</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.777850125446496</v>
+        <v>3.728588754706661</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.829193791922595</v>
+        <v>-4.911296076488986</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.809299492556093</v>
+        <v>1.776458578729537</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.03490585147283332</v>
+        <v>-0.04719643309355814</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.762276944522579</v>
+        <v>3.713015573782744</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.856563724607027</v>
+        <v>-4.938666009173418</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.79753922991875</v>
+        <v>1.764698316092194</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.03490585147283332</v>
+        <v>-0.04719643309355814</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.761464654959009</v>
+        <v>3.712203284219174</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.866948919496917</v>
+        <v>-4.949051204063307</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.803253931087867</v>
+        <v>1.770413017261311</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.024520656582944</v>
+        <v>-0.05758162798344746</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.765102317150148</v>
+        <v>3.715840946410312</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735281</v>
+        <v>3.834415493735279</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.885537078219142</v>
+        <v>-4.967639362785532</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.866655673375402</v>
+        <v>1.833814759548846</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.005932497860718644</v>
+        <v>-0.07616978670567282</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.824786427693237</v>
+        <v>3.775525056953402</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.885835624915178</v>
+        <v>-4.967937909481568</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.863405265515286</v>
+        <v>1.83056435168873</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.005932497860718644</v>
+        <v>-0.07616978670567282</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.821655438511536</v>
+        <v>3.772394067771701</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.78501249122475</v>
+        <v>-4.867114775791141</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.908265413930849</v>
+        <v>1.875424500104292</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.01839671334507248</v>
+        <v>-0.06370557122131898</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.83366486274154</v>
+        <v>3.784403492001705</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.594231130472343</v>
+        <v>-4.676333415038734</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.984707211710355</v>
+        <v>1.951866297883798</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.2091780740974798</v>
+        <v>0.1270757895310884</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.948262932671527</v>
+        <v>3.899001561931692</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.575714276430523</v>
+        <v>-4.657816560996913</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.971950799064679</v>
+        <v>1.939109885238123</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.2221082035226881</v>
+        <v>0.1400059189562966</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.935857856064249</v>
+        <v>3.886596485324414</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.550521091929205</v>
+        <v>-4.632623376495595</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.016995009477265</v>
+        <v>1.984154095650709</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.2473013880240064</v>
+        <v>0.165199103457615</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.985940703377098</v>
+        <v>3.936679332637263</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.538466965016242</v>
+        <v>-4.620569249582632</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.015503228143888</v>
+        <v>1.982662314317332</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.2593555149369692</v>
+        <v>0.1772532303705778</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.986859747426314</v>
+        <v>3.937598376686479</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.5450902117066</v>
+        <v>-4.627192496272991</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.01473455965188</v>
+        <v>1.981893645825324</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.2527322682466109</v>
+        <v>0.1706299836802194</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.984766429596235</v>
+        <v>3.9355050588564</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.442209622178007</v>
+        <v>-4.524311906744398</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.0687378213412</v>
+        <v>2.035896907514644</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.3556128577752038</v>
+        <v>0.2735105732088123</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.059345809191273</v>
+        <v>4.010084438451438</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.465651661358094</v>
+        <v>-4.547753945924485</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.07956367584276</v>
+        <v>2.046722762016203</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.3556128577752038</v>
+        <v>0.2735105732088123</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.079548479364867</v>
+        <v>4.030287108625032</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781701</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.483724169649705</v>
+        <v>-4.565826454216096</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.072334672526115</v>
+        <v>2.039493758699559</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.3556128577752038</v>
+        <v>0.2735105732088123</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.079548479364867</v>
+        <v>4.030287108625032</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.67006888808283</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.714897963526337</v>
+        <v>-4.797000248092728</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.940117068568929</v>
+        <v>1.907276154742372</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.3556128577752038</v>
+        <v>0.2735105732088123</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.039800392958334</v>
+        <v>3.990539022218499</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943584</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.781119244997337</v>
+        <v>-4.739395451035904</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.920651174977469</v>
+        <v>1.937340692562042</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.2893915763042041</v>
+        <v>0.3311153702656364</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.007090243072674</v>
+        <v>4.032124519449533</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.50594574866633</v>
+        <v>3.833839130484202</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.773222716356545</v>
+        <v>3.926949038727318</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.781119244997337</v>
+        <v>-4.739395451035904</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.920651174977469</v>
+        <v>1.937340692562042</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.2893915763042041</v>
+        <v>0.3311153702656364</v>
       </c>
       <c r="G2051" t="n">
-        <v>3.766286513342913</v>
+        <v>3.920012835713686</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240809.xlsx
+++ b/tame_output/ON/bt/strategyON_20240809.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>50.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>110.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>125.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.2%</t>
+          <t>420.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-635.5%</t>
+          <t>-634.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-182.5%</t>
+          <t>-181.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>209.5%</t>
+          <t>-43.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-62.7%</t>
+          <t>-166.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-190.9%</t>
+          <t>-166.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-54.0%</t>
+          <t>-26.9%</t>
         </is>
       </c>
     </row>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.156532694792446</v>
+        <v>-9.074430410226055</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.502131288925677</v>
+        <v>-0.4692903750991206</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.696718084211095</v>
+        <v>-1.614615799644703</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.142807362778393</v>
+        <v>2.192068733518227</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.209318850392773</v>
+        <v>-9.127216565826382</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5221299613272512</v>
+        <v>-0.4892890475006952</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.792393570793492</v>
+        <v>-1.7102912862271</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.08651786066751</v>
+        <v>2.135779231407345</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.335355643761062</v>
+        <v>-9.253253359194671</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5698509500454523</v>
+        <v>-0.5370100362188963</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.767141947983749</v>
+        <v>-1.685039663417358</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.10436256298247</v>
+        <v>2.153623933722305</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.278283871865131</v>
+        <v>-9.19618158729874</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5430319056006794</v>
+        <v>-0.510190991774123</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.767141947983749</v>
+        <v>-1.685039663417358</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.108352898668871</v>
+        <v>2.157614269408707</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.419955713589252</v>
+        <v>-9.337853429022861</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6011758691890692</v>
+        <v>-0.5683349553625128</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.767141947983749</v>
+        <v>-1.685039663417358</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.10687767177013</v>
+        <v>2.156139042509965</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.370364869164417</v>
+        <v>-9.288262584598026</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5662861212542629</v>
+        <v>-0.533445207427707</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.717551103558915</v>
+        <v>-1.635448818992524</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.151685588589902</v>
+        <v>2.200946959329737</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.221446534692561</v>
+        <v>-9.13934425012617</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5197699211122035</v>
+        <v>-0.4869290072856471</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.686301512823742</v>
+        <v>-1.604199228257351</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.157384209384323</v>
+        <v>2.206645580124158</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.995601381973149</v>
+        <v>-8.91349909740676</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4198527869882303</v>
+        <v>-0.3870118731616743</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.644374837236579</v>
+        <v>-1.562272552670187</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.19211928777283</v>
+        <v>2.241380658512665</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.871022725635557</v>
+        <v>-8.788920441069168</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3688821798971342</v>
+        <v>-0.3360412660705787</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.644374837236579</v>
+        <v>-1.562272552670187</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.193258432328889</v>
+        <v>2.242519803068724</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.923918013679843</v>
+        <v>-8.841815729113454</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3874065209527413</v>
+        <v>-0.3545656071261858</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.639419491148133</v>
+        <v>-1.557317206581741</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.198865414144064</v>
+        <v>2.248126784883899</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.851784838391962</v>
+        <v>-8.769682553825573</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3528195465989525</v>
+        <v>-0.319978632772397</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.639419491148133</v>
+        <v>-1.557317206581741</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.204599118382701</v>
+        <v>2.253860489122536</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.780418445782315</v>
+        <v>-8.698316161215926</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3340102519489587</v>
+        <v>-0.3011693381224032</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.568053098538485</v>
+        <v>-1.485950813972093</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.237681691554624</v>
+        <v>2.286943062294459</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.686959411797091</v>
+        <v>-8.604857127230702</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3065101196677764</v>
+        <v>-0.2736692058412209</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.568053098538485</v>
+        <v>-1.485950813972093</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.227798210241716</v>
+        <v>2.277059580981552</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.676306230243659</v>
+        <v>-8.59420394567727</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3040834075457775</v>
+        <v>-0.2712424937192219</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.568053098538485</v>
+        <v>-1.485950813972093</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.225963649742343</v>
+        <v>2.275225020482178</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.578399191567168</v>
+        <v>-8.496296907000779</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2652209070486422</v>
+        <v>-0.2323799932220867</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.500067348677928</v>
+        <v>-1.417965064111537</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.266454784685216</v>
+        <v>2.315716155425051</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.554445650591211</v>
+        <v>-8.472343366024822</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2549709845127652</v>
+        <v>-0.2221300706862097</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.476113807701971</v>
+        <v>-1.394011523135579</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.281495415416284</v>
+        <v>2.330756786156119</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.290385712268414</v>
+        <v>-8.208283427702025</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.162607325345399</v>
+        <v>-0.1297664115188431</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.212053869379174</v>
+        <v>-1.129951584812783</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.426671062248209</v>
+        <v>2.475932432988045</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.583306088763575</v>
+        <v>-7.501203804197186</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1174374903962354</v>
+        <v>0.1502784042227914</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.212053869379174</v>
+        <v>-1.129951584812783</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.423884028587909</v>
+        <v>2.473145399327744</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.543121790397385</v>
+        <v>-7.461019505830996</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1338548336305529</v>
+        <v>0.1666957474571089</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.171869571012984</v>
+        <v>-1.089767286446592</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.448338231495465</v>
+        <v>2.4975996022353</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.379721919458023</v>
+        <v>-7.297619634891634</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1985816032270549</v>
+        <v>0.2314225170536108</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.008469700073621</v>
+        <v>-0.9263674155072295</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.545744975279839</v>
+        <v>2.595006346019674</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.146240697228424</v>
+        <v>-7.064138412662035</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2998985209567469</v>
+        <v>0.3327394347833024</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7749884778440226</v>
+        <v>-0.6928861932776309</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.69375813745545</v>
+        <v>2.743019508195286</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.996574306220909</v>
+        <v>-6.91447202165452</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3568728670467936</v>
+        <v>0.3897137808733495</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6820849866014866</v>
+        <v>-0.599982702035095</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.746608021888013</v>
+        <v>2.795869392627848</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.864298832590022</v>
+        <v>-6.782196548023633</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4051505432461755</v>
+        <v>0.437991457072731</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5498095129706</v>
+        <v>-0.4677072284042083</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.821340792813572</v>
+        <v>2.870602163553407</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.708560500030281</v>
+        <v>-6.626458215463892</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4702609369577089</v>
+        <v>0.5031018507842644</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3940711804108584</v>
+        <v>-0.3119688958444667</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.917598853037054</v>
+        <v>2.966860223776889</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.4595607013467</v>
+        <v>-6.377458416780311</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5827671976548001</v>
+        <v>0.6156081114813556</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1450713817272777</v>
+        <v>-0.06296909716088606</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.079905073470861</v>
+        <v>3.129166444210696</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.565150691119804</v>
+        <v>-6.483048406553415</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4125552721463395</v>
+        <v>0.445396185972895</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2506613715003821</v>
+        <v>-0.1685590869339904</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.888575150007779</v>
+        <v>2.937836520747615</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.583885593238401</v>
+        <v>-6.501783308672012</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4536056531759871</v>
+        <v>0.4864465670025426</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2562573811605134</v>
+        <v>-0.1741550965941217</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.933761886088787</v>
+        <v>2.983023256828622</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.435945551830802</v>
+        <v>-6.353843267264413</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3929027470508593</v>
+        <v>0.4257436608774148</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2359364652519558</v>
+        <v>-0.1538341806855641</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.826075512945754</v>
+        <v>2.875336883685589</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.382976029576813</v>
+        <v>-6.300873745010424</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4053765696989764</v>
+        <v>0.4382174835255319</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.182966942997967</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.849143240044669</v>
+        <v>2.898404610784504</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.217187833616522</v>
+        <v>-6.135085549050133</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4647312359879994</v>
+        <v>0.4975721498145553</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.182966942997967</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.842182627949576</v>
+        <v>2.891443998689411</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.183824627137754</v>
+        <v>-6.101722342571365</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4925388729606501</v>
+        <v>0.5253797867872056</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.182966942997967</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.856644982330719</v>
+        <v>2.905906353070554</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.075565490015232</v>
+        <v>-5.993463205448843</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5303746482688538</v>
+        <v>0.5632155620954094</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.182966942997967</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.851177102789914</v>
+        <v>2.900438473529749</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.952274355198101</v>
+        <v>-5.870172070631712</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.577189196206283</v>
+        <v>0.6100301100328389</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.05967580818083645</v>
+        <v>0.02242647638555523</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.922649877690769</v>
+        <v>2.971911248430605</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.931125156294658</v>
+        <v>-5.849022871728269</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5933498540049857</v>
+        <v>0.6261907678315413</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.0385266092773931</v>
+        <v>0.04357567528899858</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.943040375270161</v>
+        <v>2.992301746009995</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.687359714311214</v>
+        <v>-5.605257429744825</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6866367391454142</v>
+        <v>0.7194776529719697</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.0385266092773931</v>
+        <v>0.04357567528899858</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.938821083617211</v>
+        <v>2.988082454357046</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.585596894033919</v>
+        <v>-5.50349460946753</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7294661811763481</v>
+        <v>0.7623070950029036</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.0253075408849644</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.948876838572684</v>
+        <v>2.998138209312519</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.335746500084844</v>
+        <v>-5.253644215518455</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8221484137396802</v>
+        <v>0.8549893275662357</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.0253075408849644</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.941618913556387</v>
+        <v>2.990880284296221</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.159854407617411</v>
+        <v>-5.077752123051022</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8961043742473018</v>
+        <v>0.9289452880738573</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.0253075408849644</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.945218037077035</v>
+        <v>2.99447940781687</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.988407944594948</v>
+        <v>-4.906305660028559</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.978010465510841</v>
+        <v>1.010851379337397</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1461389221374987</v>
+        <v>0.2282412067038904</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.061413420945067</v>
+        <v>3.110674791684902</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.914118378856609</v>
+        <v>-4.832016094290219</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.006746769422474</v>
+        <v>1.039587683249029</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.220428487875838</v>
+        <v>0.3025307724422297</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.105007638004367</v>
+        <v>3.154269008744202</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.850482636622674</v>
+        <v>-4.768380352056285</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.036895867370365</v>
+        <v>1.06973678119692</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2840642301097726</v>
+        <v>0.3661665146761642</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.147883884399045</v>
+        <v>3.197145255138881</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.739055877296754</v>
+        <v>-4.656953592730365</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.062660829884528</v>
+        <v>1.095501743711084</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2840642301097726</v>
+        <v>0.3661665146761642</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.129078143182841</v>
+        <v>3.178339513922676</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.749558500362043</v>
+        <v>-4.667456215795654</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.06020285728329</v>
+        <v>1.093043771109846</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2735616070444837</v>
+        <v>0.3556638916108754</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.124519645968545</v>
+        <v>3.17378101670838</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.677315932190848</v>
+        <v>-4.595213647624459</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.093029198386588</v>
+        <v>1.125870112213144</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2735616070444837</v>
+        <v>0.3556638916108754</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.128448959803365</v>
+        <v>3.1777103305432</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879963</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.659602245312983</v>
+        <v>-4.577499960746594</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.100793257055074</v>
+        <v>1.13363417088163</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2767429359414005</v>
+        <v>0.3588452205077922</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.131036341058855</v>
+        <v>3.18029771179869</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.550797359833256</v>
+        <v>-4.468695075266867</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.141313282466959</v>
+        <v>1.174154196293514</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2767429359414005</v>
+        <v>0.3588452205077922</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.128034412278849</v>
+        <v>3.177295783018684</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.330776561796245</v>
+        <v>-4.248674277229856</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.230900638692377</v>
+        <v>1.263741552518933</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4179627810093807</v>
+        <v>0.5000650655757723</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.214345356330251</v>
+        <v>3.263606727070086</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.197908872732968</v>
+        <v>-4.115806588166579</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.299941897119511</v>
+        <v>1.332782810946067</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4179627810093807</v>
+        <v>0.5000650655757723</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.230239539132074</v>
+        <v>3.279500909871909</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.077735789368469</v>
+        <v>-3.99563350480208</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.349156974905613</v>
+        <v>1.381997888732168</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5381358643738796</v>
+        <v>0.6202381489402713</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.303489233591076</v>
+        <v>3.352750604330911</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.942482428038492</v>
+        <v>-3.860380143472103</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.413346421999043</v>
+        <v>1.446187335825599</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6733892257038567</v>
+        <v>0.7554915102702484</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.394729352950502</v>
+        <v>3.443990723690337</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.002357255396184</v>
+        <v>-3.920254970829795</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.375433982457392</v>
+        <v>1.408274896283948</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6135143983461646</v>
+        <v>0.6956166829125563</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.344841947937312</v>
+        <v>3.394103318677147</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.882537024485347</v>
+        <v>-3.800434739918958</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.438651244055936</v>
+        <v>1.471492157882492</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6135143983461646</v>
+        <v>0.6956166829125563</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.360131117171521</v>
+        <v>3.409392487911356</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.885006730947153</v>
+        <v>-3.802904446380764</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.345307560793655</v>
+        <v>1.378148474620211</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6110446918843584</v>
+        <v>0.6931469764507501</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.266293492616879</v>
+        <v>3.315554863356714</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.953376917271163</v>
+        <v>-3.871274632704774</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.237221347749353</v>
+        <v>1.270062261575908</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6203203909205733</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.191120773523909</v>
+        <v>3.240382144263744</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.967164970118209</v>
+        <v>-3.88506268555182</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.222142835242425</v>
+        <v>1.254983749068981</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6203203909205733</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.1815574821558</v>
+        <v>3.230818852895635</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.022685046010799</v>
+        <v>-3.94058276144441</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.336965641577592</v>
+        <v>1.369806555404147</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6203203909205733</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.318588318848003</v>
+        <v>3.367849689587838</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.84721078621833</v>
+        <v>-3.765108501651941</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.411722577486367</v>
+        <v>1.444563491312923</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6203203909205733</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.323155550839791</v>
+        <v>3.372416921579625</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.958147038859578</v>
+        <v>-3.876044754293189</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.343090105191075</v>
+        <v>1.37593101901763</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6203203909205733</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.298897579600998</v>
+        <v>3.348158950340832</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.924483493387296</v>
+        <v>-3.842381208820907</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.285093836781437</v>
+        <v>1.317934750607993</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6539839363928552</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.247634020285816</v>
+        <v>3.296895391025652</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.864630874183573</v>
+        <v>-3.782528589617184</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.319207270895059</v>
+        <v>1.352048184721615</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6539839363928552</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.257806406717949</v>
+        <v>3.307067777457784</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.778387411157196</v>
+        <v>-3.696285126590807</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.34865092667947</v>
+        <v>1.381491840506026</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6539839363928552</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.252752677291809</v>
+        <v>3.302014048031644</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.823694230556176</v>
+        <v>-3.741591945989787</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.322303974364404</v>
+        <v>1.355144888190959</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6131737733836244</v>
+        <v>0.6952760579500161</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.220042354930796</v>
+        <v>3.269303725670631</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.852727335258477</v>
+        <v>-3.770625050692088</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.311242605516585</v>
+        <v>1.34408351934314</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6131737733836244</v>
+        <v>0.6952760579500161</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.220594227963898</v>
+        <v>3.269855598703733</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.759916853807618</v>
+        <v>-3.677814569241229</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.277639489988294</v>
+        <v>1.31048040381485</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7059842548344838</v>
+        <v>0.7880865394008755</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.205553208725779</v>
+        <v>3.254814579465614</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.804306323137046</v>
+        <v>-3.722204038570657</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.261757178181124</v>
+        <v>1.294598092007679</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6615947855050561</v>
+        <v>0.7436970700714478</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.180793003052723</v>
+        <v>3.230054373792558</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.920847928242388</v>
+        <v>-3.838745643675999</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.21021624465071</v>
+        <v>1.243057158477265</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5450531803997134</v>
+        <v>0.6271554649661051</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.10594374850124</v>
+        <v>3.155205119241076</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.808470927059716</v>
+        <v>-3.726368642493327</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.260658340954446</v>
+        <v>1.293499254781002</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5450531803997134</v>
+        <v>0.6271554649661051</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.111435044331908</v>
+        <v>3.160696415071743</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.836251324961069</v>
+        <v>-3.75414904039468</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.261043383562444</v>
+        <v>1.293884297388999</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5172727824983603</v>
+        <v>0.599375067064752</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.106264007359635</v>
+        <v>3.15552537809947</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.954631997691207</v>
+        <v>-3.872529713124818</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.052046834471042</v>
+        <v>1.084887748297597</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4500549303473841</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.904289016069703</v>
+        <v>2.953550386809538</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.063246076134538</v>
+        <v>-3.98114379156815</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.128750863812915</v>
+        <v>1.16159177763947</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4500549303473841</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.024438676788908</v>
+        <v>3.073700047528743</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.027837037886395</v>
+        <v>-3.945734753320007</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.157427505214495</v>
+        <v>1.190268419041051</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4500549303473841</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.038951702891231</v>
+        <v>3.088213073631066</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.989453375328244</v>
+        <v>-3.907351090761856</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.170200411580124</v>
+        <v>1.20304132540668</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4884385929055353</v>
+        <v>0.5705408774719269</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.059401341768491</v>
+        <v>3.108662712508325</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.812337045293078</v>
+        <v>-3.730234760726689</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.237775972439493</v>
+        <v>1.270616886266048</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4884385929055353</v>
+        <v>0.5705408774719269</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.056130370613793</v>
+        <v>3.105391741353627</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.857429290126624</v>
+        <v>-3.775327005560235</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.220422466267987</v>
+        <v>1.253263380094543</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4265425497361455</v>
+        <v>0.5086448343025372</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.019676136474072</v>
+        <v>3.068937507213907</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.678053868887856</v>
+        <v>-3.595951584321467</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.285959610069909</v>
+        <v>1.318800523896464</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5833193079068641</v>
+        <v>0.6654215924732558</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.107529166682917</v>
+        <v>3.156790537422753</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.723068082408462</v>
+        <v>-3.640965797842073</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.248761379993256</v>
+        <v>1.281602293819812</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5529704125922595</v>
+        <v>0.6350726971586512</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.070127284825744</v>
+        <v>3.119388655565579</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.990072592680898</v>
+        <v>-3.907970308114509</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.147651138223228</v>
+        <v>1.180492052049783</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.358607374549311</v>
+        <v>0.4407096591157026</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.959201024338921</v>
+        <v>3.008462395078756</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.09127037411807</v>
+        <v>-4.009168089551681</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.10637594754486</v>
+        <v>1.139216861371416</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2901985610039918</v>
+        <v>0.3723008455703835</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.917359658108231</v>
+        <v>2.966621028848066</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.084759407503758</v>
+        <v>-4.002657122937369</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.106580295744902</v>
+        <v>1.139421209571458</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2901985610039918</v>
+        <v>0.3723008455703835</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.914959619662548</v>
+        <v>2.964220990402382</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.065721279796461</v>
+        <v>-3.983618995230072</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.110720266036066</v>
+        <v>1.143561179862621</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2320149496727972</v>
+        <v>0.3141172342391889</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.876574172072076</v>
+        <v>2.925835542811911</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.096847910947079</v>
+        <v>-4.01474562638069</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.217564015210009</v>
+        <v>1.250404929036564</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2320149496727972</v>
+        <v>0.3141172342391889</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.995868573706266</v>
+        <v>3.045129944446101</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.110714672280997</v>
+        <v>-4.028612387714608</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.212850639662575</v>
+        <v>1.245691553489131</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1941570329389743</v>
+        <v>0.276259317505366</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.973987152652106</v>
+        <v>3.023248523391941</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.065910500741067</v>
+        <v>-3.983808216174678</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.236780838675473</v>
+        <v>1.269621752502029</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1941570329389743</v>
+        <v>0.276259317505366</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.979995683049032</v>
+        <v>3.029257053788867</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.918167530506065</v>
+        <v>-3.836065245939676</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.193828248046673</v>
+        <v>1.226669161873229</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3619643901738575</v>
+        <v>0.4440666747402491</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.978630318667161</v>
+        <v>3.027891689406996</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.001988751780763</v>
+        <v>-3.919886467214374</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.163093381068275</v>
+        <v>1.195934294894831</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3619643901738575</v>
+        <v>0.4440666747402491</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.981423940198642</v>
+        <v>3.030685310938477</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.995836045727978</v>
+        <v>-3.913733761161589</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.166216811881047</v>
+        <v>1.199057725707603</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3681170962266417</v>
+        <v>0.4502193807930334</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.985777912221971</v>
+        <v>3.035039282961806</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.01264534387848</v>
+        <v>-3.930543059312091</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.158573569360957</v>
+        <v>1.191414483187512</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3513077980761401</v>
+        <v>0.4334100826425318</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.974772810071781</v>
+        <v>3.024034180811615</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.950347345102359</v>
+        <v>-3.868245060535969</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.249828322668226</v>
+        <v>1.282669236494782</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3513077980761401</v>
+        <v>0.4334100826425318</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.041108363868601</v>
+        <v>3.090369734608436</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.748557147437201</v>
+        <v>-3.666454862870811</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.132836403448417</v>
+        <v>1.165677317274972</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5493259902452945</v>
+        <v>0.6314282748116862</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.962211280884221</v>
+        <v>3.011472651624056</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.799443860123395</v>
+        <v>-3.717341575557006</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.182771950696114</v>
+        <v>1.21561286452267</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4984392775591</v>
+        <v>0.5805415621254917</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.001969485594679</v>
+        <v>3.051230856334515</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.712833117473588</v>
+        <v>-3.630730832907199</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.23204398387208</v>
+        <v>1.264884897698636</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5770650087642583</v>
+        <v>0.6591672933306499</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.063772660433818</v>
+        <v>3.113034031173653</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.773042415478872</v>
+        <v>-3.690940130912483</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.206496245494638</v>
+        <v>1.239337159321194</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5168557107589737</v>
+        <v>0.5989579953253654</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.026183062455319</v>
+        <v>3.075444433195154</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.696620369046946</v>
+        <v>-3.614518084480556</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.235556682107338</v>
+        <v>1.268397595933893</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5168557107589737</v>
+        <v>0.5989579953253654</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.024674680495248</v>
+        <v>3.073936051235083</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.652247237408377</v>
+        <v>-3.570144952841988</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.253168802198201</v>
+        <v>1.286009716024757</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5612288423975423</v>
+        <v>0.643331126963934</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.051161426913825</v>
+        <v>3.10042279765366</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.674727588267262</v>
+        <v>-3.592625303700872</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.238570455993238</v>
+        <v>1.271411369819794</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5612288423975423</v>
+        <v>0.643331126963934</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.045555221052416</v>
+        <v>3.094816591792251</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.627071857706206</v>
+        <v>-3.544969573139817</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.264014505245465</v>
+        <v>1.296855419072021</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.608884572958598</v>
+        <v>0.6909868575249897</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.080530416416853</v>
+        <v>3.129791787156689</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.526553699207452</v>
+        <v>-3.444451414641062</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.309114142019691</v>
+        <v>1.341955055846247</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7094027314573526</v>
+        <v>0.7915050160237442</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.145733684890831</v>
+        <v>3.194995055630666</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.510648369775099</v>
+        <v>-3.428546085208709</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.302230946268505</v>
+        <v>1.335071860095061</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6302900707481136</v>
+        <v>0.7123923553145053</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.08502076094116</v>
+        <v>3.134282131680995</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.81683703393277</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.465809968166701</v>
+        <v>-3.480360442297912</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.324264009522492</v>
+        <v>1.318443819870008</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6348335036929831</v>
+        <v>0.755938150818757</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.09184452331871</v>
+        <v>3.164507311594174</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.485308424408709</v>
+        <v>-3.49985889853992</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.320625566656767</v>
+        <v>1.314805377004283</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5867488624130788</v>
+        <v>0.7078535095388527</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.067154678181846</v>
+        <v>3.13981746645731</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.441105587322809</v>
+        <v>-3.45565606145402</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.344186304018964</v>
+        <v>1.33836611436648</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6309516994989792</v>
+        <v>0.7520563466247532</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.099555982961223</v>
+        <v>3.172218771236687</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.478084614986252</v>
+        <v>-3.492635089117463</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.327804693422835</v>
+        <v>1.32198450377035</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6679256012903098</v>
+        <v>0.7890302484160837</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.120150324505269</v>
+        <v>3.192813112780733</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.31979319744698</v>
+        <v>-3.334343671578191</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.442369025621583</v>
+        <v>1.436548835969099</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6679256012903098</v>
+        <v>0.7890302484160837</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.171398089688309</v>
+        <v>3.244060877963773</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.112151193812504</v>
+        <v>-3.126701667943715</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.523866531669627</v>
+        <v>1.518046342017142</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8755676049247859</v>
+        <v>0.9966722520505598</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.294423996463247</v>
+        <v>3.367086784738712</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.061119101089976</v>
+        <v>-3.075669575221187</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.539227596996908</v>
+        <v>1.533407407344424</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9265996976473139</v>
+        <v>1.047704344773088</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.319991480335034</v>
+        <v>3.392654268610499</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.99589491996277</v>
+        <v>-3.010445394093981</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.582504673540495</v>
+        <v>1.576684483888011</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9918238787745195</v>
+        <v>1.112928525900293</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.376313393104062</v>
+        <v>3.448976181379527</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.958467899891636</v>
+        <v>-2.973018374022848</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.593436453868229</v>
+        <v>1.587616264215745</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.997075416803701</v>
+        <v>1.118180063929475</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.375425288220852</v>
+        <v>3.448088076496316</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.978579555926344</v>
+        <v>-2.993130030057556</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.586648583785586</v>
+        <v>1.580828394133102</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.00810276180112</v>
+        <v>1.129207408926894</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.383298487550544</v>
+        <v>3.455961275826008</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.92483474149914</v>
+        <v>-2.939385215630351</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.768704280577679</v>
+        <v>1.762884090925194</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.018166071241582</v>
+        <v>1.139270718367356</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.549894244236032</v>
+        <v>3.622557032511496</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.850052480474127</v>
+        <v>-2.864602954605338</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.918730094205501</v>
+        <v>1.912909904553017</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.092948332266595</v>
+        <v>1.214052979392369</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.714876510068856</v>
+        <v>3.787539298344321</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.823968396210319</v>
+        <v>-2.83851887034153</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.920871703924883</v>
+        <v>1.915051514272399</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.092948332266595</v>
+        <v>1.214052979392369</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.706584486082715</v>
+        <v>3.77924727435818</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.736090483101199</v>
+        <v>-2.75064095723241</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.954216064752311</v>
+        <v>1.948395875099826</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.208873974689946</v>
+        <v>1.32997862181572</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.774333067120506</v>
+        <v>3.84699585539597</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.727198021707915</v>
+        <v>-2.861820410764344</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.975327455036416</v>
+        <v>1.921478499413844</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.208873974689946</v>
+        <v>1.32997862181572</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.791887472847297</v>
+        <v>3.864550261122762</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.895674138677793</v>
+        <v>-3.030296527734222</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.899792055653049</v>
+        <v>1.845943100030477</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.180926138973365</v>
+        <v>1.30203078609914</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.766973818821933</v>
+        <v>3.839636607097397</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.19787460981621</v>
+        <v>-2.332496998872639</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.160181564385544</v>
+        <v>2.106332608762972</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.110578079602955</v>
+        <v>1.231682726728729</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.706034680387548</v>
+        <v>3.778697468663013</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.175153506133057</v>
+        <v>-2.309775895189486</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.159934028355709</v>
+        <v>2.106085072733137</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.110578079602955</v>
+        <v>1.231682726728729</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.696698702884452</v>
+        <v>3.769361491159917</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.3043553194271</v>
+        <v>-2.438977708483529</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.267159428889261</v>
+        <v>2.21331047326669</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9813762663089125</v>
+        <v>1.102480913434687</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.778083740759196</v>
+        <v>3.850746529034661</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.459136326205355</v>
+        <v>-2.593758715261784</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.242324848671606</v>
+        <v>2.188475893049034</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9480085922544363</v>
+        <v>1.069113239380211</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.795140958820157</v>
+        <v>3.867803747095621</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.452081635990182</v>
+        <v>-2.586704025046611</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.24182208074722</v>
+        <v>2.187973125124649</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9550632824696101</v>
+        <v>1.076167929595384</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.796049128938806</v>
+        <v>3.868711917214271</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.425130411663694</v>
+        <v>-2.559752800720123</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.262608724122557</v>
+        <v>2.208759768499985</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9699436284973293</v>
+        <v>1.091048275623103</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.814983490200179</v>
+        <v>3.887646278475644</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.56108341972001</v>
+        <v>-2.695705808776439</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.39233065304499</v>
+        <v>2.338481697422418</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9699436284973293</v>
+        <v>1.091048275623103</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.999086622345139</v>
+        <v>4.071749410620604</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.583491537524882</v>
+        <v>-2.718113926581311</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.375484100826035</v>
+        <v>2.321635145203463</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9699436284973293</v>
+        <v>1.091048275623103</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.991203317248132</v>
+        <v>4.063866105523597</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.611715773102482</v>
+        <v>-2.746338162158911</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.366248406144632</v>
+        <v>2.31239945052206</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9879203809486379</v>
+        <v>1.109025028074412</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.004043368268555</v>
+        <v>4.076706156544019</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.759719822713479</v>
+        <v>-2.755779088047441</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.363300504022081</v>
+        <v>2.364876797888495</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9884505206543066</v>
+        <v>1.231452145617804</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.060615169813803</v>
+        <v>4.206416144791902</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.81199343004912</v>
+        <v>-2.808052695383083</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.345282155633125</v>
+        <v>2.34685844949954</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9361769133186654</v>
+        <v>1.179178538282162</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.03214209995772</v>
+        <v>4.177943074935818</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.888323407650026</v>
+        <v>-2.884382672983989</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.312861977486538</v>
+        <v>2.314438271352953</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9361769133186654</v>
+        <v>1.179178538282162</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.030253912851495</v>
+        <v>4.176054887829593</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.090577127974379</v>
+        <v>-3.086636393308342</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.226780718959659</v>
+        <v>2.228357012826073</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.733923192994312</v>
+        <v>0.9769248179578087</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.903721910259745</v>
+        <v>4.049522885237843</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.252145553501634</v>
+        <v>-3.248204818835597</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.160587358958909</v>
+        <v>2.162163652825324</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6071402691964326</v>
+        <v>0.8501418941599294</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.826086166191169</v>
+        <v>3.971887141169268</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389346</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.384446845599188</v>
+        <v>-3.38050611093315</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.120740248985806</v>
+        <v>2.122316542852221</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6071402691964326</v>
+        <v>0.8501418941599294</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.839159573057088</v>
+        <v>3.984960548035186</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.570315156438418</v>
+        <v>-3.56637442177238</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.038398121433054</v>
+        <v>2.039974415299469</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4485746758764849</v>
+        <v>0.6915763008399817</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.73602541384806</v>
+        <v>3.881826388826158</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.598215943547891</v>
+        <v>-3.594275208881853</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.025761847716267</v>
+        <v>2.027338141582682</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4139777517335501</v>
+        <v>0.6569793766970469</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.713791300489301</v>
+        <v>3.859592275467399</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.720742046250785</v>
+        <v>-3.716801311584747</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.973515850612308</v>
+        <v>1.975092144478723</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2914516490306562</v>
+        <v>0.534453273994153</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.637040082844763</v>
+        <v>3.782841057822861</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.951256542436373</v>
+        <v>-3.947315807770336</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.948016011728576</v>
+        <v>1.949592305594991</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.06093715284506751</v>
+        <v>0.3039387778085643</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.565437344723914</v>
+        <v>3.711238319702012</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.207977360431197</v>
+        <v>-4.204036625765159</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.985639403532494</v>
+        <v>1.987215697398909</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.04747742129874732</v>
+        <v>0.1955242036647494</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.640700319239472</v>
+        <v>3.78650129421757</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.361963778207338</v>
+        <v>-4.3580230435413</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.993025105567678</v>
+        <v>1.994601399434092</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.04747742129874732</v>
+        <v>0.1955242036647494</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.709680588385111</v>
+        <v>3.85548156336321</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.311441874379672</v>
+        <v>-4.307501139713634</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.999285069218864</v>
+        <v>2.00086136308528</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.04747742129874732</v>
+        <v>0.1955242036647494</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.695731790505232</v>
+        <v>3.84153276548333</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.563917028387396</v>
+        <v>-4.559976293721358</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.910165496671189</v>
+        <v>1.911741790537604</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.04747742129874732</v>
+        <v>0.1955242036647494</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.707602279560646</v>
+        <v>3.853403254538744</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.856812784866809</v>
+        <v>-4.85287205020077</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.794217728598368</v>
+        <v>1.795794022464783</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.04747742129874732</v>
+        <v>0.1955242036647494</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.70881281407959</v>
+        <v>3.854613789057688</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.01435685659625</v>
+        <v>-5.010416121930212</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.735321842133912</v>
+        <v>1.736898136000327</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1143792264390218</v>
+        <v>0.1286223985244749</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.672793473222747</v>
+        <v>3.818594448200845</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.292321252179524</v>
+        <v>-5.288380517513485</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.619213936636792</v>
+        <v>1.620790230503208</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2039989607245061</v>
+        <v>0.03900266423899068</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.614099485387646</v>
+        <v>3.759900460365744</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.409288944818415</v>
+        <v>-5.405348210152376</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.73463091628028</v>
+        <v>1.736207210146695</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2039989607245061</v>
+        <v>0.03900266423899068</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.77630354208669</v>
+        <v>3.922104517064788</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.494006887039368</v>
+        <v>-5.49006615237333</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.695590377355713</v>
+        <v>1.697166671222128</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.2891149896525524</v>
+        <v>-0.04611336468905569</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.720080562693676</v>
+        <v>3.865881537671774</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.575941705308251</v>
+        <v>-5.572000970642213</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.673045867616651</v>
+        <v>1.674622161483066</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.2990497352396326</v>
+        <v>-0.05604811027613588</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.724349132909919</v>
+        <v>3.870150107888017</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.677917827556659</v>
+        <v>-5.67397709289062</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.64118105717319</v>
+        <v>1.642757351039605</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4010258574880402</v>
+        <v>-0.1580242325245435</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.672089098016777</v>
+        <v>3.817890072994875</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.567911544079437</v>
+        <v>-5.563970809413399</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.677336457808254</v>
+        <v>1.67891275167467</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.377821285570765</v>
+        <v>-0.1348196606072682</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.678164728411318</v>
+        <v>3.823965703389416</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.424851968338512</v>
+        <v>-5.420911233672474</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.738810298826599</v>
+        <v>1.740386592693014</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.3698078589807857</v>
+        <v>-0.126806234017289</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.687222795087279</v>
+        <v>3.833023770065378</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.123405242866674</v>
+        <v>-5.119464508200636</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.86664987189787</v>
+        <v>1.868226165764285</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.06836113350894846</v>
+        <v>0.1746404914545483</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.875351713252918</v>
+        <v>4.021152688231016</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.147995487101858</v>
+        <v>-5.14405475243582</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.857784951956507</v>
+        <v>1.859361245822922</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.06836113350894846</v>
+        <v>0.1746404914545483</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.876322891005628</v>
+        <v>4.022123865983726</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.096957111095338</v>
+        <v>-5.0930163764293</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.87904320673887</v>
+        <v>1.880619500605285</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.06836113350894846</v>
+        <v>0.1746404914545483</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.877165795385384</v>
+        <v>4.022966770363482</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.055817816228707</v>
+        <v>-5.051877081562669</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.914537023559668</v>
+        <v>1.916113317426083</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.02722183864231764</v>
+        <v>0.2157797863211791</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.920887471179507</v>
+        <v>4.066688446157605</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.945211676149105</v>
+        <v>-4.941270941483067</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.774963475715443</v>
+        <v>1.776539769581858</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.08338430143728437</v>
+        <v>0.3263859264007811</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.803435151351203</v>
+        <v>3.949236126329302</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.075792410679948</v>
+        <v>-5.071851676013909</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.72623322597707</v>
+        <v>1.727809519843485</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.04719643309355814</v>
+        <v>0.1958051918699386</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.728588754706661</v>
+        <v>3.87438972968476</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.911296076488986</v>
+        <v>-4.907355341822948</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.776458578729537</v>
+        <v>1.778034872595952</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.04719643309355814</v>
+        <v>0.1958051918699386</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.713015573782744</v>
+        <v>3.858816548760842</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.938666009173418</v>
+        <v>-4.93472527450738</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.764698316092194</v>
+        <v>1.766274609958609</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.04719643309355814</v>
+        <v>0.1958051918699386</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.712203284219174</v>
+        <v>3.858004259197272</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.949051204063307</v>
+        <v>-4.945110469397269</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.770413017261311</v>
+        <v>1.771989311127726</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.05758162798344746</v>
+        <v>0.1854199969800493</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.715840946410312</v>
+        <v>3.861641921388411</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735279</v>
+        <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.967639362785532</v>
+        <v>-4.963698628119494</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.833814759548846</v>
+        <v>1.835391053415261</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.07616978670567282</v>
+        <v>0.1668318382578239</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.775525056953402</v>
+        <v>3.921326031931501</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.967937909481568</v>
+        <v>-4.96399717481553</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.83056435168873</v>
+        <v>1.832140645555145</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.07616978670567282</v>
+        <v>0.1668318382578239</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.772394067771701</v>
+        <v>3.918195042749799</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.867114775791141</v>
+        <v>-4.863174041125102</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.875424500104292</v>
+        <v>1.877000793970708</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.06370557122131898</v>
+        <v>0.1792960537421778</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.784403492001705</v>
+        <v>3.930204466979803</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.676333415038734</v>
+        <v>-4.672392680372695</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.951866297883798</v>
+        <v>1.953442591750214</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.1270757895310884</v>
+        <v>0.3700774144945851</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.899001561931692</v>
+        <v>4.04480253690979</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.657816560996913</v>
+        <v>-4.653875826330875</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.939109885238123</v>
+        <v>1.940686179104539</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.1400059189562966</v>
+        <v>0.3830075439197934</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.886596485324414</v>
+        <v>4.032397460302512</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.632623376495595</v>
+        <v>-4.628682641829557</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.984154095650709</v>
+        <v>1.985730389517124</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.165199103457615</v>
+        <v>0.4082007284211117</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.936679332637263</v>
+        <v>4.082480307615361</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.620569249582632</v>
+        <v>-4.616628514916594</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.982662314317332</v>
+        <v>1.984238608183747</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.1772532303705778</v>
+        <v>0.4202548553340745</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.937598376686479</v>
+        <v>4.083399351664577</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.627192496272991</v>
+        <v>-4.623251761606952</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.981893645825324</v>
+        <v>1.983469939691739</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.1706299836802194</v>
+        <v>0.4136316086437162</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.9355050588564</v>
+        <v>4.081306033834498</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.524311906744398</v>
+        <v>-4.520371172078359</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.035896907514644</v>
+        <v>2.037473201381059</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.2735105732088123</v>
+        <v>0.5165121981723091</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.010084438451438</v>
+        <v>4.155885413429536</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760311</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.547753945924485</v>
+        <v>-4.543813211258446</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.046722762016203</v>
+        <v>2.048299055882619</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.2735105732088123</v>
+        <v>0.5165121981723091</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.030287108625032</v>
+        <v>4.17608808360313</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781701</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.565826454216096</v>
+        <v>-4.561885719550058</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.039493758699559</v>
+        <v>2.041070052565974</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.2735105732088123</v>
+        <v>0.5165121981723091</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.030287108625032</v>
+        <v>4.17608808360313</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.67006888808283</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.797000248092728</v>
+        <v>-4.79305951342669</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.907276154742372</v>
+        <v>1.908852448608788</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.2735105732088123</v>
+        <v>0.5165121981723091</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.990539022218499</v>
+        <v>4.136339997196597</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.739395451035904</v>
+        <v>-4.793659518816543</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.937340692562042</v>
+        <v>1.915635065449787</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.3311153702656364</v>
+        <v>0.5159121927824561</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.032124519449533</v>
+        <v>4.143002612959625</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.833839130484202</v>
+        <v>3.787415324383684</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.926949038727318</v>
+        <v>3.843263306343992</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.739395451035904</v>
+        <v>-4.730071517132487</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.937340692562042</v>
+        <v>1.95087827517725</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.3311153702656364</v>
+        <v>0.5795001944665124</v>
       </c>
       <c r="G2051" t="n">
-        <v>3.920012835713686</v>
+        <v>4.1909634230239</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240809.xlsx
+++ b/tame_output/ON/bt/strategyON_20240809.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.8%</t>
+          <t>421.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-634.6%</t>
+          <t>-624.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-181.1%</t>
+          <t>-177.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-43.0%</t>
+          <t>-36.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-166.1%</t>
+          <t>-161.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.0%</t>
+          <t>-173.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-31.3%</t>
         </is>
       </c>
     </row>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.127216565826382</v>
+        <v>-9.195082156200918</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4892890475006952</v>
+        <v>-0.5164352836505097</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.7102912862271</v>
+        <v>-1.701257507836702</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.135779231407345</v>
+        <v>2.141199498441584</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.253253359194671</v>
+        <v>-9.321118949569208</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5370100362188963</v>
+        <v>-0.5641562723687108</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.685039663417358</v>
+        <v>-1.67600588502696</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.153623933722305</v>
+        <v>2.159044200756544</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.19618158729874</v>
+        <v>-9.264047177673277</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.510190991774123</v>
+        <v>-0.5373372279239375</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.685039663417358</v>
+        <v>-1.67600588502696</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.157614269408707</v>
+        <v>2.163034536442945</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.337853429022861</v>
+        <v>-9.405719019397397</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5683349553625128</v>
+        <v>-0.5954811915123273</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.685039663417358</v>
+        <v>-1.67600588502696</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.156139042509965</v>
+        <v>2.161559309544203</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.288262584598026</v>
+        <v>-9.356128174972563</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.533445207427707</v>
+        <v>-0.5605914435775214</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.635448818992524</v>
+        <v>-1.626415040602126</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.200946959329737</v>
+        <v>2.206367226363976</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.13934425012617</v>
+        <v>-9.207209840500706</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4869290072856471</v>
+        <v>-0.5140752434354616</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.604199228257351</v>
+        <v>-1.595165449866953</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.206645580124158</v>
+        <v>2.212065847158397</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.91349909740676</v>
+        <v>-8.981364687781294</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3870118731616743</v>
+        <v>-0.4141581093114883</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.562272552670187</v>
+        <v>-1.55323877427979</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.241380658512665</v>
+        <v>2.246800925546903</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.788920441069168</v>
+        <v>-8.856786031443702</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3360412660705787</v>
+        <v>-0.3631875022203928</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.562272552670187</v>
+        <v>-1.55323877427979</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.242519803068724</v>
+        <v>2.247940070102962</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.841815729113454</v>
+        <v>-8.909681319487989</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3545656071261858</v>
+        <v>-0.3817118432759994</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.557317206581741</v>
+        <v>-1.548283428191343</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.248126784883899</v>
+        <v>2.253547051918138</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.769682553825573</v>
+        <v>-8.837548144200108</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.319978632772397</v>
+        <v>-0.3471248689222106</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.557317206581741</v>
+        <v>-1.548283428191343</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.253860489122536</v>
+        <v>2.259280756156774</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.698316161215926</v>
+        <v>-8.766181751590461</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3011693381224032</v>
+        <v>-0.3283155742722168</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.485950813972093</v>
+        <v>-1.476917035581695</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.286943062294459</v>
+        <v>2.292363329328698</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.604857127230702</v>
+        <v>-8.672722717605236</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2736692058412209</v>
+        <v>-0.3008154419910345</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.485950813972093</v>
+        <v>-1.476917035581695</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.277059580981552</v>
+        <v>2.28247984801579</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.59420394567727</v>
+        <v>-8.662069536051805</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2712424937192219</v>
+        <v>-0.298388729869036</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.485950813972093</v>
+        <v>-1.476917035581695</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.275225020482178</v>
+        <v>2.280645287516416</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.496296907000779</v>
+        <v>-8.564162497375314</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2323799932220867</v>
+        <v>-0.2595262293719003</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.417965064111537</v>
+        <v>-1.408931285721139</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.315716155425051</v>
+        <v>2.321136422459289</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.472343366024822</v>
+        <v>-8.540208956399356</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2221300706862097</v>
+        <v>-0.2492763068360238</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.394011523135579</v>
+        <v>-1.384977744745181</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.330756786156119</v>
+        <v>2.336177053190358</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.208283427702025</v>
+        <v>-8.276149018076559</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1297664115188431</v>
+        <v>-0.1569126476686571</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.129951584812783</v>
+        <v>-1.120917806422385</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.475932432988045</v>
+        <v>2.481352700022283</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.501203804197186</v>
+        <v>-7.569069394571721</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1502784042227914</v>
+        <v>0.1231321680729773</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.129951584812783</v>
+        <v>-1.120917806422385</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.473145399327744</v>
+        <v>2.478565666361982</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.461019505830996</v>
+        <v>-7.52888509620553</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1666957474571089</v>
+        <v>0.1395495113072949</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.089767286446592</v>
+        <v>-1.080733508056194</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.4975996022353</v>
+        <v>2.503019869269538</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.297619634891634</v>
+        <v>-7.365485225266168</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2314225170536108</v>
+        <v>0.2042762809037968</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9263674155072295</v>
+        <v>-0.9173336371168319</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.595006346019674</v>
+        <v>2.600426613053913</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.064138412662035</v>
+        <v>-7.132004003036569</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3327394347833024</v>
+        <v>0.3055931986334888</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6928861932776309</v>
+        <v>-0.6838524148872334</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.743019508195286</v>
+        <v>2.748439775229524</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.91447202165452</v>
+        <v>-6.982337612029054</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3897137808733495</v>
+        <v>0.3625675447235355</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.599982702035095</v>
+        <v>-0.5909489236446974</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.795869392627848</v>
+        <v>2.801289659662086</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.782196548023633</v>
+        <v>-6.850062138398168</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.437991457072731</v>
+        <v>0.410845220922917</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4677072284042083</v>
+        <v>-0.4586734500138108</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.870602163553407</v>
+        <v>2.876022430587645</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.626458215463892</v>
+        <v>-6.694323805838426</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5031018507842644</v>
+        <v>0.4759556146344508</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3119688958444667</v>
+        <v>-0.3029351174540692</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.966860223776889</v>
+        <v>2.972280490811127</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.377458416780311</v>
+        <v>-6.445324007154845</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6156081114813556</v>
+        <v>0.5884618753315416</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06296909716088606</v>
+        <v>-0.05393531877048852</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.129166444210696</v>
+        <v>3.134586711244934</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.483048406553415</v>
+        <v>-6.55091399692795</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.445396185972895</v>
+        <v>0.4182499498230814</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1685590869339904</v>
+        <v>-0.1595253085435929</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937836520747615</v>
+        <v>2.943256787781853</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.501783308672012</v>
+        <v>-6.569648899046546</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4864465670025426</v>
+        <v>0.459300330852729</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1741550965941217</v>
+        <v>-0.1651213182037242</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.983023256828622</v>
+        <v>2.98844352386286</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.353843267264413</v>
+        <v>-6.421708857638947</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4257436608774148</v>
+        <v>0.3985974247276012</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1538341806855641</v>
+        <v>-0.1448004022951666</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.875336883685589</v>
+        <v>2.880757150719828</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.300873745010424</v>
+        <v>-6.368739335384959</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4382174835255319</v>
+        <v>0.4110712473757183</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.09183088004117773</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.898404610784504</v>
+        <v>2.903824877818743</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.135085549050133</v>
+        <v>-6.202951139424668</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4975721498145553</v>
+        <v>0.4704259136647413</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.09183088004117773</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.891443998689411</v>
+        <v>2.89686426572365</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.101722342571365</v>
+        <v>-6.169587932945899</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5253797867872056</v>
+        <v>0.4982335506373921</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.09183088004117773</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.905906353070554</v>
+        <v>2.911326620104793</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.993463205448843</v>
+        <v>-6.061328795823377</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5632155620954094</v>
+        <v>0.5360693259455958</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.09183088004117773</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.900438473529749</v>
+        <v>2.905858740563988</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.870172070631712</v>
+        <v>-5.938037661006247</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6100301100328389</v>
+        <v>0.5828838738830249</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.02242647638555523</v>
+        <v>0.03146025477595277</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.971911248430605</v>
+        <v>2.977331515464843</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.849022871728269</v>
+        <v>-5.916888462102803</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6261907678315413</v>
+        <v>0.5990445316817277</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.04357567528899858</v>
+        <v>0.05260945367939612</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.992301746009995</v>
+        <v>2.997722013044234</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.605257429744825</v>
+        <v>-5.673123020119359</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7194776529719697</v>
+        <v>0.6923314168221557</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.04357567528899858</v>
+        <v>0.05260945367939612</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.988082454357046</v>
+        <v>2.993502721391285</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.50349460946753</v>
+        <v>-5.571360199842064</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7623070950029036</v>
+        <v>0.73516085885309</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.05679474368142728</v>
+        <v>0.06582852207182482</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.998138209312519</v>
+        <v>3.003558476346758</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.253644215518455</v>
+        <v>-5.321509805892989</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8549893275662357</v>
+        <v>0.8278430914164217</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.05679474368142728</v>
+        <v>0.06582852207182482</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.990880284296221</v>
+        <v>2.99630055133046</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.077752123051022</v>
+        <v>-5.145617713425557</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9289452880738573</v>
+        <v>0.9017990519240437</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.05679474368142728</v>
+        <v>0.06582852207182482</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.99447940781687</v>
+        <v>2.999899674851109</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.906305660028559</v>
+        <v>-4.974171250403093</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.010851379337397</v>
+        <v>0.9837051431875827</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2282412067038904</v>
+        <v>0.237274985094288</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.110674791684902</v>
+        <v>3.11609505871914</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.832016094290219</v>
+        <v>-4.899881684664754</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.039587683249029</v>
+        <v>1.012441447099215</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3025307724422297</v>
+        <v>0.3115645508326272</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.154269008744202</v>
+        <v>3.159689275778441</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.768380352056285</v>
+        <v>-4.83624594243082</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.06973678119692</v>
+        <v>1.042590545047106</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.3752002930665618</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.197145255138881</v>
+        <v>3.202565522173119</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.656953592730365</v>
+        <v>-4.724819183104899</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.095501743711084</v>
+        <v>1.06835550756127</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.3752002930665618</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.178339513922676</v>
+        <v>3.183759780956914</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.667456215795654</v>
+        <v>-4.735321806170188</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.093043771109846</v>
+        <v>1.065897534960032</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.3646976700012729</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.17378101670838</v>
+        <v>3.179201283742619</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.595213647624459</v>
+        <v>-4.663079237998994</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.125870112213144</v>
+        <v>1.09872387606333</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.3646976700012729</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.1777103305432</v>
+        <v>3.183130597577439</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.577499960746594</v>
+        <v>-4.645365551121128</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.13363417088163</v>
+        <v>1.106487934731816</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.3678789988981897</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.18029771179869</v>
+        <v>3.185717978832929</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.468695075266867</v>
+        <v>-4.536560665641401</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.174154196293514</v>
+        <v>1.1470079601437</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.3678789988981897</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.177295783018684</v>
+        <v>3.182716050052922</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.248674277229856</v>
+        <v>-4.316539867604391</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.263741552518933</v>
+        <v>1.236595316369119</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.5090988439661699</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.263606727070086</v>
+        <v>3.269026994104324</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.115806588166579</v>
+        <v>-4.183672178541113</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.332782810946067</v>
+        <v>1.305636574796253</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.5090988439661699</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.279500909871909</v>
+        <v>3.284921176906148</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.99563350480208</v>
+        <v>-4.063499095176614</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.381997888732168</v>
+        <v>1.354851652582355</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6202381489402713</v>
+        <v>0.6292719273306688</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.352750604330911</v>
+        <v>3.358170871365149</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.860380143472103</v>
+        <v>-3.928245733846637</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.446187335825599</v>
+        <v>1.419041099675785</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7554915102702484</v>
+        <v>0.764525288660646</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.443990723690337</v>
+        <v>3.449410990724575</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.920254970829795</v>
+        <v>-3.98812056120433</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.408274896283948</v>
+        <v>1.381128660134134</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.7046504613029538</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.394103318677147</v>
+        <v>3.399523585711386</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.800434739918958</v>
+        <v>-3.868300330293492</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.471492157882492</v>
+        <v>1.444345921732678</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.7046504613029538</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.409392487911356</v>
+        <v>3.414812754945594</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.802904446380764</v>
+        <v>-3.870770036755298</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.378148474620211</v>
+        <v>1.351002238470397</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6931469764507501</v>
+        <v>0.7021807548411476</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.315554863356714</v>
+        <v>3.320975130390952</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.871274632704774</v>
+        <v>-3.939140223079308</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.270062261575908</v>
+        <v>1.242916025426094</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.702422675486965</v>
+        <v>0.7114564538773626</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.240382144263744</v>
+        <v>3.245802411297983</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.88506268555182</v>
+        <v>-3.952928275926355</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.254983749068981</v>
+        <v>1.227837512919167</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.702422675486965</v>
+        <v>0.7114564538773626</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.230818852895635</v>
+        <v>3.236239119929874</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.94058276144441</v>
+        <v>-4.008448351818944</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.369806555404147</v>
+        <v>1.342660319254334</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.702422675486965</v>
+        <v>0.7114564538773626</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.367849689587838</v>
+        <v>3.373269956622076</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.765108501651941</v>
+        <v>-3.832974092026475</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.444563491312923</v>
+        <v>1.417417255163109</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.702422675486965</v>
+        <v>0.7114564538773626</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.372416921579625</v>
+        <v>3.377837188613864</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.876044754293189</v>
+        <v>-3.943910344667723</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.37593101901763</v>
+        <v>1.348784782867817</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.702422675486965</v>
+        <v>0.7114564538773626</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.348158950340832</v>
+        <v>3.353579217375071</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.842381208820907</v>
+        <v>-3.910246799195442</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.317934750607993</v>
+        <v>1.290788514458179</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.7451199993496445</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.296895391025652</v>
+        <v>3.30231565805989</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.782528589617184</v>
+        <v>-3.850394179991719</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.352048184721615</v>
+        <v>1.324901948571801</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.7451199993496445</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.307067777457784</v>
+        <v>3.312488044492023</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.696285126590807</v>
+        <v>-3.764150716965341</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.381491840506026</v>
+        <v>1.354345604356212</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.7451199993496445</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.302014048031644</v>
+        <v>3.307434315065882</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.741591945989787</v>
+        <v>-3.809457536364321</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.355144888190959</v>
+        <v>1.327998652041146</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.7043098363404137</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.269303725670631</v>
+        <v>3.27472399270487</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.770625050692088</v>
+        <v>-3.838490641066623</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.34408351934314</v>
+        <v>1.316937283193327</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.7043098363404137</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.269855598703733</v>
+        <v>3.275275865737971</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.677814569241229</v>
+        <v>-3.745680159615763</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.31048040381485</v>
+        <v>1.283334167665036</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7880865394008755</v>
+        <v>0.797120317791273</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.254814579465614</v>
+        <v>3.260234846499853</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.722204038570657</v>
+        <v>-3.790069628945191</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.294598092007679</v>
+        <v>1.267451855857866</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7436970700714478</v>
+        <v>0.7527308484618453</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.230054373792558</v>
+        <v>3.235474640826797</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.838745643675999</v>
+        <v>-3.906611234050534</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.243057158477265</v>
+        <v>1.215910922327452</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.6361892433565026</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.155205119241076</v>
+        <v>3.160625386275314</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.726368642493327</v>
+        <v>-3.794234232867861</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.293499254781002</v>
+        <v>1.266353018631188</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.6361892433565026</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.160696415071743</v>
+        <v>3.166116682105981</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.75414904039468</v>
+        <v>-3.822014630769214</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.293884297388999</v>
+        <v>1.266738061239186</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.599375067064752</v>
+        <v>0.6084088454551495</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.15552537809947</v>
+        <v>3.160945645133709</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.872529713124818</v>
+        <v>-3.940395303499353</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.084887748297597</v>
+        <v>1.057741512147784</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.5411909933041733</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.953550386809538</v>
+        <v>2.958970653843776</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.98114379156815</v>
+        <v>-4.049009381942684</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.16159177763947</v>
+        <v>1.134445541489657</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.5411909933041733</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.073700047528743</v>
+        <v>3.079120314562982</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.945734753320007</v>
+        <v>-4.013600343694541</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.190268419041051</v>
+        <v>1.163122182891237</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.5411909933041733</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.088213073631066</v>
+        <v>3.093633340665305</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.907351090761856</v>
+        <v>-3.97521668113639</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.20304132540668</v>
+        <v>1.175895089256866</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.5795746558623245</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.108662712508325</v>
+        <v>3.114082979542564</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.730234760726689</v>
+        <v>-3.798100351101223</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.270616886266048</v>
+        <v>1.243470650116234</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.5795746558623245</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.105391741353627</v>
+        <v>3.110812008387866</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.775327005560235</v>
+        <v>-3.843192595934769</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.253263380094543</v>
+        <v>1.226117143944729</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5086448343025372</v>
+        <v>0.5176786126929347</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.068937507213907</v>
+        <v>3.074357774248145</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.595951584321467</v>
+        <v>-3.663817174696002</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.318800523896464</v>
+        <v>1.291654287746651</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6654215924732558</v>
+        <v>0.6744553708636534</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.156790537422753</v>
+        <v>3.162210804456991</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.640965797842073</v>
+        <v>-3.708831388216608</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.281602293819812</v>
+        <v>1.254456057669998</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6350726971586512</v>
+        <v>0.6441064755490488</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.119388655565579</v>
+        <v>3.124808922599818</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.907970308114509</v>
+        <v>-3.975835898489043</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.180492052049783</v>
+        <v>1.15334581589997</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4407096591157026</v>
+        <v>0.4497434375061002</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.008462395078756</v>
+        <v>3.013882662112994</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.009168089551681</v>
+        <v>-4.077033679926216</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.139216861371416</v>
+        <v>1.112070625221602</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.381334623960781</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.966621028848066</v>
+        <v>2.972041295882304</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.002657122937369</v>
+        <v>-4.070522713311903</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.139421209571458</v>
+        <v>1.112274973421644</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.381334623960781</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.964220990402382</v>
+        <v>2.969641257436621</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.983618995230072</v>
+        <v>-4.051484585604606</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.143561179862621</v>
+        <v>1.116414943712807</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.3231510126295865</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.925835542811911</v>
+        <v>2.931255809846149</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.01474562638069</v>
+        <v>-4.082611216755224</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.250404929036564</v>
+        <v>1.223258692886751</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.3231510126295865</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.045129944446101</v>
+        <v>3.05055021148034</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.028612387714608</v>
+        <v>-4.096477978089142</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.245691553489131</v>
+        <v>1.218545317339317</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.276259317505366</v>
+        <v>0.2852930958957635</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.023248523391941</v>
+        <v>3.028668790426179</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.983808216174678</v>
+        <v>-4.051673806549212</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.269621752502029</v>
+        <v>1.242475516352215</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.276259317505366</v>
+        <v>0.2852930958957635</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.029257053788867</v>
+        <v>3.034677320823105</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.836065245939676</v>
+        <v>-3.90393083631421</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.226669161873229</v>
+        <v>1.199522925723415</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.4531004531306467</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.027891689406996</v>
+        <v>3.033311956441235</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.919886467214374</v>
+        <v>-3.987752057588908</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.195934294894831</v>
+        <v>1.168788058745017</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.4531004531306467</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.030685310938477</v>
+        <v>3.036105577972716</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.913733761161589</v>
+        <v>-3.981599351536124</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.199057725707603</v>
+        <v>1.171911489557789</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4502193807930334</v>
+        <v>0.459253159183431</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.035039282961806</v>
+        <v>3.040459549996045</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.930543059312091</v>
+        <v>-3.998408649686625</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.191414483187512</v>
+        <v>1.164268247037699</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.4424438610329293</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.024034180811615</v>
+        <v>3.029454447845854</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.868245060535969</v>
+        <v>-3.936110650910503</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.282669236494782</v>
+        <v>1.255523000344968</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.4424438610329293</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.090369734608436</v>
+        <v>3.095790001642675</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.666454862870811</v>
+        <v>-3.734320453245346</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.165677317274972</v>
+        <v>1.138531081125159</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6314282748116862</v>
+        <v>0.6404620532020837</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.011472651624056</v>
+        <v>3.016892918658295</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.717341575557006</v>
+        <v>-3.78520716593154</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.21561286452267</v>
+        <v>1.188466628372856</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5805415621254917</v>
+        <v>0.5895753405158892</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.051230856334515</v>
+        <v>3.056651123368753</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.630730832907199</v>
+        <v>-3.698596423281733</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.264884897698636</v>
+        <v>1.237738661548822</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6591672933306499</v>
+        <v>0.6682010717210475</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.113034031173653</v>
+        <v>3.118454298207892</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.690940130912483</v>
+        <v>-3.758805721287017</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.239337159321194</v>
+        <v>1.21219092317138</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.607991773715763</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.075444433195154</v>
+        <v>3.080864700229393</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.614518084480556</v>
+        <v>-3.682383674855091</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.268397595933893</v>
+        <v>1.24125135978408</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.607991773715763</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.073936051235083</v>
+        <v>3.079356318269321</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.570144952841988</v>
+        <v>-3.638010543216522</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.286009716024757</v>
+        <v>1.258863479874943</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.643331126963934</v>
+        <v>0.6523649053543316</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.10042279765366</v>
+        <v>3.105843064687899</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.592625303700872</v>
+        <v>-3.660490894075407</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.271411369819794</v>
+        <v>1.24426513366998</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.643331126963934</v>
+        <v>0.6523649053543316</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.094816591792251</v>
+        <v>3.100236858826489</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.544969573139817</v>
+        <v>-3.612835163514351</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.296855419072021</v>
+        <v>1.269709182922207</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6909868575249897</v>
+        <v>0.7000206359153872</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.129791787156689</v>
+        <v>3.135212054190927</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.444451414641062</v>
+        <v>-3.512317005015596</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.341955055846247</v>
+        <v>1.314808819696434</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7915050160237442</v>
+        <v>0.8005387944141418</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.194995055630666</v>
+        <v>3.200415322664905</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.428546085208709</v>
+        <v>-3.496411675583244</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.335071860095061</v>
+        <v>1.307925623945247</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7123923553145053</v>
+        <v>0.7214261337049028</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.134282131680995</v>
+        <v>3.139702398715233</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.480360442297912</v>
+        <v>-3.451573273974846</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.318443819870008</v>
+        <v>1.329958687199235</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.755938150818757</v>
+        <v>0.7259695666497723</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.164507311594174</v>
+        <v>3.146526161092784</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.49985889853992</v>
+        <v>-3.471071730216854</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.314805377004283</v>
+        <v>1.326320244333509</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7078535095388527</v>
+        <v>0.677884925369868</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.13981746645731</v>
+        <v>3.121836315955919</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.45565606145402</v>
+        <v>-3.426868893130953</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.33836611436648</v>
+        <v>1.349880981695707</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7520563466247532</v>
+        <v>0.7220877624557684</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.172218771236687</v>
+        <v>3.154237620735297</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.492635089117463</v>
+        <v>-3.463847920794397</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.32198450377035</v>
+        <v>1.333499371099577</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7890302484160837</v>
+        <v>0.759061664247099</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.192813112780733</v>
+        <v>3.174831962279343</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.334343671578191</v>
+        <v>-3.305556503255124</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.436548835969099</v>
+        <v>1.448063703298325</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7890302484160837</v>
+        <v>0.759061664247099</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.244060877963773</v>
+        <v>3.226079727462382</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.126701667943715</v>
+        <v>-3.097914499620648</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.518046342017142</v>
+        <v>1.529561209346369</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9966722520505598</v>
+        <v>0.9667036678815751</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.367086784738712</v>
+        <v>3.349105634237321</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.075669575221187</v>
+        <v>-3.04688240689812</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.533407407344424</v>
+        <v>1.54492227467365</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.047704344773088</v>
+        <v>1.017735760604103</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.392654268610499</v>
+        <v>3.374673118109108</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.010445394093981</v>
+        <v>-2.981658225770914</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.576684483888011</v>
+        <v>1.588199351217238</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.112928525900293</v>
+        <v>1.082959941731309</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.448976181379527</v>
+        <v>3.430995030878136</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.973018374022848</v>
+        <v>-2.944231205699781</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.587616264215745</v>
+        <v>1.599131131544971</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.118180063929475</v>
+        <v>1.08821147976049</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.448088076496316</v>
+        <v>3.430106925994926</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.993130030057556</v>
+        <v>-2.964342861734489</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.580828394133102</v>
+        <v>1.592343261462329</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.129207408926894</v>
+        <v>1.099238824757909</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.455961275826008</v>
+        <v>3.437980125324617</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.939385215630351</v>
+        <v>-2.910598047307284</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.762884090925194</v>
+        <v>1.774398958254421</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.139270718367356</v>
+        <v>1.109302134198372</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.622557032511496</v>
+        <v>3.604575882010105</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.864602954605338</v>
+        <v>-2.835815786282271</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.912909904553017</v>
+        <v>1.924424771882244</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.214052979392369</v>
+        <v>1.184084395223384</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.787539298344321</v>
+        <v>3.76955814784293</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.83851887034153</v>
+        <v>-2.809731702018464</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.915051514272399</v>
+        <v>1.926566381601625</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.214052979392369</v>
+        <v>1.184084395223384</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.77924727435818</v>
+        <v>3.761266123856789</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.75064095723241</v>
+        <v>-2.721853788909343</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.948395875099826</v>
+        <v>1.959910742429053</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.32997862181572</v>
+        <v>1.300010037646735</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.84699585539597</v>
+        <v>3.829014704894579</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.861820410764344</v>
+        <v>-2.71296132751606</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.921478499413844</v>
+        <v>1.981022132713158</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.32997862181572</v>
+        <v>1.300010037646735</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.864550261122762</v>
+        <v>3.84656911062137</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.030296527734222</v>
+        <v>-2.881437444485937</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.845943100030477</v>
+        <v>1.905486733329791</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.30203078609914</v>
+        <v>1.272062201930155</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.839636607097397</v>
+        <v>3.821655456596006</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.332496998872639</v>
+        <v>-2.183637915624354</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.106332608762972</v>
+        <v>2.165876242062286</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.231682726728729</v>
+        <v>1.201714142559744</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.778697468663013</v>
+        <v>3.760716318161621</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.309775895189486</v>
+        <v>-2.160916811941202</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.106085072733137</v>
+        <v>2.165628706032452</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.231682726728729</v>
+        <v>1.201714142559744</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.769361491159917</v>
+        <v>3.751380340658526</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.438977708483529</v>
+        <v>-2.290118625235244</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.21331047326669</v>
+        <v>2.272854106566004</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.102480913434687</v>
+        <v>1.072512329265702</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.850746529034661</v>
+        <v>3.83276537853327</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.593758715261784</v>
+        <v>-2.4448996320135</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.188475893049034</v>
+        <v>2.248019526348348</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.069113239380211</v>
+        <v>1.039144655211226</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.867803747095621</v>
+        <v>3.849822596594231</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.586704025046611</v>
+        <v>-2.437844941798326</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.187973125124649</v>
+        <v>2.247516758423962</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.076167929595384</v>
+        <v>1.046199345426399</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.868711917214271</v>
+        <v>3.85073076671288</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.559752800720123</v>
+        <v>-2.410893717471838</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.208759768499985</v>
+        <v>2.268303401799299</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.091048275623103</v>
+        <v>1.061079691454119</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.887646278475644</v>
+        <v>3.869665127974253</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.695705808776439</v>
+        <v>-2.546846725528154</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.338481697422418</v>
+        <v>2.398025330721732</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.091048275623103</v>
+        <v>1.061079691454119</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.071749410620604</v>
+        <v>4.053768260119213</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.718113926581311</v>
+        <v>-2.569254843333026</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.321635145203463</v>
+        <v>2.381178778502777</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.091048275623103</v>
+        <v>1.061079691454119</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.063866105523597</v>
+        <v>4.045884955022206</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.746338162158911</v>
+        <v>-2.597479078910627</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.31239945052206</v>
+        <v>2.371943083821374</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.109025028074412</v>
+        <v>1.079056443905427</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.076706156544019</v>
+        <v>4.058725006042629</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.755779088047441</v>
+        <v>-2.606920004799157</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.364876797888495</v>
+        <v>2.424420431187809</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.231452145617804</v>
+        <v>1.201483561448819</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.206416144791902</v>
+        <v>4.18843499429051</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.808052695383083</v>
+        <v>-2.659193612134798</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.34685844949954</v>
+        <v>2.406402082798853</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.179178538282162</v>
+        <v>1.149209954113177</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.177943074935818</v>
+        <v>4.159961924434427</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.884382672983989</v>
+        <v>-2.735523589735704</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.314438271352953</v>
+        <v>2.373981904652267</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.179178538282162</v>
+        <v>1.149209954113177</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.176054887829593</v>
+        <v>4.158073737328202</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.086636393308342</v>
+        <v>-2.937777310060057</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.228357012826073</v>
+        <v>2.287900646125387</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9769248179578087</v>
+        <v>0.9469562337888238</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.049522885237843</v>
+        <v>4.031541734736452</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.248204818835597</v>
+        <v>-3.099345735587312</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.162163652825324</v>
+        <v>2.221707286124638</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8501418941599294</v>
+        <v>0.8201733099909444</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.971887141169268</v>
+        <v>3.953905990667876</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.38050611093315</v>
+        <v>-3.231647027684866</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.122316542852221</v>
+        <v>2.181860176151535</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8501418941599294</v>
+        <v>0.8201733099909444</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.984960548035186</v>
+        <v>3.966979397533795</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.56637442177238</v>
+        <v>-3.417515338524096</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.039974415299469</v>
+        <v>2.099518048598783</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6915763008399817</v>
+        <v>0.6616077166709967</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.881826388826158</v>
+        <v>3.863845238324767</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.594275208881853</v>
+        <v>-3.445416125633569</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.027338141582682</v>
+        <v>2.086881774881996</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6569793766970469</v>
+        <v>0.6270107925280619</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.859592275467399</v>
+        <v>3.841611124966008</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.716801311584747</v>
+        <v>-3.567942228336463</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.975092144478723</v>
+        <v>2.034635777778037</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.534453273994153</v>
+        <v>0.504484689825168</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.782841057822861</v>
+        <v>3.76485990732147</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.947315807770336</v>
+        <v>-3.78295531649671</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.949592305594991</v>
+        <v>2.015336502104441</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3039387778085643</v>
+        <v>0.2894716016649202</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.711238319702012</v>
+        <v>3.702558014015825</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.204036625765159</v>
+        <v>-4.039676134491534</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.987215697398909</v>
+        <v>2.052959893908359</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1955242036647494</v>
+        <v>0.1810570275211054</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.78650129421757</v>
+        <v>3.777820988531383</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.3580230435413</v>
+        <v>-4.193662552267675</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.994601399434092</v>
+        <v>2.060345595943542</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1955242036647494</v>
+        <v>0.1810570275211054</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.85548156336321</v>
+        <v>3.846801257677023</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.307501139713634</v>
+        <v>-4.143140648440009</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.00086136308528</v>
+        <v>2.06660555959473</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1955242036647494</v>
+        <v>0.1810570275211054</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.84153276548333</v>
+        <v>3.832852459797144</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.559976293721358</v>
+        <v>-4.395615802447733</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.911741790537604</v>
+        <v>1.977485987047054</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1955242036647494</v>
+        <v>0.1810570275211054</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.853403254538744</v>
+        <v>3.844722948852558</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.85287205020077</v>
+        <v>-4.688511558927146</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.795794022464783</v>
+        <v>1.861538218974233</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1955242036647494</v>
+        <v>0.1810570275211054</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.854613789057688</v>
+        <v>3.845933483371502</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.010416121930212</v>
+        <v>-4.846055630656587</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.736898136000327</v>
+        <v>1.802642332509778</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1286223985244749</v>
+        <v>0.1141552223808309</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.818594448200845</v>
+        <v>3.809914142514658</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.288380517513485</v>
+        <v>-5.124020026239861</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.620790230503208</v>
+        <v>1.686534427012658</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.03900266423899068</v>
+        <v>0.02453548809534661</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.759900460365744</v>
+        <v>3.751220154679557</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.405348210152376</v>
+        <v>-5.240987718878752</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.736207210146695</v>
+        <v>1.801951406656146</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.03900266423899068</v>
+        <v>0.02453548809534661</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.922104517064788</v>
+        <v>3.913424211378602</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.49006615237333</v>
+        <v>-5.325705661099705</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.697166671222128</v>
+        <v>1.762910867731578</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04611336468905569</v>
+        <v>-0.06058054083269976</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.865881537671774</v>
+        <v>3.857201231985588</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.572000970642213</v>
+        <v>-5.407640479368588</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.674622161483066</v>
+        <v>1.740366357992516</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.05604811027613588</v>
+        <v>-0.07051528641977994</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.870150107888017</v>
+        <v>3.861469802201831</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.67397709289062</v>
+        <v>-5.509616601616996</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.642757351039605</v>
+        <v>1.708501547549055</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1580242325245435</v>
+        <v>-0.1724914086681875</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.817890072994875</v>
+        <v>3.809209767308689</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.563970809413399</v>
+        <v>-5.399610318139774</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.67891275167467</v>
+        <v>1.74465694818412</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1348196606072682</v>
+        <v>-0.1492868367509123</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.823965703389416</v>
+        <v>3.815285397703229</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.420911233672474</v>
+        <v>-5.256550742398849</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.740386592693014</v>
+        <v>1.806130789202464</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.126806234017289</v>
+        <v>-0.141273410160933</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.833023770065378</v>
+        <v>3.824343464379191</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.119464508200636</v>
+        <v>-4.955104016927011</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.868226165764285</v>
+        <v>1.933970362273735</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1746404914545483</v>
+        <v>0.1601733153109042</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.021152688231016</v>
+        <v>4.012472382544829</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.14405475243582</v>
+        <v>-4.979694261162195</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.859361245822922</v>
+        <v>1.925105442332372</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1746404914545483</v>
+        <v>0.1601733153109042</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.022123865983726</v>
+        <v>4.01344356029754</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.0930163764293</v>
+        <v>-4.928655885155675</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.880619500605285</v>
+        <v>1.946363697114735</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1746404914545483</v>
+        <v>0.1601733153109042</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.022966770363482</v>
+        <v>4.014286464677295</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.051877081562669</v>
+        <v>-4.887516590289044</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.916113317426083</v>
+        <v>1.981857513935533</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2157797863211791</v>
+        <v>0.201312610177535</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.066688446157605</v>
+        <v>4.058008140471419</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.941270941483067</v>
+        <v>-4.776910450209442</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.776539769581858</v>
+        <v>1.842283966091308</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3263859264007811</v>
+        <v>0.3119187502571371</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.949236126329302</v>
+        <v>3.940555820643115</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.071851676013909</v>
+        <v>-4.907491184740285</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.727809519843485</v>
+        <v>1.793553716352935</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1958051918699386</v>
+        <v>0.1813380157262945</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.87438972968476</v>
+        <v>3.865709423998573</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.907355341822948</v>
+        <v>-4.742994850549323</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.778034872595952</v>
+        <v>1.843779069105402</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.1958051918699386</v>
+        <v>0.1813380157262945</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.858816548760842</v>
+        <v>3.850136243074656</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.93472527450738</v>
+        <v>-4.770364783233755</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.766274609958609</v>
+        <v>1.832018806468059</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.1958051918699386</v>
+        <v>0.1813380157262945</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.858004259197272</v>
+        <v>3.849323953511085</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.945110469397269</v>
+        <v>-4.780749978123644</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.771989311127726</v>
+        <v>1.837733507637176</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1854199969800493</v>
+        <v>0.1709528208364052</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.861641921388411</v>
+        <v>3.852961615702224</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.963698628119494</v>
+        <v>-4.799338136845869</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.835391053415261</v>
+        <v>1.901135249924711</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1668318382578239</v>
+        <v>0.1523646621141799</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.921326031931501</v>
+        <v>3.912645726245314</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.96399717481553</v>
+        <v>-4.799636683541905</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.832140645555145</v>
+        <v>1.897884842064595</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1668318382578239</v>
+        <v>0.1523646621141799</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.918195042749799</v>
+        <v>3.909514737063613</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.863174041125102</v>
+        <v>-4.698813549851478</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.877000793970708</v>
+        <v>1.942744990480158</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.1792960537421778</v>
+        <v>0.1648288775985337</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.930204466979803</v>
+        <v>3.921524161293616</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.672392680372695</v>
+        <v>-4.508032189099071</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.953442591750214</v>
+        <v>2.019186788259664</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3700774144945851</v>
+        <v>0.3556102383509411</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.04480253690979</v>
+        <v>4.036122231223604</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.653875826330875</v>
+        <v>-4.48951533505725</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.940686179104539</v>
+        <v>2.006430375613988</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.3830075439197934</v>
+        <v>0.3685403677761493</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.032397460302512</v>
+        <v>4.023717154616326</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.628682641829557</v>
+        <v>-4.464322150555932</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.985730389517124</v>
+        <v>2.051474586026574</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4082007284211117</v>
+        <v>0.3937335522774676</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.082480307615361</v>
+        <v>4.073800001929175</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.616628514916594</v>
+        <v>-4.452268023642969</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.984238608183747</v>
+        <v>2.049982804693196</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4202548553340745</v>
+        <v>0.4057876791904305</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.083399351664577</v>
+        <v>4.07471904597839</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.623251761606952</v>
+        <v>-4.458891270333328</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.983469939691739</v>
+        <v>2.049214136201189</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4136316086437162</v>
+        <v>0.3991644325000721</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.081306033834498</v>
+        <v>4.072625728148311</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.520371172078359</v>
+        <v>-4.356010680804735</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.037473201381059</v>
+        <v>2.103217397890509</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5165121981723091</v>
+        <v>0.502045022028665</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.155885413429536</v>
+        <v>4.14720510774335</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.543813211258446</v>
+        <v>-4.379452719984822</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.048299055882619</v>
+        <v>2.114043252392069</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5165121981723091</v>
+        <v>0.502045022028665</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.17608808360313</v>
+        <v>4.167407777916944</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.561885719550058</v>
+        <v>-4.397525228276433</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.041070052565974</v>
+        <v>2.106814249075424</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5165121981723091</v>
+        <v>0.502045022028665</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.17608808360313</v>
+        <v>4.167407777916944</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.79305951342669</v>
+        <v>-4.628699022153065</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.908852448608788</v>
+        <v>1.974596645118238</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5165121981723091</v>
+        <v>0.502045022028665</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.136339997196597</v>
+        <v>4.12765969151041</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.793659518816543</v>
+        <v>-4.694920303624065</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.915635065449787</v>
+        <v>1.955130751526778</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.5159121927824561</v>
+        <v>0.4358237405576653</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.143002612959625</v>
+        <v>4.09494954162475</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.787415324383684</v>
+        <v>3.747640486745342</v>
       </c>
       <c r="C2051" t="n">
         <v>3.843263306343992</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.730071517132487</v>
+        <v>-4.628441681522764</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.95087827517725</v>
+        <v>1.991530209421139</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.5795001944665124</v>
+        <v>0.5074507973704261</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.1909634230239</v>
+        <v>4.147733784766248</v>
       </c>
     </row>
   </sheetData>
